--- a/Base_Maestra_Consolidada_Dialogos_Chatbot.xlsx
+++ b/Base_Maestra_Consolidada_Dialogos_Chatbot.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="21">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -146,8 +146,28 @@
       <color rgb="00808080"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00856404"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001F4E79"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="009C0006"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00065F46"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -197,6 +217,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+        <bgColor rgb="00DBEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F4F8"/>
+        <bgColor rgb="00F0F4F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -284,7 +334,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -390,6 +440,17 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2962,18 +3023,30 @@
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr"/>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>4 diálogos modificados: correcciones de junio no aplicadas — contacto reservas, day pass, camas twin, gimnasio</t>
+        </is>
+      </c>
       <c r="I46" s="6" t="inlineStr"/>
-      <c r="J46" s="5" t="inlineStr"/>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>El hotel reporta que estos 4 cambios ya se habían solicitado en junio y no se aplicaron en el chatbot; los reenvía</t>
+        </is>
+      </c>
+      <c r="K46" s="37" t="inlineStr">
+        <is>
+          <t>Pendiente actualización</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr"/>
@@ -3386,18 +3459,26 @@
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="F56" s="6" t="inlineStr"/>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H56" s="5" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="n"/>
       <c r="I56" s="6" t="inlineStr"/>
-      <c r="J56" s="5" t="inlineStr"/>
-      <c r="K56" s="5" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>Envió observaciones en formato ambiguo (mixto español/inglés); se registra como sin modificaciones hasta aclarar con el hotel</t>
+        </is>
+      </c>
+      <c r="K56" s="38" t="inlineStr">
+        <is>
+          <t>Sin modificaciones</t>
         </is>
       </c>
       <c r="L56" s="5" t="inlineStr"/>
@@ -3470,18 +3551,26 @@
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="F58" s="6" t="inlineStr"/>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H58" s="5" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="n"/>
       <c r="I58" s="6" t="inlineStr"/>
-      <c r="J58" s="5" t="inlineStr"/>
-      <c r="K58" s="5" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>Consultó sobre 2 teléfonos distintos en diálogos 10-04/10-06 vs. Reservation/Events; se registra como sin modificaciones hasta resolver la duda con el hotel</t>
+        </is>
+      </c>
+      <c r="K58" s="38" t="inlineStr">
+        <is>
+          <t>Sin modificaciones</t>
         </is>
       </c>
       <c r="L58" s="5" t="inlineStr"/>
@@ -3512,18 +3601,26 @@
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="F59" s="6" t="inlineStr"/>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H59" s="8" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>6 diálogos modificados: remodelación piscina/fechas, política menores, balcón, cajero ATM</t>
+        </is>
+      </c>
       <c r="I59" s="6" t="inlineStr"/>
-      <c r="J59" s="8" t="inlineStr"/>
-      <c r="K59" s="8" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+      <c r="J59" s="8" t="n"/>
+      <c r="K59" s="37" t="inlineStr">
+        <is>
+          <t>Pendiente actualización</t>
         </is>
       </c>
       <c r="L59" s="8" t="inlineStr"/>
@@ -3680,18 +3777,26 @@
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="F63" s="6" t="inlineStr"/>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H63" s="8" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="n"/>
       <c r="I63" s="6" t="inlineStr"/>
-      <c r="J63" s="8" t="inlineStr"/>
-      <c r="K63" s="8" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+      <c r="J63" s="8" t="inlineStr">
+        <is>
+          <t>Confirmó sin novedad para cambios</t>
+        </is>
+      </c>
+      <c r="K63" s="38" t="inlineStr">
+        <is>
+          <t>Sin modificaciones</t>
         </is>
       </c>
       <c r="L63" s="8" t="inlineStr"/>
@@ -3764,18 +3869,26 @@
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="F65" s="6" t="inlineStr"/>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H65" s="8" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>5 diálogos modificados: ubicación, check-in/out tardío, horario y tarifa de desayuno</t>
+        </is>
+      </c>
       <c r="I65" s="6" t="inlineStr"/>
-      <c r="J65" s="8" t="inlineStr"/>
-      <c r="K65" s="8" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+      <c r="J65" s="8" t="n"/>
+      <c r="K65" s="37" t="inlineStr">
+        <is>
+          <t>Pendiente actualización</t>
         </is>
       </c>
       <c r="L65" s="8" t="inlineStr"/>
@@ -3806,18 +3919,26 @@
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="F66" s="6" t="inlineStr"/>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H66" s="5" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>2 diálogos modificados: check-in y check-out anticipado/tardío (aclaración de impuestos)</t>
+        </is>
+      </c>
       <c r="I66" s="6" t="inlineStr"/>
-      <c r="J66" s="5" t="inlineStr"/>
-      <c r="K66" s="5" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+      <c r="J66" s="5" t="n"/>
+      <c r="K66" s="37" t="inlineStr">
+        <is>
+          <t>Pendiente actualización</t>
         </is>
       </c>
       <c r="L66" s="5" t="inlineStr"/>
@@ -3848,18 +3969,26 @@
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="F67" s="6" t="inlineStr"/>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H67" s="8" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>2 diálogos modificados: cajero automático, horario y marcación de room service</t>
+        </is>
+      </c>
       <c r="I67" s="6" t="inlineStr"/>
-      <c r="J67" s="8" t="inlineStr"/>
-      <c r="K67" s="8" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+      <c r="J67" s="8" t="n"/>
+      <c r="K67" s="37" t="inlineStr">
+        <is>
+          <t>Pendiente actualización</t>
         </is>
       </c>
       <c r="L67" s="8" t="inlineStr"/>
@@ -3974,16 +4103,20 @@
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="F70" s="6" t="inlineStr"/>
+      <c r="F70" s="6" t="n"/>
       <c r="G70" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H70" s="5" t="inlineStr"/>
+      <c r="H70" s="5" t="n"/>
       <c r="I70" s="6" t="inlineStr"/>
-      <c r="J70" s="5" t="inlineStr"/>
-      <c r="K70" s="5" t="inlineStr">
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>Confirmó recibido (09/07) pero a la fecha no ha enviado la revisión</t>
+        </is>
+      </c>
+      <c r="K70" s="39" t="inlineStr">
         <is>
           <t>Sin respuesta</t>
         </is>
@@ -4268,18 +4401,26 @@
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="F77" s="6" t="inlineStr"/>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H77" s="8" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t>4 diálogos modificados: contacto recepción, tarifas check-in/out, room service 24/7</t>
+        </is>
+      </c>
       <c r="I77" s="6" t="inlineStr"/>
-      <c r="J77" s="8" t="inlineStr"/>
-      <c r="K77" s="8" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+      <c r="J77" s="8" t="n"/>
+      <c r="K77" s="37" t="inlineStr">
+        <is>
+          <t>Pendiente actualización</t>
         </is>
       </c>
       <c r="L77" s="8" t="inlineStr"/>
@@ -4352,18 +4493,26 @@
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="F79" s="6" t="inlineStr"/>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="8" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>15 diálogos modificados: empleos, propinas, bar, spa x2, restaurante x6, brunch, san valentín, distancia al centro, celebraciones</t>
+        </is>
+      </c>
       <c r="I79" s="6" t="inlineStr"/>
-      <c r="J79" s="8" t="inlineStr"/>
-      <c r="K79" s="8" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+      <c r="J79" s="8" t="n"/>
+      <c r="K79" s="37" t="inlineStr">
+        <is>
+          <t>Pendiente actualización</t>
         </is>
       </c>
       <c r="L79" s="8" t="inlineStr"/>
@@ -4394,18 +4543,26 @@
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="F80" s="6" t="inlineStr"/>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="5" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>8 diálogos modificados: check-in/out, desayuno horario/precio, niños, mascotas, redes, restaurante</t>
+        </is>
+      </c>
       <c r="I80" s="6" t="inlineStr"/>
-      <c r="J80" s="5" t="inlineStr"/>
-      <c r="K80" s="5" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+      <c r="J80" s="5" t="n"/>
+      <c r="K80" s="37" t="inlineStr">
+        <is>
+          <t>Pendiente actualización</t>
         </is>
       </c>
       <c r="L80" s="5" t="inlineStr"/>
@@ -4847,23 +5004,23 @@
         <v>42</v>
       </c>
       <c r="C5" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D5" s="12" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G5" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="I5" s="17">
@@ -4986,23 +5143,23 @@
         <v>42</v>
       </c>
       <c r="C4" s="19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D4" s="19" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E4" s="19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F4" s="19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4" s="20" t="n">
-        <v>0</v>
+        <v>0.2619047619047619</v>
       </c>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t>░░░░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
+          <t>████████░░░░░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
       <c r="I4" s="22" t="inlineStr">
@@ -5056,23 +5213,23 @@
         <v>84</v>
       </c>
       <c r="C6" s="28" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D6" s="28" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E6" s="28" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G6" s="29" t="n">
-        <v>0.2738095238095238</v>
+        <v>0.4047619047619048</v>
       </c>
       <c r="H6" s="30" t="inlineStr">
         <is>
-          <t>████████░░░░░░░░░░░░░░░░░░░░░░</t>
+          <t>████████████░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
       <c r="I6" s="28" t="inlineStr"/>
@@ -5101,7 +5258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H273"/>
+  <dimension ref="A1:H319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -15445,6 +15602,1754 @@
         </is>
       </c>
       <c r="H273" s="8" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B274" s="41" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="C274" s="41" t="inlineStr">
+        <is>
+          <t>10-04</t>
+        </is>
+      </c>
+      <c r="D274" s="41" t="inlineStr">
+        <is>
+          <t>Reservation modification</t>
+        </is>
+      </c>
+      <c r="E274" s="41" t="inlineStr">
+        <is>
+          <t>Teléfono de contacto</t>
+        </is>
+      </c>
+      <c r="F274" s="41" t="inlineStr">
+        <is>
+          <t>+57 6056605831 (no se actualizó desde junio)</t>
+        </is>
+      </c>
+      <c r="G274" s="41" t="inlineStr">
+        <is>
+          <t>+57 3160107651</t>
+        </is>
+      </c>
+      <c r="H274" s="41" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B275" s="41" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="C275" s="41" t="inlineStr">
+        <is>
+          <t>10-41</t>
+        </is>
+      </c>
+      <c r="D275" s="41" t="inlineStr">
+        <is>
+          <t>Day use / day pass</t>
+        </is>
+      </c>
+      <c r="E275" s="41" t="inlineStr">
+        <is>
+          <t>Precio</t>
+        </is>
+      </c>
+      <c r="F275" s="41" t="inlineStr">
+        <is>
+          <t>$150.000 COP tarifa única (no se actualizó desde junio)</t>
+        </is>
+      </c>
+      <c r="G275" s="41" t="inlineStr">
+        <is>
+          <t>$240.000 COP adultos / $120.000 COP niños</t>
+        </is>
+      </c>
+      <c r="H275" s="41" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B276" s="41" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="C276" s="41" t="inlineStr">
+        <is>
+          <t>15-26</t>
+        </is>
+      </c>
+      <c r="D276" s="41" t="inlineStr">
+        <is>
+          <t>Twin beds</t>
+        </is>
+      </c>
+      <c r="E276" s="41" t="inlineStr">
+        <is>
+          <t>Teléfono de contacto</t>
+        </is>
+      </c>
+      <c r="F276" s="41" t="inlineStr">
+        <is>
+          <t>Tel +57 (605) 660 5831 (no se actualizó desde junio)</t>
+        </is>
+      </c>
+      <c r="G276" s="41" t="inlineStr">
+        <is>
+          <t>Celular +57 3160107651</t>
+        </is>
+      </c>
+      <c r="H276" s="41" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B277" s="41" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="C277" s="41" t="inlineStr">
+        <is>
+          <t>17-31</t>
+        </is>
+      </c>
+      <c r="D277" s="41" t="inlineStr">
+        <is>
+          <t>Fitness gym</t>
+        </is>
+      </c>
+      <c r="E277" s="41" t="inlineStr">
+        <is>
+          <t>Instalaciones disponibles</t>
+        </is>
+      </c>
+      <c r="F277" s="41" t="inlineStr">
+        <is>
+          <t>Duchas y taquillas disponibles (no se actualizó desde junio)</t>
+        </is>
+      </c>
+      <c r="G277" s="41" t="inlineStr">
+        <is>
+          <t>No hay duchas ni taquillas; sí hay toallas y estación de agua filtrada</t>
+        </is>
+      </c>
+      <c r="H277" s="41" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B278" s="41" t="inlineStr">
+        <is>
+          <t>GHL Relax Club Hotel el Puente</t>
+        </is>
+      </c>
+      <c r="C278" s="41" t="inlineStr">
+        <is>
+          <t>10-13</t>
+        </is>
+      </c>
+      <c r="D278" s="41" t="inlineStr">
+        <is>
+          <t>Opening, closing &amp; renovation</t>
+        </is>
+      </c>
+      <c r="E278" s="41" t="inlineStr">
+        <is>
+          <t>Estado de remodelación</t>
+        </is>
+      </c>
+      <c r="F278" s="41" t="inlineStr">
+        <is>
+          <t>Abrimos todo el año; sin remodelación prevista</t>
+        </is>
+      </c>
+      <c r="G278" s="41" t="inlineStr">
+        <is>
+          <t>Remodelación en curso; piscina principal, infantil y jacuzzi fuera de servicio hasta aprox. el 31 de agosto</t>
+        </is>
+      </c>
+      <c r="H278" s="41" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B279" s="41" t="inlineStr">
+        <is>
+          <t>GHL Relax Club Hotel el Puente</t>
+        </is>
+      </c>
+      <c r="C279" s="41" t="inlineStr">
+        <is>
+          <t>10-42</t>
+        </is>
+      </c>
+      <c r="D279" s="41" t="inlineStr">
+        <is>
+          <t>Day use reservation</t>
+        </is>
+      </c>
+      <c r="E279" s="41" t="inlineStr">
+        <is>
+          <t>Fecha fin remodelación</t>
+        </is>
+      </c>
+      <c r="F279" s="41" t="inlineStr">
+        <is>
+          <t>Hasta aprox. el 15 de junio</t>
+        </is>
+      </c>
+      <c r="G279" s="41" t="inlineStr">
+        <is>
+          <t>Hasta aprox. el 31 de agosto</t>
+        </is>
+      </c>
+      <c r="H279" s="41" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B280" s="41" t="inlineStr">
+        <is>
+          <t>GHL Relax Club Hotel el Puente</t>
+        </is>
+      </c>
+      <c r="C280" s="41" t="inlineStr">
+        <is>
+          <t>13-21</t>
+        </is>
+      </c>
+      <c r="D280" s="41" t="inlineStr">
+        <is>
+          <t>Kids</t>
+        </is>
+      </c>
+      <c r="E280" s="41" t="inlineStr">
+        <is>
+          <t>Política de ingreso de menores</t>
+        </is>
+      </c>
+      <c r="F280" s="41" t="inlineStr">
+        <is>
+          <t>Sin detalle de documentación requerida</t>
+        </is>
+      </c>
+      <c r="G280" s="41" t="inlineStr">
+        <is>
+          <t>Se agrega requisito de documento válido y autorización escrita para menores no acompañados por sus padres</t>
+        </is>
+      </c>
+      <c r="H280" s="41" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B281" s="41" t="inlineStr">
+        <is>
+          <t>GHL Relax Club Hotel el Puente</t>
+        </is>
+      </c>
+      <c r="C281" s="41" t="inlineStr">
+        <is>
+          <t>15-61</t>
+        </is>
+      </c>
+      <c r="D281" s="41" t="inlineStr">
+        <is>
+          <t>Balcony &amp; windows</t>
+        </is>
+      </c>
+      <c r="E281" s="41" t="inlineStr">
+        <is>
+          <t>Disponibilidad de balcón</t>
+        </is>
+      </c>
+      <c r="F281" s="41" t="inlineStr">
+        <is>
+          <t>Todas las habitaciones tienen balcón</t>
+        </is>
+      </c>
+      <c r="G281" s="41" t="inlineStr">
+        <is>
+          <t>Algunas habitaciones tienen balcón; no se reserva ubicación específica</t>
+        </is>
+      </c>
+      <c r="H281" s="41" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B282" s="41" t="inlineStr">
+        <is>
+          <t>GHL Relax Club Hotel el Puente</t>
+        </is>
+      </c>
+      <c r="C282" s="41" t="inlineStr">
+        <is>
+          <t>17-61</t>
+        </is>
+      </c>
+      <c r="D282" s="41" t="inlineStr">
+        <is>
+          <t>Swimming pool</t>
+        </is>
+      </c>
+      <c r="E282" s="41" t="inlineStr">
+        <is>
+          <t>Fecha fin remodelación</t>
+        </is>
+      </c>
+      <c r="F282" s="41" t="inlineStr">
+        <is>
+          <t>Hasta aprox. el 15 de junio</t>
+        </is>
+      </c>
+      <c r="G282" s="41" t="inlineStr">
+        <is>
+          <t>Hasta aprox. el 31 de agosto</t>
+        </is>
+      </c>
+      <c r="H282" s="41" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B283" s="41" t="inlineStr">
+        <is>
+          <t>GHL Relax Club Hotel el Puente</t>
+        </is>
+      </c>
+      <c r="C283" s="41" t="inlineStr">
+        <is>
+          <t>13-45</t>
+        </is>
+      </c>
+      <c r="D283" s="41" t="inlineStr">
+        <is>
+          <t>Change &amp; ATM</t>
+        </is>
+      </c>
+      <c r="E283" s="41" t="inlineStr">
+        <is>
+          <t>Cajero más cercano</t>
+        </is>
+      </c>
+      <c r="F283" s="41" t="inlineStr">
+        <is>
+          <t>Cajero ATH Eds Terpel / Banco Popular, Cra 5 #20-63, Girardot</t>
+        </is>
+      </c>
+      <c r="G283" s="41" t="inlineStr">
+        <is>
+          <t>C.cial Premier Jumbo Girardot: cajeros Bancolombia, BBVA, Servibanca, Avvillas</t>
+        </is>
+      </c>
+      <c r="H283" s="41" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B284" s="41" t="inlineStr">
+        <is>
+          <t>GHL Style Neiva</t>
+        </is>
+      </c>
+      <c r="C284" s="41" t="inlineStr">
+        <is>
+          <t>9-01</t>
+        </is>
+      </c>
+      <c r="D284" s="41" t="inlineStr">
+        <is>
+          <t>Ubicación</t>
+        </is>
+      </c>
+      <c r="E284" s="41" t="inlineStr">
+        <is>
+          <t>Dirección</t>
+        </is>
+      </c>
+      <c r="F284" s="41" t="inlineStr">
+        <is>
+          <t>⚠ No especificada en el diálogo previo</t>
+        </is>
+      </c>
+      <c r="G284" s="41" t="inlineStr">
+        <is>
+          <t>Cra. 16 #42-195, Comuna 2, Neiva, Huila, Colombia</t>
+        </is>
+      </c>
+      <c r="H284" s="41" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B285" s="41" t="inlineStr">
+        <is>
+          <t>GHL Style Neiva</t>
+        </is>
+      </c>
+      <c r="C285" s="41" t="inlineStr">
+        <is>
+          <t>11-01</t>
+        </is>
+      </c>
+      <c r="D285" s="41" t="inlineStr">
+        <is>
+          <t>Check-in time</t>
+        </is>
+      </c>
+      <c r="E285" s="41" t="inlineStr">
+        <is>
+          <t>Early check-in</t>
+        </is>
+      </c>
+      <c r="F285" s="41" t="inlineStr">
+        <is>
+          <t>Desde las 10:00, costo no especificado</t>
+        </is>
+      </c>
+      <c r="G285" s="41" t="inlineStr">
+        <is>
+          <t>Desde las 10:00, 150.000 COP por habitación, sujeto a disponibilidad</t>
+        </is>
+      </c>
+      <c r="H285" s="41" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B286" s="41" t="inlineStr">
+        <is>
+          <t>GHL Style Neiva</t>
+        </is>
+      </c>
+      <c r="C286" s="41" t="inlineStr">
+        <is>
+          <t>11-11</t>
+        </is>
+      </c>
+      <c r="D286" s="41" t="inlineStr">
+        <is>
+          <t>Check-out time</t>
+        </is>
+      </c>
+      <c r="E286" s="41" t="inlineStr">
+        <is>
+          <t>Check-out tardío</t>
+        </is>
+      </c>
+      <c r="F286" s="41" t="inlineStr">
+        <is>
+          <t>Hasta las 18:00, costo no especificado</t>
+        </is>
+      </c>
+      <c r="G286" s="41" t="inlineStr">
+        <is>
+          <t>Check-out regular hasta las 13:00; tardío hasta las 18:00 por 150.000 COP por habitación</t>
+        </is>
+      </c>
+      <c r="H286" s="41" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B287" s="41" t="inlineStr">
+        <is>
+          <t>GHL Style Neiva</t>
+        </is>
+      </c>
+      <c r="C287" s="41" t="inlineStr">
+        <is>
+          <t>12-01</t>
+        </is>
+      </c>
+      <c r="D287" s="41" t="inlineStr">
+        <is>
+          <t>Breakfast time</t>
+        </is>
+      </c>
+      <c r="E287" s="41" t="inlineStr">
+        <is>
+          <t>Horario desayuno</t>
+        </is>
+      </c>
+      <c r="F287" s="41" t="inlineStr">
+        <is>
+          <t>⚠ No especificado</t>
+        </is>
+      </c>
+      <c r="G287" s="41" t="inlineStr">
+        <is>
+          <t>Buffet diario de 6:30 a.m. a 10:00 a.m.</t>
+        </is>
+      </c>
+      <c r="H287" s="41" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B288" s="41" t="inlineStr">
+        <is>
+          <t>GHL Style Neiva</t>
+        </is>
+      </c>
+      <c r="C288" s="41" t="inlineStr">
+        <is>
+          <t>12-02</t>
+        </is>
+      </c>
+      <c r="D288" s="41" t="inlineStr">
+        <is>
+          <t>Breakfast rates</t>
+        </is>
+      </c>
+      <c r="E288" s="41" t="inlineStr">
+        <is>
+          <t>Precio adulto</t>
+        </is>
+      </c>
+      <c r="F288" s="41" t="inlineStr">
+        <is>
+          <t>⚠ No especificado</t>
+        </is>
+      </c>
+      <c r="G288" s="41" t="inlineStr">
+        <is>
+          <t>40.000 COP por adulto; incluido en tarifa de habitación; visitantes también bienvenidos</t>
+        </is>
+      </c>
+      <c r="H288" s="41" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B289" s="41" t="inlineStr">
+        <is>
+          <t>GHL Style Yopal</t>
+        </is>
+      </c>
+      <c r="C289" s="41" t="inlineStr">
+        <is>
+          <t>11-01</t>
+        </is>
+      </c>
+      <c r="D289" s="41" t="inlineStr">
+        <is>
+          <t>Check in time</t>
+        </is>
+      </c>
+      <c r="E289" s="41" t="inlineStr">
+        <is>
+          <t>Costo early check-in</t>
+        </is>
+      </c>
+      <c r="F289" s="41" t="inlineStr">
+        <is>
+          <t>70.000 COP por habitación</t>
+        </is>
+      </c>
+      <c r="G289" s="41" t="inlineStr">
+        <is>
+          <t>COP 70.000 + impuestos por habitación</t>
+        </is>
+      </c>
+      <c r="H289" s="41" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B290" s="41" t="inlineStr">
+        <is>
+          <t>GHL Style Yopal</t>
+        </is>
+      </c>
+      <c r="C290" s="41" t="inlineStr">
+        <is>
+          <t>11-11</t>
+        </is>
+      </c>
+      <c r="D290" s="41" t="inlineStr">
+        <is>
+          <t>Check out time</t>
+        </is>
+      </c>
+      <c r="E290" s="41" t="inlineStr">
+        <is>
+          <t>Costo late check-out</t>
+        </is>
+      </c>
+      <c r="F290" s="41" t="inlineStr">
+        <is>
+          <t>70.000 COP por habitación</t>
+        </is>
+      </c>
+      <c r="G290" s="41" t="inlineStr">
+        <is>
+          <t>COP 70.000 + impuestos por habitación</t>
+        </is>
+      </c>
+      <c r="H290" s="41" t="n"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B291" s="41" t="inlineStr">
+        <is>
+          <t>Hotel Tequendama Bogotá</t>
+        </is>
+      </c>
+      <c r="C291" s="41" t="inlineStr">
+        <is>
+          <t>13-45</t>
+        </is>
+      </c>
+      <c r="D291" s="41" t="inlineStr">
+        <is>
+          <t>Change &amp; ATM</t>
+        </is>
+      </c>
+      <c r="E291" s="41" t="inlineStr">
+        <is>
+          <t>Disponibilidad de cajero automático</t>
+        </is>
+      </c>
+      <c r="F291" s="41" t="inlineStr">
+        <is>
+          <t>Sí tenemos un cajero automático en la propiedad</t>
+        </is>
+      </c>
+      <c r="G291" s="41" t="inlineStr">
+        <is>
+          <t>No tenemos un cajero automático en la propiedad</t>
+        </is>
+      </c>
+      <c r="H291" s="41" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B292" s="41" t="inlineStr">
+        <is>
+          <t>Hotel Tequendama Bogotá</t>
+        </is>
+      </c>
+      <c r="C292" s="41" t="inlineStr">
+        <is>
+          <t>13-06</t>
+        </is>
+      </c>
+      <c r="D292" s="41" t="inlineStr">
+        <is>
+          <t>Room Service</t>
+        </is>
+      </c>
+      <c r="E292" s="41" t="inlineStr">
+        <is>
+          <t>Horario y marcación</t>
+        </is>
+      </c>
+      <c r="F292" s="41" t="inlineStr">
+        <is>
+          <t>Disponible de 06:00 a 22:00; marcar 2356</t>
+        </is>
+      </c>
+      <c r="G292" s="41" t="inlineStr">
+        <is>
+          <t>Disponible de 06:00 a 00:00; marcar *2</t>
+        </is>
+      </c>
+      <c r="H292" s="41" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B293" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Cusco</t>
+        </is>
+      </c>
+      <c r="C293" s="41" t="inlineStr">
+        <is>
+          <t>16-02</t>
+        </is>
+      </c>
+      <c r="D293" s="41" t="inlineStr">
+        <is>
+          <t>Contact staff — Recepción</t>
+        </is>
+      </c>
+      <c r="E293" s="41" t="inlineStr">
+        <is>
+          <t>Correo</t>
+        </is>
+      </c>
+      <c r="F293" s="41" t="inlineStr">
+        <is>
+          <t>recepcion.sonestahotelcusco@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="G293" s="41" t="inlineStr">
+        <is>
+          <t>recepcion.sonestacusco@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="H293" s="41" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B294" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Cusco</t>
+        </is>
+      </c>
+      <c r="C294" s="41" t="inlineStr">
+        <is>
+          <t>11-01</t>
+        </is>
+      </c>
+      <c r="D294" s="41" t="inlineStr">
+        <is>
+          <t>Check-in time</t>
+        </is>
+      </c>
+      <c r="E294" s="41" t="inlineStr">
+        <is>
+          <t>Costo early check-in</t>
+        </is>
+      </c>
+      <c r="F294" s="41" t="inlineStr">
+        <is>
+          <t>40.00 USD por habitación</t>
+        </is>
+      </c>
+      <c r="G294" s="41" t="inlineStr">
+        <is>
+          <t>60.00 USD por habitación (impuestos no incluidos)</t>
+        </is>
+      </c>
+      <c r="H294" s="41" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B295" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Cusco</t>
+        </is>
+      </c>
+      <c r="C295" s="41" t="inlineStr">
+        <is>
+          <t>11-11</t>
+        </is>
+      </c>
+      <c r="D295" s="41" t="inlineStr">
+        <is>
+          <t>Check-out time</t>
+        </is>
+      </c>
+      <c r="E295" s="41" t="inlineStr">
+        <is>
+          <t>Costo late check-out</t>
+        </is>
+      </c>
+      <c r="F295" s="41" t="inlineStr">
+        <is>
+          <t>40.00 USD por habitación</t>
+        </is>
+      </c>
+      <c r="G295" s="41" t="inlineStr">
+        <is>
+          <t>60.00 USD por habitación</t>
+        </is>
+      </c>
+      <c r="H295" s="41" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B296" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Cusco</t>
+        </is>
+      </c>
+      <c r="C296" s="41" t="inlineStr">
+        <is>
+          <t>13-06</t>
+        </is>
+      </c>
+      <c r="D296" s="41" t="inlineStr">
+        <is>
+          <t>Room service</t>
+        </is>
+      </c>
+      <c r="E296" s="41" t="inlineStr">
+        <is>
+          <t>Horario</t>
+        </is>
+      </c>
+      <c r="F296" s="41" t="inlineStr">
+        <is>
+          <t>Disponible de 06:00 a 21:00</t>
+        </is>
+      </c>
+      <c r="G296" s="41" t="inlineStr">
+        <is>
+          <t>Disponible 24/7</t>
+        </is>
+      </c>
+      <c r="H296" s="41" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B297" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C297" s="41" t="inlineStr">
+        <is>
+          <t>16-06</t>
+        </is>
+      </c>
+      <c r="D297" s="41" t="inlineStr">
+        <is>
+          <t>Jobs &amp; internships</t>
+        </is>
+      </c>
+      <c r="E297" s="41" t="inlineStr">
+        <is>
+          <t>Correo de contacto RR.HH.</t>
+        </is>
+      </c>
+      <c r="F297" s="41" t="inlineStr">
+        <is>
+          <t>contactenos@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="G297" s="41" t="inlineStr">
+        <is>
+          <t>laydy.pauca@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="H297" s="41" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B298" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C298" s="41" t="inlineStr">
+        <is>
+          <t>16-25</t>
+        </is>
+      </c>
+      <c r="D298" s="41" t="inlineStr">
+        <is>
+          <t>Tips policy</t>
+        </is>
+      </c>
+      <c r="E298" s="41" t="inlineStr">
+        <is>
+          <t>Política de propinas</t>
+        </is>
+      </c>
+      <c r="F298" s="41" t="inlineStr">
+        <is>
+          <t>Tarifa estándar incluye 19% de impuesto de servicio; propina habitual y opcional</t>
+        </is>
+      </c>
+      <c r="G298" s="41" t="inlineStr">
+        <is>
+          <t>Tarifa estándar incluye el cargo por servicio; propina opcional</t>
+        </is>
+      </c>
+      <c r="H298" s="41" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B299" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C299" s="41" t="inlineStr">
+        <is>
+          <t>17-01</t>
+        </is>
+      </c>
+      <c r="D299" s="41" t="inlineStr">
+        <is>
+          <t>Bar</t>
+        </is>
+      </c>
+      <c r="E299" s="41" t="inlineStr">
+        <is>
+          <t>Detalles bar Arcadia</t>
+        </is>
+      </c>
+      <c r="F299" s="41" t="inlineStr">
+        <is>
+          <t>Capacidad máx. 25 pax; se sirve comida; sin happy hour listado por separado</t>
+        </is>
+      </c>
+      <c r="G299" s="41" t="inlineStr">
+        <is>
+          <t>Se retira capacidad máxima y mención de comida servida; resto de condiciones igual</t>
+        </is>
+      </c>
+      <c r="H299" s="41" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B300" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C300" s="41" t="inlineStr">
+        <is>
+          <t>17-02</t>
+        </is>
+      </c>
+      <c r="D300" s="41" t="inlineStr">
+        <is>
+          <t>Bar reservation</t>
+        </is>
+      </c>
+      <c r="E300" s="41" t="inlineStr">
+        <is>
+          <t>Reservas de bar</t>
+        </is>
+      </c>
+      <c r="F300" s="41" t="inlineStr">
+        <is>
+          <t>No se toman reservas</t>
+        </is>
+      </c>
+      <c r="G300" s="41" t="inlineStr">
+        <is>
+          <t>Para reservar, contactar al +51 945739921</t>
+        </is>
+      </c>
+      <c r="H300" s="41" t="n"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B301" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C301" s="41" t="inlineStr">
+        <is>
+          <t>17-10</t>
+        </is>
+      </c>
+      <c r="D301" s="41" t="inlineStr">
+        <is>
+          <t>Spa</t>
+        </is>
+      </c>
+      <c r="E301" s="41" t="inlineStr">
+        <is>
+          <t>Tarifas y kit obligatorio</t>
+        </is>
+      </c>
+      <c r="F301" s="41" t="inlineStr">
+        <is>
+          <t>Precio de huésped variable; obligatorio: pantuflas y vestido de baño; no obligatorio: bata y gorro</t>
+        </is>
+      </c>
+      <c r="G301" s="41" t="inlineStr">
+        <is>
+          <t>Masajes con cargo adicional; obligatorio: pantuflas, gorro y vestido de baño; no obligatorio: bata</t>
+        </is>
+      </c>
+      <c r="H301" s="41" t="n"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B302" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C302" s="41" t="inlineStr">
+        <is>
+          <t>17-15</t>
+        </is>
+      </c>
+      <c r="D302" s="41" t="inlineStr">
+        <is>
+          <t>Spa hours</t>
+        </is>
+      </c>
+      <c r="E302" s="41" t="inlineStr">
+        <is>
+          <t>Límite de tiempo</t>
+        </is>
+      </c>
+      <c r="F302" s="41" t="inlineStr">
+        <is>
+          <t>Sin límite de tiempo</t>
+        </is>
+      </c>
+      <c r="G302" s="41" t="inlineStr">
+        <is>
+          <t>Estancia máxima de 1 hora</t>
+        </is>
+      </c>
+      <c r="H302" s="41" t="n"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B303" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C303" s="41" t="inlineStr">
+        <is>
+          <t>18-01</t>
+        </is>
+      </c>
+      <c r="D303" s="41" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E303" s="41" t="inlineStr">
+        <is>
+          <t>Descripción restaurante Micaela</t>
+        </is>
+      </c>
+      <c r="F303" s="41" t="inlineStr">
+        <is>
+          <t>Descripción extensa (tipo de cocina, capacidad, niños, reservas, cajas altas, etc.)</t>
+        </is>
+      </c>
+      <c r="G303" s="41" t="inlineStr">
+        <is>
+          <t>Descripción simplificada: horario, accesibilidad, mascotas no aceptadas</t>
+        </is>
+      </c>
+      <c r="H303" s="41" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B304" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C304" s="41" t="inlineStr">
+        <is>
+          <t>18-02</t>
+        </is>
+      </c>
+      <c r="D304" s="41" t="inlineStr">
+        <is>
+          <t>Restaurant reservation</t>
+        </is>
+      </c>
+      <c r="E304" s="41" t="inlineStr">
+        <is>
+          <t>Método de reserva</t>
+        </is>
+      </c>
+      <c r="F304" s="41" t="inlineStr">
+        <is>
+          <t>Reservar por correo a reservas.sonestaarequipa@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="G304" s="41" t="inlineStr">
+        <is>
+          <t>Contactar al +51 945739921</t>
+        </is>
+      </c>
+      <c r="H304" s="41" t="n"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B305" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C305" s="41" t="inlineStr">
+        <is>
+          <t>18-03</t>
+        </is>
+      </c>
+      <c r="D305" s="41" t="inlineStr">
+        <is>
+          <t>Restaurant reservation cancellation</t>
+        </is>
+      </c>
+      <c r="E305" s="41" t="inlineStr">
+        <is>
+          <t>Método de cancelación</t>
+        </is>
+      </c>
+      <c r="F305" s="41" t="inlineStr">
+        <is>
+          <t>Cancelar por correo</t>
+        </is>
+      </c>
+      <c r="G305" s="41" t="inlineStr">
+        <is>
+          <t>Contactar al +51 945739921</t>
+        </is>
+      </c>
+      <c r="H305" s="41" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B306" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C306" s="41" t="inlineStr">
+        <is>
+          <t>18-04</t>
+        </is>
+      </c>
+      <c r="D306" s="41" t="inlineStr">
+        <is>
+          <t>Restaurant reservation modification</t>
+        </is>
+      </c>
+      <c r="E306" s="41" t="inlineStr">
+        <is>
+          <t>Método de modificación</t>
+        </is>
+      </c>
+      <c r="F306" s="41" t="inlineStr">
+        <is>
+          <t>Modificar por correo</t>
+        </is>
+      </c>
+      <c r="G306" s="41" t="inlineStr">
+        <is>
+          <t>Contactar al +51 945739921</t>
+        </is>
+      </c>
+      <c r="H306" s="41" t="n"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B307" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C307" s="41" t="inlineStr">
+        <is>
+          <t>18-05</t>
+        </is>
+      </c>
+      <c r="D307" s="41" t="inlineStr">
+        <is>
+          <t>Restaurant reservation confirmation</t>
+        </is>
+      </c>
+      <c r="E307" s="41" t="inlineStr">
+        <is>
+          <t>Método de confirmación</t>
+        </is>
+      </c>
+      <c r="F307" s="41" t="inlineStr">
+        <is>
+          <t>Confirmar por correo</t>
+        </is>
+      </c>
+      <c r="G307" s="41" t="inlineStr">
+        <is>
+          <t>Contactar al +51 945739921</t>
+        </is>
+      </c>
+      <c r="H307" s="41" t="n"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B308" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C308" s="41" t="inlineStr">
+        <is>
+          <t>18-11</t>
+        </is>
+      </c>
+      <c r="D308" s="41" t="inlineStr">
+        <is>
+          <t>Brunch</t>
+        </is>
+      </c>
+      <c r="E308" s="41" t="inlineStr">
+        <is>
+          <t>Recomendación externa</t>
+        </is>
+      </c>
+      <c r="F308" s="41" t="inlineStr">
+        <is>
+          <t>No ofrecen brunch; recomiendan Restaurante Santé como alternativa externa</t>
+        </is>
+      </c>
+      <c r="G308" s="41" t="inlineStr">
+        <is>
+          <t>No ofrecemos brunch (se retira la recomendación externa)</t>
+        </is>
+      </c>
+      <c r="H308" s="41" t="n"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B309" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C309" s="41" t="inlineStr">
+        <is>
+          <t>18-26</t>
+        </is>
+      </c>
+      <c r="D309" s="41" t="inlineStr">
+        <is>
+          <t>Valentine's day</t>
+        </is>
+      </c>
+      <c r="E309" s="41" t="inlineStr">
+        <is>
+          <t>Forma de consulta</t>
+        </is>
+      </c>
+      <c r="F309" s="41" t="inlineStr">
+        <is>
+          <t>Ver oferta mediante enlace</t>
+        </is>
+      </c>
+      <c r="G309" s="41" t="inlineStr">
+        <is>
+          <t>Escribir a reservas.sonestaarequipa@ghlhoteles.com o contactar al +51 939753285</t>
+        </is>
+      </c>
+      <c r="H309" s="41" t="n"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B310" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C310" s="41" t="inlineStr">
+        <is>
+          <t>19-03</t>
+        </is>
+      </c>
+      <c r="D310" s="41" t="inlineStr">
+        <is>
+          <t>City center</t>
+        </is>
+      </c>
+      <c r="E310" s="41" t="inlineStr">
+        <is>
+          <t>Distancia al centro</t>
+        </is>
+      </c>
+      <c r="F310" s="41" t="inlineStr">
+        <is>
+          <t>26 m, 1 min caminando</t>
+        </is>
+      </c>
+      <c r="G310" s="41" t="inlineStr">
+        <is>
+          <t>4 km</t>
+        </is>
+      </c>
+      <c r="H310" s="41" t="n"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B311" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C311" s="41" t="inlineStr">
+        <is>
+          <t>20-21</t>
+        </is>
+      </c>
+      <c r="D311" s="41" t="inlineStr">
+        <is>
+          <t>Celebration</t>
+        </is>
+      </c>
+      <c r="E311" s="41" t="inlineStr">
+        <is>
+          <t>Teléfono de eventos</t>
+        </is>
+      </c>
+      <c r="F311" s="41" t="inlineStr">
+        <is>
+          <t>+51 945 739 48</t>
+        </is>
+      </c>
+      <c r="G311" s="41" t="inlineStr">
+        <is>
+          <t>+51 945 739 484 (corrección de dígito faltante)</t>
+        </is>
+      </c>
+      <c r="H311" s="41" t="n"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B312" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Bogotá</t>
+        </is>
+      </c>
+      <c r="C312" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D312" s="41" t="inlineStr">
+        <is>
+          <t>Check in time</t>
+        </is>
+      </c>
+      <c r="E312" s="41" t="inlineStr">
+        <is>
+          <t>Costo early check-in</t>
+        </is>
+      </c>
+      <c r="F312" s="41" t="inlineStr">
+        <is>
+          <t>Versión anterior</t>
+        </is>
+      </c>
+      <c r="G312" s="41" t="inlineStr">
+        <is>
+          <t>$35.000, sujeto a disponibilidad</t>
+        </is>
+      </c>
+      <c r="H312" s="41" t="n"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B313" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Bogotá</t>
+        </is>
+      </c>
+      <c r="C313" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D313" s="41" t="inlineStr">
+        <is>
+          <t>Check out time</t>
+        </is>
+      </c>
+      <c r="E313" s="41" t="inlineStr">
+        <is>
+          <t>Late check-out</t>
+        </is>
+      </c>
+      <c r="F313" s="41" t="inlineStr">
+        <is>
+          <t>Versión anterior</t>
+        </is>
+      </c>
+      <c r="G313" s="41" t="inlineStr">
+        <is>
+          <t>$35.000 por hora; después de las 6:00 p.m. se cobra la tarifa completa</t>
+        </is>
+      </c>
+      <c r="H313" s="41" t="n"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B314" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Bogotá</t>
+        </is>
+      </c>
+      <c r="C314" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D314" s="41" t="inlineStr">
+        <is>
+          <t>Breakfast time</t>
+        </is>
+      </c>
+      <c r="E314" s="41" t="inlineStr">
+        <is>
+          <t>Horario sábados, domingos y festivos</t>
+        </is>
+      </c>
+      <c r="F314" s="41" t="inlineStr">
+        <is>
+          <t>Versión anterior</t>
+        </is>
+      </c>
+      <c r="G314" s="41" t="inlineStr">
+        <is>
+          <t>6:30 a.m. a 10:30 a.m.</t>
+        </is>
+      </c>
+      <c r="H314" s="41" t="n"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B315" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Bogotá</t>
+        </is>
+      </c>
+      <c r="C315" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D315" s="41" t="inlineStr">
+        <is>
+          <t>Breakfast rates</t>
+        </is>
+      </c>
+      <c r="E315" s="41" t="inlineStr">
+        <is>
+          <t>Precio por persona</t>
+        </is>
+      </c>
+      <c r="F315" s="41" t="inlineStr">
+        <is>
+          <t>Versión anterior</t>
+        </is>
+      </c>
+      <c r="G315" s="41" t="inlineStr">
+        <is>
+          <t>$65.000 COP</t>
+        </is>
+      </c>
+      <c r="H315" s="41" t="n"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B316" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Bogotá</t>
+        </is>
+      </c>
+      <c r="C316" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D316" s="41" t="inlineStr">
+        <is>
+          <t>Kids</t>
+        </is>
+      </c>
+      <c r="E316" s="41" t="inlineStr">
+        <is>
+          <t>Tarifa niños</t>
+        </is>
+      </c>
+      <c r="F316" s="41" t="inlineStr">
+        <is>
+          <t>Versión anterior</t>
+        </is>
+      </c>
+      <c r="G316" s="41" t="inlineStr">
+        <is>
+          <t>Menores de 12 años gratis con sus padres; mayores de 12 años $80.000 por noche</t>
+        </is>
+      </c>
+      <c r="H316" s="41" t="n"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B317" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Bogotá</t>
+        </is>
+      </c>
+      <c r="C317" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D317" s="41" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="E317" s="41" t="inlineStr">
+        <is>
+          <t>Peso permitido</t>
+        </is>
+      </c>
+      <c r="F317" s="41" t="inlineStr">
+        <is>
+          <t>Versión anterior</t>
+        </is>
+      </c>
+      <c r="G317" s="41" t="inlineStr">
+        <is>
+          <t>10 kg</t>
+        </is>
+      </c>
+      <c r="H317" s="41" t="n"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B318" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Bogotá</t>
+        </is>
+      </c>
+      <c r="C318" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D318" s="41" t="inlineStr">
+        <is>
+          <t>Social &amp; photoshoot</t>
+        </is>
+      </c>
+      <c r="E318" s="41" t="inlineStr">
+        <is>
+          <t>Correo de contacto</t>
+        </is>
+      </c>
+      <c r="F318" s="41" t="inlineStr">
+        <is>
+          <t>Versión anterior</t>
+        </is>
+      </c>
+      <c r="G318" s="41" t="inlineStr">
+        <is>
+          <t>cateryne.palacios@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="H318" s="41" t="n"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B319" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Bogotá</t>
+        </is>
+      </c>
+      <c r="C319" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D319" s="41" t="inlineStr">
+        <is>
+          <t>Restaurant Cook's Restaurante</t>
+        </is>
+      </c>
+      <c r="E319" s="41" t="inlineStr">
+        <is>
+          <t>Horario de apertura</t>
+        </is>
+      </c>
+      <c r="F319" s="41" t="inlineStr">
+        <is>
+          <t>Versión anterior</t>
+        </is>
+      </c>
+      <c r="G319" s="41" t="inlineStr">
+        <is>
+          <t>6:00 a.m. a 12:00 p.m.</t>
+        </is>
+      </c>
+      <c r="H319" s="41" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:H227"/>

--- a/Base_Maestra_Consolidada_Dialogos_Chatbot.xlsx
+++ b/Base_Maestra_Consolidada_Dialogos_Chatbot.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -166,8 +166,13 @@
       <color rgb="00065F46"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00006100"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -247,6 +252,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F0F4F8"/>
         <bgColor rgb="00F0F4F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -334,7 +345,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -451,6 +462,9 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3038,15 +3052,19 @@
           <t>4 diálogos modificados: correcciones de junio no aplicadas — contacto reservas, day pass, camas twin, gimnasio</t>
         </is>
       </c>
-      <c r="I46" s="6" t="inlineStr"/>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
           <t>El hotel reporta que estos 4 cambios ya se habían solicitado en junio y no se aplicaron en el chatbot; los reenvía</t>
         </is>
       </c>
-      <c r="K46" s="37" t="inlineStr">
-        <is>
-          <t>Pendiente actualización</t>
+      <c r="K46" s="42" t="inlineStr">
+        <is>
+          <t>Actualizado</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr"/>
@@ -3616,11 +3634,15 @@
           <t>6 diálogos modificados: remodelación piscina/fechas, política menores, balcón, cajero ATM</t>
         </is>
       </c>
-      <c r="I59" s="6" t="inlineStr"/>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
       <c r="J59" s="8" t="n"/>
-      <c r="K59" s="37" t="inlineStr">
-        <is>
-          <t>Pendiente actualización</t>
+      <c r="K59" s="42" t="inlineStr">
+        <is>
+          <t>Actualizado</t>
         </is>
       </c>
       <c r="L59" s="8" t="inlineStr"/>
@@ -3884,11 +3906,15 @@
           <t>5 diálogos modificados: ubicación, check-in/out tardío, horario y tarifa de desayuno</t>
         </is>
       </c>
-      <c r="I65" s="6" t="inlineStr"/>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
       <c r="J65" s="8" t="n"/>
-      <c r="K65" s="37" t="inlineStr">
-        <is>
-          <t>Pendiente actualización</t>
+      <c r="K65" s="42" t="inlineStr">
+        <is>
+          <t>Actualizado</t>
         </is>
       </c>
       <c r="L65" s="8" t="inlineStr"/>
@@ -3934,11 +3960,15 @@
           <t>2 diálogos modificados: check-in y check-out anticipado/tardío (aclaración de impuestos)</t>
         </is>
       </c>
-      <c r="I66" s="6" t="inlineStr"/>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
       <c r="J66" s="5" t="n"/>
-      <c r="K66" s="37" t="inlineStr">
-        <is>
-          <t>Pendiente actualización</t>
+      <c r="K66" s="42" t="inlineStr">
+        <is>
+          <t>Actualizado</t>
         </is>
       </c>
       <c r="L66" s="5" t="inlineStr"/>
@@ -3984,11 +4014,15 @@
           <t>2 diálogos modificados: cajero automático, horario y marcación de room service</t>
         </is>
       </c>
-      <c r="I67" s="6" t="inlineStr"/>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
       <c r="J67" s="8" t="n"/>
-      <c r="K67" s="37" t="inlineStr">
-        <is>
-          <t>Pendiente actualización</t>
+      <c r="K67" s="42" t="inlineStr">
+        <is>
+          <t>Actualizado</t>
         </is>
       </c>
       <c r="L67" s="8" t="inlineStr"/>
@@ -4416,11 +4450,15 @@
           <t>4 diálogos modificados: contacto recepción, tarifas check-in/out, room service 24/7</t>
         </is>
       </c>
-      <c r="I77" s="6" t="inlineStr"/>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
       <c r="J77" s="8" t="n"/>
-      <c r="K77" s="37" t="inlineStr">
-        <is>
-          <t>Pendiente actualización</t>
+      <c r="K77" s="42" t="inlineStr">
+        <is>
+          <t>Actualizado</t>
         </is>
       </c>
       <c r="L77" s="8" t="inlineStr"/>
@@ -4508,11 +4546,15 @@
           <t>15 diálogos modificados: empleos, propinas, bar, spa x2, restaurante x6, brunch, san valentín, distancia al centro, celebraciones</t>
         </is>
       </c>
-      <c r="I79" s="6" t="inlineStr"/>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
       <c r="J79" s="8" t="n"/>
-      <c r="K79" s="37" t="inlineStr">
-        <is>
-          <t>Pendiente actualización</t>
+      <c r="K79" s="42" t="inlineStr">
+        <is>
+          <t>Actualizado</t>
         </is>
       </c>
       <c r="L79" s="8" t="inlineStr"/>
@@ -4558,11 +4600,15 @@
           <t>8 diálogos modificados: check-in/out, desayuno horario/precio, niños, mascotas, redes, restaurante</t>
         </is>
       </c>
-      <c r="I80" s="6" t="inlineStr"/>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
       <c r="J80" s="5" t="n"/>
-      <c r="K80" s="37" t="inlineStr">
-        <is>
-          <t>Pendiente actualización</t>
+      <c r="K80" s="42" t="inlineStr">
+        <is>
+          <t>Actualizado</t>
         </is>
       </c>
       <c r="L80" s="5" t="inlineStr"/>
@@ -5016,7 +5062,7 @@
         <v>3</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>

--- a/Base_Maestra_Consolidada_Dialogos_Chatbot.xlsx
+++ b/Base_Maestra_Consolidada_Dialogos_Chatbot.xlsx
@@ -3309,18 +3309,26 @@
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="F52" s="6" t="inlineStr"/>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="6" t="inlineStr"/>
-      <c r="J52" s="5" t="inlineStr"/>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>Confirmó sin cambios para julio</t>
+        </is>
+      </c>
+      <c r="K52" s="38" t="inlineStr">
+        <is>
+          <t>Sin modificaciones</t>
         </is>
       </c>
       <c r="L52" s="5" t="inlineStr"/>
@@ -3351,18 +3359,26 @@
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr"/>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr"/>
       <c r="I53" s="6" t="inlineStr"/>
-      <c r="J53" s="8" t="inlineStr"/>
-      <c r="K53" s="8" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+      <c r="J53" s="8" t="inlineStr">
+        <is>
+          <t>Confirmó sin cambios para julio</t>
+        </is>
+      </c>
+      <c r="K53" s="38" t="inlineStr">
+        <is>
+          <t>Sin modificaciones</t>
         </is>
       </c>
       <c r="L53" s="8" t="inlineStr"/>
@@ -3393,18 +3409,26 @@
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="F54" s="6" t="inlineStr"/>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr"/>
       <c r="I54" s="6" t="inlineStr"/>
-      <c r="J54" s="5" t="inlineStr"/>
-      <c r="K54" s="5" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>Confirmó sin cambios para julio</t>
+        </is>
+      </c>
+      <c r="K54" s="38" t="inlineStr">
+        <is>
+          <t>Sin modificaciones</t>
         </is>
       </c>
       <c r="L54" s="5" t="inlineStr"/>
@@ -5050,23 +5074,23 @@
         <v>42</v>
       </c>
       <c r="C5" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D5" s="12" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>8</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G5" s="12" t="n">
         <v>8</v>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="I5" s="17">
@@ -5189,23 +5213,23 @@
         <v>42</v>
       </c>
       <c r="C4" s="19" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D4" s="19" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E4" s="19" t="n">
         <v>8</v>
       </c>
       <c r="F4" s="19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G4" s="20" t="n">
-        <v>0.2619047619047619</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t>████████░░░░░░░░░░░░░░░░░░░░░░</t>
+          <t>██████████░░░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
       <c r="I4" s="22" t="inlineStr">
@@ -5259,23 +5283,23 @@
         <v>84</v>
       </c>
       <c r="C6" s="28" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D6" s="28" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E6" s="28" t="n">
         <v>31</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G6" s="29" t="n">
-        <v>0.4047619047619048</v>
+        <v>0.4404761904761905</v>
       </c>
       <c r="H6" s="30" t="inlineStr">
         <is>
-          <t>████████████░░░░░░░░░░░░░░░░░░</t>
+          <t>█████████████░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
       <c r="I6" s="28" t="inlineStr"/>

--- a/Base_Maestra_Consolidada_Dialogos_Chatbot.xlsx
+++ b/Base_Maestra_Consolidada_Dialogos_Chatbot.xlsx
@@ -3739,18 +3739,26 @@
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="F61" s="6" t="inlineStr"/>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr"/>
       <c r="I61" s="6" t="inlineStr"/>
-      <c r="J61" s="8" t="inlineStr"/>
-      <c r="K61" s="8" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+      <c r="J61" s="8" t="inlineStr">
+        <is>
+          <t>Confirmó sin cambios para julio</t>
+        </is>
+      </c>
+      <c r="K61" s="38" t="inlineStr">
+        <is>
+          <t>Sin modificaciones</t>
         </is>
       </c>
       <c r="L61" s="8" t="inlineStr"/>
@@ -4077,18 +4085,26 @@
           <t>02/07/2026</t>
         </is>
       </c>
-      <c r="F68" s="6" t="inlineStr"/>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>15/07/2026</t>
+        </is>
+      </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr"/>
       <c r="I68" s="6" t="inlineStr"/>
-      <c r="J68" s="5" t="inlineStr"/>
-      <c r="K68" s="5" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>Confirmó sin cambios para julio</t>
+        </is>
+      </c>
+      <c r="K68" s="38" t="inlineStr">
+        <is>
+          <t>Sin modificaciones</t>
         </is>
       </c>
       <c r="L68" s="5" t="inlineStr"/>
@@ -5074,23 +5090,23 @@
         <v>42</v>
       </c>
       <c r="C5" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D5" s="12" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>8</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G5" s="12" t="n">
         <v>8</v>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="I5" s="17">
@@ -5213,23 +5229,23 @@
         <v>42</v>
       </c>
       <c r="C4" s="19" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" s="19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E4" s="19" t="n">
         <v>8</v>
       </c>
       <c r="F4" s="19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G4" s="20" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t>██████████░░░░░░░░░░░░░░░░░░░░</t>
+          <t>███████████░░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
       <c r="I4" s="22" t="inlineStr">
@@ -5283,23 +5299,23 @@
         <v>84</v>
       </c>
       <c r="C6" s="28" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D6" s="28" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E6" s="28" t="n">
         <v>31</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G6" s="29" t="n">
-        <v>0.4404761904761905</v>
+        <v>0.4642857142857143</v>
       </c>
       <c r="H6" s="30" t="inlineStr">
         <is>
-          <t>█████████████░░░░░░░░░░░░░░░░░</t>
+          <t>██████████████░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
       <c r="I6" s="28" t="inlineStr"/>

--- a/Base_Maestra_Consolidada_Dialogos_Chatbot.xlsx
+++ b/Base_Maestra_Consolidada_Dialogos_Chatbot.xlsx
@@ -1040,12 +1040,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Andrea Rojas</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>catalina.rojas@ghlhoteles.com</t>
+          <t>calidad.bioxury@ghlhoteles.com</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -1063,7 +1063,7 @@
       <c r="I6" s="6" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>⚠ El correo catalina.rojas@ghlhoteles.com ahora corresponde a Sonesta Bogotá (Catalina Rojas) — verificar/definir contacto propio de Bioxury</t>
+          <t>Correo actualizado a calidad.bioxury@ghlhoteles.com; sin nombre de contacto</t>
         </is>
       </c>
       <c r="K6" s="22" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Andrea Rojas</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>catalina.rojas@ghlhoteles.com</t>
+          <t>calidad.bioxury@ghlhoteles.com</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -3147,7 +3147,7 @@
       <c r="I48" s="6" t="inlineStr"/>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>⚠ El correo catalina.rojas@ghlhoteles.com ahora corresponde a Sonesta Bogotá (Catalina Rojas) — verificar/definir contacto propio de Bioxury</t>
+          <t>Correo actualizado a calidad.bioxury@ghlhoteles.com; sin nombre de contacto</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">

--- a/Base_Maestra_Consolidada_Dialogos_Chatbot.xlsx
+++ b/Base_Maestra_Consolidada_Dialogos_Chatbot.xlsx
@@ -3054,7 +3054,7 @@
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J59" s="8" t="n"/>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J65" s="8" t="n"/>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J66" s="5" t="n"/>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J67" s="8" t="n"/>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J77" s="8" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J79" s="8" t="n"/>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J80" s="5" t="n"/>
@@ -17767,6 +17767,8 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>

--- a/Base_Maestra_Consolidada_Dialogos_Chatbot.xlsx
+++ b/Base_Maestra_Consolidada_Dialogos_Chatbot.xlsx
@@ -3935,7 +3935,7 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>5 diálogos modificados: ubicación, check-in/out tardío, horario y tarifa de desayuno</t>
+          <t>3 diálogos modificados: ubicación, check-in/out tardío</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
@@ -3943,7 +3943,11 @@
           <t>30/07/2026</t>
         </is>
       </c>
-      <c r="J65" s="8" t="n"/>
+      <c r="J65" s="8" t="inlineStr">
+        <is>
+          <t>Se retiran horario y tarifa de desayuno del listado: coinciden con el PDF de julio vigente, no eran cambios reales</t>
+        </is>
+      </c>
       <c r="K65" s="42" t="inlineStr">
         <is>
           <t>Actualizado</t>
@@ -4632,23 +4636,19 @@
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="H80" s="5" t="inlineStr">
-        <is>
-          <t>8 diálogos modificados: check-in/out, desayuno horario/precio, niños, mascotas, redes, restaurante</t>
-        </is>
-      </c>
-      <c r="I80" s="6" t="inlineStr">
-        <is>
-          <t>30/07/2026</t>
-        </is>
-      </c>
-      <c r="J80" s="5" t="n"/>
-      <c r="K80" s="42" t="inlineStr">
-        <is>
-          <t>Actualizado</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="n"/>
+      <c r="I80" s="6" t="n"/>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>Los 8 puntos que reportó ya coinciden con el PDF de julio vigente — no eran cambios reales, solo confirmó valores ya correctos</t>
+        </is>
+      </c>
+      <c r="K80" s="38" t="inlineStr">
+        <is>
+          <t>Sin modificaciones</t>
         </is>
       </c>
       <c r="L80" s="5" t="inlineStr"/>
@@ -5096,13 +5096,13 @@
         <v>26</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
@@ -5235,10 +5235,10 @@
         <v>26</v>
       </c>
       <c r="E4" s="19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" s="19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4" s="20" t="n">
         <v>0.3809523809523809</v>
@@ -5305,10 +5305,10 @@
         <v>45</v>
       </c>
       <c r="E6" s="28" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6" s="29" t="n">
         <v>0.4642857142857143</v>
@@ -5344,7 +5344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H319"/>
+  <dimension ref="A1:H309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="C284" s="41" t="inlineStr">
         <is>
-          <t>9-01</t>
+          <t>19-01</t>
         </is>
       </c>
       <c r="D284" s="41" t="inlineStr">
@@ -16097,7 +16097,7 @@
       </c>
       <c r="F284" s="41" t="inlineStr">
         <is>
-          <t>⚠ No especificada en el diálogo previo</t>
+          <t>Cra. 8a #38-42, Comuna 2, Neiva, Huila, Colombia</t>
         </is>
       </c>
       <c r="G284" s="41" t="inlineStr">
@@ -16191,32 +16191,32 @@
       </c>
       <c r="B287" s="41" t="inlineStr">
         <is>
-          <t>GHL Style Neiva</t>
+          <t>GHL Style Yopal</t>
         </is>
       </c>
       <c r="C287" s="41" t="inlineStr">
         <is>
-          <t>12-01</t>
+          <t>11-01</t>
         </is>
       </c>
       <c r="D287" s="41" t="inlineStr">
         <is>
-          <t>Breakfast time</t>
+          <t>Check in time</t>
         </is>
       </c>
       <c r="E287" s="41" t="inlineStr">
         <is>
-          <t>Horario desayuno</t>
+          <t>Costo early check-in</t>
         </is>
       </c>
       <c r="F287" s="41" t="inlineStr">
         <is>
-          <t>⚠ No especificado</t>
+          <t>70.000 COP por habitación</t>
         </is>
       </c>
       <c r="G287" s="41" t="inlineStr">
         <is>
-          <t>Buffet diario de 6:30 a.m. a 10:00 a.m.</t>
+          <t>COP 70.000 + impuestos por habitación</t>
         </is>
       </c>
       <c r="H287" s="41" t="n"/>
@@ -16229,32 +16229,32 @@
       </c>
       <c r="B288" s="41" t="inlineStr">
         <is>
-          <t>GHL Style Neiva</t>
+          <t>GHL Style Yopal</t>
         </is>
       </c>
       <c r="C288" s="41" t="inlineStr">
         <is>
-          <t>12-02</t>
+          <t>11-11</t>
         </is>
       </c>
       <c r="D288" s="41" t="inlineStr">
         <is>
-          <t>Breakfast rates</t>
+          <t>Check out time</t>
         </is>
       </c>
       <c r="E288" s="41" t="inlineStr">
         <is>
-          <t>Precio adulto</t>
+          <t>Costo late check-out</t>
         </is>
       </c>
       <c r="F288" s="41" t="inlineStr">
         <is>
-          <t>⚠ No especificado</t>
+          <t>70.000 COP por habitación</t>
         </is>
       </c>
       <c r="G288" s="41" t="inlineStr">
         <is>
-          <t>40.000 COP por adulto; incluido en tarifa de habitación; visitantes también bienvenidos</t>
+          <t>COP 70.000 + impuestos por habitación</t>
         </is>
       </c>
       <c r="H288" s="41" t="n"/>
@@ -16267,32 +16267,32 @@
       </c>
       <c r="B289" s="41" t="inlineStr">
         <is>
-          <t>GHL Style Yopal</t>
+          <t>Hotel Tequendama Bogotá</t>
         </is>
       </c>
       <c r="C289" s="41" t="inlineStr">
         <is>
-          <t>11-01</t>
+          <t>13-45</t>
         </is>
       </c>
       <c r="D289" s="41" t="inlineStr">
         <is>
-          <t>Check in time</t>
+          <t>Change &amp; ATM</t>
         </is>
       </c>
       <c r="E289" s="41" t="inlineStr">
         <is>
-          <t>Costo early check-in</t>
+          <t>Disponibilidad de cajero automático</t>
         </is>
       </c>
       <c r="F289" s="41" t="inlineStr">
         <is>
-          <t>70.000 COP por habitación</t>
+          <t>Sí tenemos un cajero automático en la propiedad</t>
         </is>
       </c>
       <c r="G289" s="41" t="inlineStr">
         <is>
-          <t>COP 70.000 + impuestos por habitación</t>
+          <t>No tenemos un cajero automático en la propiedad</t>
         </is>
       </c>
       <c r="H289" s="41" t="n"/>
@@ -16305,32 +16305,32 @@
       </c>
       <c r="B290" s="41" t="inlineStr">
         <is>
-          <t>GHL Style Yopal</t>
+          <t>Hotel Tequendama Bogotá</t>
         </is>
       </c>
       <c r="C290" s="41" t="inlineStr">
         <is>
-          <t>11-11</t>
+          <t>13-06</t>
         </is>
       </c>
       <c r="D290" s="41" t="inlineStr">
         <is>
-          <t>Check out time</t>
+          <t>Room Service</t>
         </is>
       </c>
       <c r="E290" s="41" t="inlineStr">
         <is>
-          <t>Costo late check-out</t>
+          <t>Horario y marcación</t>
         </is>
       </c>
       <c r="F290" s="41" t="inlineStr">
         <is>
-          <t>70.000 COP por habitación</t>
+          <t>Disponible de 06:00 a 22:00; marcar 2356</t>
         </is>
       </c>
       <c r="G290" s="41" t="inlineStr">
         <is>
-          <t>COP 70.000 + impuestos por habitación</t>
+          <t>Disponible de 06:00 a 00:00; marcar *2</t>
         </is>
       </c>
       <c r="H290" s="41" t="n"/>
@@ -16343,32 +16343,32 @@
       </c>
       <c r="B291" s="41" t="inlineStr">
         <is>
-          <t>Hotel Tequendama Bogotá</t>
+          <t>Sonesta Cusco</t>
         </is>
       </c>
       <c r="C291" s="41" t="inlineStr">
         <is>
-          <t>13-45</t>
+          <t>16-02</t>
         </is>
       </c>
       <c r="D291" s="41" t="inlineStr">
         <is>
-          <t>Change &amp; ATM</t>
+          <t>Contact staff — Recepción</t>
         </is>
       </c>
       <c r="E291" s="41" t="inlineStr">
         <is>
-          <t>Disponibilidad de cajero automático</t>
+          <t>Correo</t>
         </is>
       </c>
       <c r="F291" s="41" t="inlineStr">
         <is>
-          <t>Sí tenemos un cajero automático en la propiedad</t>
+          <t>recepcion.sonestahotelcusco@ghlhoteles.com</t>
         </is>
       </c>
       <c r="G291" s="41" t="inlineStr">
         <is>
-          <t>No tenemos un cajero automático en la propiedad</t>
+          <t>recepcion.sonestacusco@ghlhoteles.com</t>
         </is>
       </c>
       <c r="H291" s="41" t="n"/>
@@ -16381,32 +16381,32 @@
       </c>
       <c r="B292" s="41" t="inlineStr">
         <is>
-          <t>Hotel Tequendama Bogotá</t>
+          <t>Sonesta Cusco</t>
         </is>
       </c>
       <c r="C292" s="41" t="inlineStr">
         <is>
-          <t>13-06</t>
+          <t>11-01</t>
         </is>
       </c>
       <c r="D292" s="41" t="inlineStr">
         <is>
-          <t>Room Service</t>
+          <t>Check-in time</t>
         </is>
       </c>
       <c r="E292" s="41" t="inlineStr">
         <is>
-          <t>Horario y marcación</t>
+          <t>Costo early check-in</t>
         </is>
       </c>
       <c r="F292" s="41" t="inlineStr">
         <is>
-          <t>Disponible de 06:00 a 22:00; marcar 2356</t>
+          <t>40.00 USD por habitación</t>
         </is>
       </c>
       <c r="G292" s="41" t="inlineStr">
         <is>
-          <t>Disponible de 06:00 a 00:00; marcar *2</t>
+          <t>60.00 USD por habitación (impuestos no incluidos)</t>
         </is>
       </c>
       <c r="H292" s="41" t="n"/>
@@ -16424,27 +16424,27 @@
       </c>
       <c r="C293" s="41" t="inlineStr">
         <is>
-          <t>16-02</t>
+          <t>11-11</t>
         </is>
       </c>
       <c r="D293" s="41" t="inlineStr">
         <is>
-          <t>Contact staff — Recepción</t>
+          <t>Check-out time</t>
         </is>
       </c>
       <c r="E293" s="41" t="inlineStr">
         <is>
-          <t>Correo</t>
+          <t>Costo late check-out</t>
         </is>
       </c>
       <c r="F293" s="41" t="inlineStr">
         <is>
-          <t>recepcion.sonestahotelcusco@ghlhoteles.com</t>
+          <t>40.00 USD por habitación</t>
         </is>
       </c>
       <c r="G293" s="41" t="inlineStr">
         <is>
-          <t>recepcion.sonestacusco@ghlhoteles.com</t>
+          <t>60.00 USD por habitación</t>
         </is>
       </c>
       <c r="H293" s="41" t="n"/>
@@ -16462,27 +16462,27 @@
       </c>
       <c r="C294" s="41" t="inlineStr">
         <is>
-          <t>11-01</t>
+          <t>13-06</t>
         </is>
       </c>
       <c r="D294" s="41" t="inlineStr">
         <is>
-          <t>Check-in time</t>
+          <t>Room service</t>
         </is>
       </c>
       <c r="E294" s="41" t="inlineStr">
         <is>
-          <t>Costo early check-in</t>
+          <t>Horario</t>
         </is>
       </c>
       <c r="F294" s="41" t="inlineStr">
         <is>
-          <t>40.00 USD por habitación</t>
+          <t>Disponible de 06:00 a 21:00</t>
         </is>
       </c>
       <c r="G294" s="41" t="inlineStr">
         <is>
-          <t>60.00 USD por habitación (impuestos no incluidos)</t>
+          <t>Disponible 24/7</t>
         </is>
       </c>
       <c r="H294" s="41" t="n"/>
@@ -16495,32 +16495,32 @@
       </c>
       <c r="B295" s="41" t="inlineStr">
         <is>
-          <t>Sonesta Cusco</t>
+          <t>Sonesta Arequipa</t>
         </is>
       </c>
       <c r="C295" s="41" t="inlineStr">
         <is>
-          <t>11-11</t>
+          <t>16-06</t>
         </is>
       </c>
       <c r="D295" s="41" t="inlineStr">
         <is>
-          <t>Check-out time</t>
+          <t>Jobs &amp; internships</t>
         </is>
       </c>
       <c r="E295" s="41" t="inlineStr">
         <is>
-          <t>Costo late check-out</t>
+          <t>Correo de contacto RR.HH.</t>
         </is>
       </c>
       <c r="F295" s="41" t="inlineStr">
         <is>
-          <t>40.00 USD por habitación</t>
+          <t>contactenos@ghlhoteles.com</t>
         </is>
       </c>
       <c r="G295" s="41" t="inlineStr">
         <is>
-          <t>60.00 USD por habitación</t>
+          <t>laydy.pauca@ghlhoteles.com</t>
         </is>
       </c>
       <c r="H295" s="41" t="n"/>
@@ -16533,32 +16533,32 @@
       </c>
       <c r="B296" s="41" t="inlineStr">
         <is>
-          <t>Sonesta Cusco</t>
+          <t>Sonesta Arequipa</t>
         </is>
       </c>
       <c r="C296" s="41" t="inlineStr">
         <is>
-          <t>13-06</t>
+          <t>16-25</t>
         </is>
       </c>
       <c r="D296" s="41" t="inlineStr">
         <is>
-          <t>Room service</t>
+          <t>Tips policy</t>
         </is>
       </c>
       <c r="E296" s="41" t="inlineStr">
         <is>
-          <t>Horario</t>
+          <t>Política de propinas</t>
         </is>
       </c>
       <c r="F296" s="41" t="inlineStr">
         <is>
-          <t>Disponible de 06:00 a 21:00</t>
+          <t>Tarifa estándar incluye 19% de impuesto de servicio; propina habitual y opcional</t>
         </is>
       </c>
       <c r="G296" s="41" t="inlineStr">
         <is>
-          <t>Disponible 24/7</t>
+          <t>Tarifa estándar incluye el cargo por servicio; propina opcional</t>
         </is>
       </c>
       <c r="H296" s="41" t="n"/>
@@ -16576,27 +16576,27 @@
       </c>
       <c r="C297" s="41" t="inlineStr">
         <is>
-          <t>16-06</t>
+          <t>17-01</t>
         </is>
       </c>
       <c r="D297" s="41" t="inlineStr">
         <is>
-          <t>Jobs &amp; internships</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="E297" s="41" t="inlineStr">
         <is>
-          <t>Correo de contacto RR.HH.</t>
+          <t>Detalles bar Arcadia</t>
         </is>
       </c>
       <c r="F297" s="41" t="inlineStr">
         <is>
-          <t>contactenos@ghlhoteles.com</t>
+          <t>Capacidad máx. 25 pax; se sirve comida; sin happy hour listado por separado</t>
         </is>
       </c>
       <c r="G297" s="41" t="inlineStr">
         <is>
-          <t>laydy.pauca@ghlhoteles.com</t>
+          <t>Se retira capacidad máxima y mención de comida servida; resto de condiciones igual</t>
         </is>
       </c>
       <c r="H297" s="41" t="n"/>
@@ -16614,27 +16614,27 @@
       </c>
       <c r="C298" s="41" t="inlineStr">
         <is>
-          <t>16-25</t>
+          <t>17-02</t>
         </is>
       </c>
       <c r="D298" s="41" t="inlineStr">
         <is>
-          <t>Tips policy</t>
+          <t>Bar reservation</t>
         </is>
       </c>
       <c r="E298" s="41" t="inlineStr">
         <is>
-          <t>Política de propinas</t>
+          <t>Reservas de bar</t>
         </is>
       </c>
       <c r="F298" s="41" t="inlineStr">
         <is>
-          <t>Tarifa estándar incluye 19% de impuesto de servicio; propina habitual y opcional</t>
+          <t>No se toman reservas</t>
         </is>
       </c>
       <c r="G298" s="41" t="inlineStr">
         <is>
-          <t>Tarifa estándar incluye el cargo por servicio; propina opcional</t>
+          <t>Para reservar, contactar al +51 945739921</t>
         </is>
       </c>
       <c r="H298" s="41" t="n"/>
@@ -16652,27 +16652,27 @@
       </c>
       <c r="C299" s="41" t="inlineStr">
         <is>
-          <t>17-01</t>
+          <t>17-10</t>
         </is>
       </c>
       <c r="D299" s="41" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Spa</t>
         </is>
       </c>
       <c r="E299" s="41" t="inlineStr">
         <is>
-          <t>Detalles bar Arcadia</t>
+          <t>Tarifas y kit obligatorio</t>
         </is>
       </c>
       <c r="F299" s="41" t="inlineStr">
         <is>
-          <t>Capacidad máx. 25 pax; se sirve comida; sin happy hour listado por separado</t>
+          <t>Precio de huésped variable; obligatorio: pantuflas y vestido de baño; no obligatorio: bata y gorro</t>
         </is>
       </c>
       <c r="G299" s="41" t="inlineStr">
         <is>
-          <t>Se retira capacidad máxima y mención de comida servida; resto de condiciones igual</t>
+          <t>Masajes con cargo adicional; obligatorio: pantuflas, gorro y vestido de baño; no obligatorio: bata</t>
         </is>
       </c>
       <c r="H299" s="41" t="n"/>
@@ -16690,27 +16690,27 @@
       </c>
       <c r="C300" s="41" t="inlineStr">
         <is>
-          <t>17-02</t>
+          <t>17-15</t>
         </is>
       </c>
       <c r="D300" s="41" t="inlineStr">
         <is>
-          <t>Bar reservation</t>
+          <t>Spa hours</t>
         </is>
       </c>
       <c r="E300" s="41" t="inlineStr">
         <is>
-          <t>Reservas de bar</t>
+          <t>Límite de tiempo</t>
         </is>
       </c>
       <c r="F300" s="41" t="inlineStr">
         <is>
-          <t>No se toman reservas</t>
+          <t>Sin límite de tiempo</t>
         </is>
       </c>
       <c r="G300" s="41" t="inlineStr">
         <is>
-          <t>Para reservar, contactar al +51 945739921</t>
+          <t>Estancia máxima de 1 hora</t>
         </is>
       </c>
       <c r="H300" s="41" t="n"/>
@@ -16728,27 +16728,27 @@
       </c>
       <c r="C301" s="41" t="inlineStr">
         <is>
-          <t>17-10</t>
+          <t>18-01</t>
         </is>
       </c>
       <c r="D301" s="41" t="inlineStr">
         <is>
-          <t>Spa</t>
+          <t>Restaurant</t>
         </is>
       </c>
       <c r="E301" s="41" t="inlineStr">
         <is>
-          <t>Tarifas y kit obligatorio</t>
+          <t>Descripción restaurante Micaela</t>
         </is>
       </c>
       <c r="F301" s="41" t="inlineStr">
         <is>
-          <t>Precio de huésped variable; obligatorio: pantuflas y vestido de baño; no obligatorio: bata y gorro</t>
+          <t>Descripción extensa (tipo de cocina, capacidad, niños, reservas, cajas altas, etc.)</t>
         </is>
       </c>
       <c r="G301" s="41" t="inlineStr">
         <is>
-          <t>Masajes con cargo adicional; obligatorio: pantuflas, gorro y vestido de baño; no obligatorio: bata</t>
+          <t>Descripción simplificada: horario, accesibilidad, mascotas no aceptadas</t>
         </is>
       </c>
       <c r="H301" s="41" t="n"/>
@@ -16766,27 +16766,27 @@
       </c>
       <c r="C302" s="41" t="inlineStr">
         <is>
-          <t>17-15</t>
+          <t>18-02</t>
         </is>
       </c>
       <c r="D302" s="41" t="inlineStr">
         <is>
-          <t>Spa hours</t>
+          <t>Restaurant reservation</t>
         </is>
       </c>
       <c r="E302" s="41" t="inlineStr">
         <is>
-          <t>Límite de tiempo</t>
+          <t>Método de reserva</t>
         </is>
       </c>
       <c r="F302" s="41" t="inlineStr">
         <is>
-          <t>Sin límite de tiempo</t>
+          <t>Reservar por correo a reservas.sonestaarequipa@ghlhoteles.com</t>
         </is>
       </c>
       <c r="G302" s="41" t="inlineStr">
         <is>
-          <t>Estancia máxima de 1 hora</t>
+          <t>Contactar al +51 945739921</t>
         </is>
       </c>
       <c r="H302" s="41" t="n"/>
@@ -16804,27 +16804,27 @@
       </c>
       <c r="C303" s="41" t="inlineStr">
         <is>
-          <t>18-01</t>
+          <t>18-03</t>
         </is>
       </c>
       <c r="D303" s="41" t="inlineStr">
         <is>
-          <t>Restaurant</t>
+          <t>Restaurant reservation cancellation</t>
         </is>
       </c>
       <c r="E303" s="41" t="inlineStr">
         <is>
-          <t>Descripción restaurante Micaela</t>
+          <t>Método de cancelación</t>
         </is>
       </c>
       <c r="F303" s="41" t="inlineStr">
         <is>
-          <t>Descripción extensa (tipo de cocina, capacidad, niños, reservas, cajas altas, etc.)</t>
+          <t>Cancelar por correo</t>
         </is>
       </c>
       <c r="G303" s="41" t="inlineStr">
         <is>
-          <t>Descripción simplificada: horario, accesibilidad, mascotas no aceptadas</t>
+          <t>Contactar al +51 945739921</t>
         </is>
       </c>
       <c r="H303" s="41" t="n"/>
@@ -16842,22 +16842,22 @@
       </c>
       <c r="C304" s="41" t="inlineStr">
         <is>
-          <t>18-02</t>
+          <t>18-04</t>
         </is>
       </c>
       <c r="D304" s="41" t="inlineStr">
         <is>
-          <t>Restaurant reservation</t>
+          <t>Restaurant reservation modification</t>
         </is>
       </c>
       <c r="E304" s="41" t="inlineStr">
         <is>
-          <t>Método de reserva</t>
+          <t>Método de modificación</t>
         </is>
       </c>
       <c r="F304" s="41" t="inlineStr">
         <is>
-          <t>Reservar por correo a reservas.sonestaarequipa@ghlhoteles.com</t>
+          <t>Modificar por correo</t>
         </is>
       </c>
       <c r="G304" s="41" t="inlineStr">
@@ -16880,22 +16880,22 @@
       </c>
       <c r="C305" s="41" t="inlineStr">
         <is>
-          <t>18-03</t>
+          <t>18-05</t>
         </is>
       </c>
       <c r="D305" s="41" t="inlineStr">
         <is>
-          <t>Restaurant reservation cancellation</t>
+          <t>Restaurant reservation confirmation</t>
         </is>
       </c>
       <c r="E305" s="41" t="inlineStr">
         <is>
-          <t>Método de cancelación</t>
+          <t>Método de confirmación</t>
         </is>
       </c>
       <c r="F305" s="41" t="inlineStr">
         <is>
-          <t>Cancelar por correo</t>
+          <t>Confirmar por correo</t>
         </is>
       </c>
       <c r="G305" s="41" t="inlineStr">
@@ -16918,27 +16918,27 @@
       </c>
       <c r="C306" s="41" t="inlineStr">
         <is>
-          <t>18-04</t>
+          <t>18-11</t>
         </is>
       </c>
       <c r="D306" s="41" t="inlineStr">
         <is>
-          <t>Restaurant reservation modification</t>
+          <t>Brunch</t>
         </is>
       </c>
       <c r="E306" s="41" t="inlineStr">
         <is>
-          <t>Método de modificación</t>
+          <t>Recomendación externa</t>
         </is>
       </c>
       <c r="F306" s="41" t="inlineStr">
         <is>
-          <t>Modificar por correo</t>
+          <t>No ofrecen brunch; recomiendan Restaurante Santé como alternativa externa</t>
         </is>
       </c>
       <c r="G306" s="41" t="inlineStr">
         <is>
-          <t>Contactar al +51 945739921</t>
+          <t>No ofrecemos brunch (se retira la recomendación externa)</t>
         </is>
       </c>
       <c r="H306" s="41" t="n"/>
@@ -16956,27 +16956,27 @@
       </c>
       <c r="C307" s="41" t="inlineStr">
         <is>
-          <t>18-05</t>
+          <t>18-26</t>
         </is>
       </c>
       <c r="D307" s="41" t="inlineStr">
         <is>
-          <t>Restaurant reservation confirmation</t>
+          <t>Valentine's day</t>
         </is>
       </c>
       <c r="E307" s="41" t="inlineStr">
         <is>
-          <t>Método de confirmación</t>
+          <t>Forma de consulta</t>
         </is>
       </c>
       <c r="F307" s="41" t="inlineStr">
         <is>
-          <t>Confirmar por correo</t>
+          <t>Ver oferta mediante enlace</t>
         </is>
       </c>
       <c r="G307" s="41" t="inlineStr">
         <is>
-          <t>Contactar al +51 945739921</t>
+          <t>Escribir a reservas.sonestaarequipa@ghlhoteles.com o contactar al +51 939753285</t>
         </is>
       </c>
       <c r="H307" s="41" t="n"/>
@@ -16994,27 +16994,27 @@
       </c>
       <c r="C308" s="41" t="inlineStr">
         <is>
-          <t>18-11</t>
+          <t>19-03</t>
         </is>
       </c>
       <c r="D308" s="41" t="inlineStr">
         <is>
-          <t>Brunch</t>
+          <t>City center</t>
         </is>
       </c>
       <c r="E308" s="41" t="inlineStr">
         <is>
-          <t>Recomendación externa</t>
+          <t>Distancia al centro</t>
         </is>
       </c>
       <c r="F308" s="41" t="inlineStr">
         <is>
-          <t>No ofrecen brunch; recomiendan Restaurante Santé como alternativa externa</t>
+          <t>26 m, 1 min caminando</t>
         </is>
       </c>
       <c r="G308" s="41" t="inlineStr">
         <is>
-          <t>No ofrecemos brunch (se retira la recomendación externa)</t>
+          <t>4 km</t>
         </is>
       </c>
       <c r="H308" s="41" t="n"/>
@@ -17032,410 +17032,30 @@
       </c>
       <c r="C309" s="41" t="inlineStr">
         <is>
-          <t>18-26</t>
+          <t>20-21</t>
         </is>
       </c>
       <c r="D309" s="41" t="inlineStr">
         <is>
-          <t>Valentine's day</t>
+          <t>Celebration</t>
         </is>
       </c>
       <c r="E309" s="41" t="inlineStr">
         <is>
-          <t>Forma de consulta</t>
+          <t>Teléfono de eventos</t>
         </is>
       </c>
       <c r="F309" s="41" t="inlineStr">
         <is>
-          <t>Ver oferta mediante enlace</t>
+          <t>+51 945 739 48</t>
         </is>
       </c>
       <c r="G309" s="41" t="inlineStr">
         <is>
-          <t>Escribir a reservas.sonestaarequipa@ghlhoteles.com o contactar al +51 939753285</t>
+          <t>+51 945 739 484 (corrección de dígito faltante)</t>
         </is>
       </c>
       <c r="H309" s="41" t="n"/>
-    </row>
-    <row r="310">
-      <c r="A310" s="40" t="inlineStr">
-        <is>
-          <t>Jul-26</t>
-        </is>
-      </c>
-      <c r="B310" s="41" t="inlineStr">
-        <is>
-          <t>Sonesta Arequipa</t>
-        </is>
-      </c>
-      <c r="C310" s="41" t="inlineStr">
-        <is>
-          <t>19-03</t>
-        </is>
-      </c>
-      <c r="D310" s="41" t="inlineStr">
-        <is>
-          <t>City center</t>
-        </is>
-      </c>
-      <c r="E310" s="41" t="inlineStr">
-        <is>
-          <t>Distancia al centro</t>
-        </is>
-      </c>
-      <c r="F310" s="41" t="inlineStr">
-        <is>
-          <t>26 m, 1 min caminando</t>
-        </is>
-      </c>
-      <c r="G310" s="41" t="inlineStr">
-        <is>
-          <t>4 km</t>
-        </is>
-      </c>
-      <c r="H310" s="41" t="n"/>
-    </row>
-    <row r="311">
-      <c r="A311" s="40" t="inlineStr">
-        <is>
-          <t>Jul-26</t>
-        </is>
-      </c>
-      <c r="B311" s="41" t="inlineStr">
-        <is>
-          <t>Sonesta Arequipa</t>
-        </is>
-      </c>
-      <c r="C311" s="41" t="inlineStr">
-        <is>
-          <t>20-21</t>
-        </is>
-      </c>
-      <c r="D311" s="41" t="inlineStr">
-        <is>
-          <t>Celebration</t>
-        </is>
-      </c>
-      <c r="E311" s="41" t="inlineStr">
-        <is>
-          <t>Teléfono de eventos</t>
-        </is>
-      </c>
-      <c r="F311" s="41" t="inlineStr">
-        <is>
-          <t>+51 945 739 48</t>
-        </is>
-      </c>
-      <c r="G311" s="41" t="inlineStr">
-        <is>
-          <t>+51 945 739 484 (corrección de dígito faltante)</t>
-        </is>
-      </c>
-      <c r="H311" s="41" t="n"/>
-    </row>
-    <row r="312">
-      <c r="A312" s="40" t="inlineStr">
-        <is>
-          <t>Jul-26</t>
-        </is>
-      </c>
-      <c r="B312" s="41" t="inlineStr">
-        <is>
-          <t>Sonesta Bogotá</t>
-        </is>
-      </c>
-      <c r="C312" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D312" s="41" t="inlineStr">
-        <is>
-          <t>Check in time</t>
-        </is>
-      </c>
-      <c r="E312" s="41" t="inlineStr">
-        <is>
-          <t>Costo early check-in</t>
-        </is>
-      </c>
-      <c r="F312" s="41" t="inlineStr">
-        <is>
-          <t>Versión anterior</t>
-        </is>
-      </c>
-      <c r="G312" s="41" t="inlineStr">
-        <is>
-          <t>$35.000, sujeto a disponibilidad</t>
-        </is>
-      </c>
-      <c r="H312" s="41" t="n"/>
-    </row>
-    <row r="313">
-      <c r="A313" s="40" t="inlineStr">
-        <is>
-          <t>Jul-26</t>
-        </is>
-      </c>
-      <c r="B313" s="41" t="inlineStr">
-        <is>
-          <t>Sonesta Bogotá</t>
-        </is>
-      </c>
-      <c r="C313" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D313" s="41" t="inlineStr">
-        <is>
-          <t>Check out time</t>
-        </is>
-      </c>
-      <c r="E313" s="41" t="inlineStr">
-        <is>
-          <t>Late check-out</t>
-        </is>
-      </c>
-      <c r="F313" s="41" t="inlineStr">
-        <is>
-          <t>Versión anterior</t>
-        </is>
-      </c>
-      <c r="G313" s="41" t="inlineStr">
-        <is>
-          <t>$35.000 por hora; después de las 6:00 p.m. se cobra la tarifa completa</t>
-        </is>
-      </c>
-      <c r="H313" s="41" t="n"/>
-    </row>
-    <row r="314">
-      <c r="A314" s="40" t="inlineStr">
-        <is>
-          <t>Jul-26</t>
-        </is>
-      </c>
-      <c r="B314" s="41" t="inlineStr">
-        <is>
-          <t>Sonesta Bogotá</t>
-        </is>
-      </c>
-      <c r="C314" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D314" s="41" t="inlineStr">
-        <is>
-          <t>Breakfast time</t>
-        </is>
-      </c>
-      <c r="E314" s="41" t="inlineStr">
-        <is>
-          <t>Horario sábados, domingos y festivos</t>
-        </is>
-      </c>
-      <c r="F314" s="41" t="inlineStr">
-        <is>
-          <t>Versión anterior</t>
-        </is>
-      </c>
-      <c r="G314" s="41" t="inlineStr">
-        <is>
-          <t>6:30 a.m. a 10:30 a.m.</t>
-        </is>
-      </c>
-      <c r="H314" s="41" t="n"/>
-    </row>
-    <row r="315">
-      <c r="A315" s="40" t="inlineStr">
-        <is>
-          <t>Jul-26</t>
-        </is>
-      </c>
-      <c r="B315" s="41" t="inlineStr">
-        <is>
-          <t>Sonesta Bogotá</t>
-        </is>
-      </c>
-      <c r="C315" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D315" s="41" t="inlineStr">
-        <is>
-          <t>Breakfast rates</t>
-        </is>
-      </c>
-      <c r="E315" s="41" t="inlineStr">
-        <is>
-          <t>Precio por persona</t>
-        </is>
-      </c>
-      <c r="F315" s="41" t="inlineStr">
-        <is>
-          <t>Versión anterior</t>
-        </is>
-      </c>
-      <c r="G315" s="41" t="inlineStr">
-        <is>
-          <t>$65.000 COP</t>
-        </is>
-      </c>
-      <c r="H315" s="41" t="n"/>
-    </row>
-    <row r="316">
-      <c r="A316" s="40" t="inlineStr">
-        <is>
-          <t>Jul-26</t>
-        </is>
-      </c>
-      <c r="B316" s="41" t="inlineStr">
-        <is>
-          <t>Sonesta Bogotá</t>
-        </is>
-      </c>
-      <c r="C316" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D316" s="41" t="inlineStr">
-        <is>
-          <t>Kids</t>
-        </is>
-      </c>
-      <c r="E316" s="41" t="inlineStr">
-        <is>
-          <t>Tarifa niños</t>
-        </is>
-      </c>
-      <c r="F316" s="41" t="inlineStr">
-        <is>
-          <t>Versión anterior</t>
-        </is>
-      </c>
-      <c r="G316" s="41" t="inlineStr">
-        <is>
-          <t>Menores de 12 años gratis con sus padres; mayores de 12 años $80.000 por noche</t>
-        </is>
-      </c>
-      <c r="H316" s="41" t="n"/>
-    </row>
-    <row r="317">
-      <c r="A317" s="40" t="inlineStr">
-        <is>
-          <t>Jul-26</t>
-        </is>
-      </c>
-      <c r="B317" s="41" t="inlineStr">
-        <is>
-          <t>Sonesta Bogotá</t>
-        </is>
-      </c>
-      <c r="C317" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D317" s="41" t="inlineStr">
-        <is>
-          <t>Pets</t>
-        </is>
-      </c>
-      <c r="E317" s="41" t="inlineStr">
-        <is>
-          <t>Peso permitido</t>
-        </is>
-      </c>
-      <c r="F317" s="41" t="inlineStr">
-        <is>
-          <t>Versión anterior</t>
-        </is>
-      </c>
-      <c r="G317" s="41" t="inlineStr">
-        <is>
-          <t>10 kg</t>
-        </is>
-      </c>
-      <c r="H317" s="41" t="n"/>
-    </row>
-    <row r="318">
-      <c r="A318" s="40" t="inlineStr">
-        <is>
-          <t>Jul-26</t>
-        </is>
-      </c>
-      <c r="B318" s="41" t="inlineStr">
-        <is>
-          <t>Sonesta Bogotá</t>
-        </is>
-      </c>
-      <c r="C318" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D318" s="41" t="inlineStr">
-        <is>
-          <t>Social &amp; photoshoot</t>
-        </is>
-      </c>
-      <c r="E318" s="41" t="inlineStr">
-        <is>
-          <t>Correo de contacto</t>
-        </is>
-      </c>
-      <c r="F318" s="41" t="inlineStr">
-        <is>
-          <t>Versión anterior</t>
-        </is>
-      </c>
-      <c r="G318" s="41" t="inlineStr">
-        <is>
-          <t>cateryne.palacios@ghlhoteles.com</t>
-        </is>
-      </c>
-      <c r="H318" s="41" t="n"/>
-    </row>
-    <row r="319">
-      <c r="A319" s="40" t="inlineStr">
-        <is>
-          <t>Jul-26</t>
-        </is>
-      </c>
-      <c r="B319" s="41" t="inlineStr">
-        <is>
-          <t>Sonesta Bogotá</t>
-        </is>
-      </c>
-      <c r="C319" s="41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D319" s="41" t="inlineStr">
-        <is>
-          <t>Restaurant Cook's Restaurante</t>
-        </is>
-      </c>
-      <c r="E319" s="41" t="inlineStr">
-        <is>
-          <t>Horario de apertura</t>
-        </is>
-      </c>
-      <c r="F319" s="41" t="inlineStr">
-        <is>
-          <t>Versión anterior</t>
-        </is>
-      </c>
-      <c r="G319" s="41" t="inlineStr">
-        <is>
-          <t>6:00 a.m. a 12:00 p.m.</t>
-        </is>
-      </c>
-      <c r="H319" s="41" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:H227"/>
@@ -17767,8 +17387,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>

--- a/Base_Maestra_Consolidada_Dialogos_Chatbot.xlsx
+++ b/Base_Maestra_Consolidada_Dialogos_Chatbot.xlsx
@@ -3935,7 +3935,7 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>3 diálogos modificados: ubicación, check-in/out tardío</t>
+          <t>5 diálogos modificados: ubicación, check-in/out tardío, horario y tarifa de desayuno</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
@@ -3943,11 +3943,7 @@
           <t>30/07/2026</t>
         </is>
       </c>
-      <c r="J65" s="8" t="inlineStr">
-        <is>
-          <t>Se retiran horario y tarifa de desayuno del listado: coinciden con el PDF de julio vigente, no eran cambios reales</t>
-        </is>
-      </c>
+      <c r="J65" s="8" t="n"/>
       <c r="K65" s="42" t="inlineStr">
         <is>
           <t>Actualizado</t>
@@ -4636,19 +4632,23 @@
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H80" s="5" t="n"/>
-      <c r="I80" s="6" t="n"/>
-      <c r="J80" s="5" t="inlineStr">
-        <is>
-          <t>Los 8 puntos que reportó ya coinciden con el PDF de julio vigente — no eran cambios reales, solo confirmó valores ya correctos</t>
-        </is>
-      </c>
-      <c r="K80" s="38" t="inlineStr">
-        <is>
-          <t>Sin modificaciones</t>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>8 diálogos modificados: check-in/out, desayuno horario/precio, niños, mascotas, redes, restaurante</t>
+        </is>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="n"/>
+      <c r="K80" s="42" t="inlineStr">
+        <is>
+          <t>Actualizado</t>
         </is>
       </c>
       <c r="L80" s="5" t="inlineStr"/>
@@ -5096,13 +5096,13 @@
         <v>26</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
@@ -5235,10 +5235,10 @@
         <v>26</v>
       </c>
       <c r="E4" s="19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" s="19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G4" s="20" t="n">
         <v>0.3809523809523809</v>
@@ -5305,10 +5305,10 @@
         <v>45</v>
       </c>
       <c r="E6" s="28" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G6" s="29" t="n">
         <v>0.4642857142857143</v>
@@ -5344,7 +5344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H309"/>
+  <dimension ref="A1:H319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="C284" s="41" t="inlineStr">
         <is>
-          <t>19-01</t>
+          <t>9-01</t>
         </is>
       </c>
       <c r="D284" s="41" t="inlineStr">
@@ -16097,7 +16097,7 @@
       </c>
       <c r="F284" s="41" t="inlineStr">
         <is>
-          <t>Cra. 8a #38-42, Comuna 2, Neiva, Huila, Colombia</t>
+          <t>⚠ No especificada en el diálogo previo</t>
         </is>
       </c>
       <c r="G284" s="41" t="inlineStr">
@@ -16191,32 +16191,32 @@
       </c>
       <c r="B287" s="41" t="inlineStr">
         <is>
-          <t>GHL Style Yopal</t>
+          <t>GHL Style Neiva</t>
         </is>
       </c>
       <c r="C287" s="41" t="inlineStr">
         <is>
-          <t>11-01</t>
+          <t>12-01</t>
         </is>
       </c>
       <c r="D287" s="41" t="inlineStr">
         <is>
-          <t>Check in time</t>
+          <t>Breakfast time</t>
         </is>
       </c>
       <c r="E287" s="41" t="inlineStr">
         <is>
-          <t>Costo early check-in</t>
+          <t>Horario desayuno</t>
         </is>
       </c>
       <c r="F287" s="41" t="inlineStr">
         <is>
-          <t>70.000 COP por habitación</t>
+          <t>⚠ No especificado</t>
         </is>
       </c>
       <c r="G287" s="41" t="inlineStr">
         <is>
-          <t>COP 70.000 + impuestos por habitación</t>
+          <t>Buffet diario de 6:30 a.m. a 10:00 a.m.</t>
         </is>
       </c>
       <c r="H287" s="41" t="n"/>
@@ -16229,32 +16229,32 @@
       </c>
       <c r="B288" s="41" t="inlineStr">
         <is>
-          <t>GHL Style Yopal</t>
+          <t>GHL Style Neiva</t>
         </is>
       </c>
       <c r="C288" s="41" t="inlineStr">
         <is>
-          <t>11-11</t>
+          <t>12-02</t>
         </is>
       </c>
       <c r="D288" s="41" t="inlineStr">
         <is>
-          <t>Check out time</t>
+          <t>Breakfast rates</t>
         </is>
       </c>
       <c r="E288" s="41" t="inlineStr">
         <is>
-          <t>Costo late check-out</t>
+          <t>Precio adulto</t>
         </is>
       </c>
       <c r="F288" s="41" t="inlineStr">
         <is>
-          <t>70.000 COP por habitación</t>
+          <t>⚠ No especificado</t>
         </is>
       </c>
       <c r="G288" s="41" t="inlineStr">
         <is>
-          <t>COP 70.000 + impuestos por habitación</t>
+          <t>40.000 COP por adulto; incluido en tarifa de habitación; visitantes también bienvenidos</t>
         </is>
       </c>
       <c r="H288" s="41" t="n"/>
@@ -16267,32 +16267,32 @@
       </c>
       <c r="B289" s="41" t="inlineStr">
         <is>
-          <t>Hotel Tequendama Bogotá</t>
+          <t>GHL Style Yopal</t>
         </is>
       </c>
       <c r="C289" s="41" t="inlineStr">
         <is>
-          <t>13-45</t>
+          <t>11-01</t>
         </is>
       </c>
       <c r="D289" s="41" t="inlineStr">
         <is>
-          <t>Change &amp; ATM</t>
+          <t>Check in time</t>
         </is>
       </c>
       <c r="E289" s="41" t="inlineStr">
         <is>
-          <t>Disponibilidad de cajero automático</t>
+          <t>Costo early check-in</t>
         </is>
       </c>
       <c r="F289" s="41" t="inlineStr">
         <is>
-          <t>Sí tenemos un cajero automático en la propiedad</t>
+          <t>70.000 COP por habitación</t>
         </is>
       </c>
       <c r="G289" s="41" t="inlineStr">
         <is>
-          <t>No tenemos un cajero automático en la propiedad</t>
+          <t>COP 70.000 + impuestos por habitación</t>
         </is>
       </c>
       <c r="H289" s="41" t="n"/>
@@ -16305,32 +16305,32 @@
       </c>
       <c r="B290" s="41" t="inlineStr">
         <is>
-          <t>Hotel Tequendama Bogotá</t>
+          <t>GHL Style Yopal</t>
         </is>
       </c>
       <c r="C290" s="41" t="inlineStr">
         <is>
-          <t>13-06</t>
+          <t>11-11</t>
         </is>
       </c>
       <c r="D290" s="41" t="inlineStr">
         <is>
-          <t>Room Service</t>
+          <t>Check out time</t>
         </is>
       </c>
       <c r="E290" s="41" t="inlineStr">
         <is>
-          <t>Horario y marcación</t>
+          <t>Costo late check-out</t>
         </is>
       </c>
       <c r="F290" s="41" t="inlineStr">
         <is>
-          <t>Disponible de 06:00 a 22:00; marcar 2356</t>
+          <t>70.000 COP por habitación</t>
         </is>
       </c>
       <c r="G290" s="41" t="inlineStr">
         <is>
-          <t>Disponible de 06:00 a 00:00; marcar *2</t>
+          <t>COP 70.000 + impuestos por habitación</t>
         </is>
       </c>
       <c r="H290" s="41" t="n"/>
@@ -16343,32 +16343,32 @@
       </c>
       <c r="B291" s="41" t="inlineStr">
         <is>
-          <t>Sonesta Cusco</t>
+          <t>Hotel Tequendama Bogotá</t>
         </is>
       </c>
       <c r="C291" s="41" t="inlineStr">
         <is>
-          <t>16-02</t>
+          <t>13-45</t>
         </is>
       </c>
       <c r="D291" s="41" t="inlineStr">
         <is>
-          <t>Contact staff — Recepción</t>
+          <t>Change &amp; ATM</t>
         </is>
       </c>
       <c r="E291" s="41" t="inlineStr">
         <is>
-          <t>Correo</t>
+          <t>Disponibilidad de cajero automático</t>
         </is>
       </c>
       <c r="F291" s="41" t="inlineStr">
         <is>
-          <t>recepcion.sonestahotelcusco@ghlhoteles.com</t>
+          <t>Sí tenemos un cajero automático en la propiedad</t>
         </is>
       </c>
       <c r="G291" s="41" t="inlineStr">
         <is>
-          <t>recepcion.sonestacusco@ghlhoteles.com</t>
+          <t>No tenemos un cajero automático en la propiedad</t>
         </is>
       </c>
       <c r="H291" s="41" t="n"/>
@@ -16381,32 +16381,32 @@
       </c>
       <c r="B292" s="41" t="inlineStr">
         <is>
-          <t>Sonesta Cusco</t>
+          <t>Hotel Tequendama Bogotá</t>
         </is>
       </c>
       <c r="C292" s="41" t="inlineStr">
         <is>
-          <t>11-01</t>
+          <t>13-06</t>
         </is>
       </c>
       <c r="D292" s="41" t="inlineStr">
         <is>
-          <t>Check-in time</t>
+          <t>Room Service</t>
         </is>
       </c>
       <c r="E292" s="41" t="inlineStr">
         <is>
-          <t>Costo early check-in</t>
+          <t>Horario y marcación</t>
         </is>
       </c>
       <c r="F292" s="41" t="inlineStr">
         <is>
-          <t>40.00 USD por habitación</t>
+          <t>Disponible de 06:00 a 22:00; marcar 2356</t>
         </is>
       </c>
       <c r="G292" s="41" t="inlineStr">
         <is>
-          <t>60.00 USD por habitación (impuestos no incluidos)</t>
+          <t>Disponible de 06:00 a 00:00; marcar *2</t>
         </is>
       </c>
       <c r="H292" s="41" t="n"/>
@@ -16424,27 +16424,27 @@
       </c>
       <c r="C293" s="41" t="inlineStr">
         <is>
-          <t>11-11</t>
+          <t>16-02</t>
         </is>
       </c>
       <c r="D293" s="41" t="inlineStr">
         <is>
-          <t>Check-out time</t>
+          <t>Contact staff — Recepción</t>
         </is>
       </c>
       <c r="E293" s="41" t="inlineStr">
         <is>
-          <t>Costo late check-out</t>
+          <t>Correo</t>
         </is>
       </c>
       <c r="F293" s="41" t="inlineStr">
         <is>
-          <t>40.00 USD por habitación</t>
+          <t>recepcion.sonestahotelcusco@ghlhoteles.com</t>
         </is>
       </c>
       <c r="G293" s="41" t="inlineStr">
         <is>
-          <t>60.00 USD por habitación</t>
+          <t>recepcion.sonestacusco@ghlhoteles.com</t>
         </is>
       </c>
       <c r="H293" s="41" t="n"/>
@@ -16462,27 +16462,27 @@
       </c>
       <c r="C294" s="41" t="inlineStr">
         <is>
-          <t>13-06</t>
+          <t>11-01</t>
         </is>
       </c>
       <c r="D294" s="41" t="inlineStr">
         <is>
-          <t>Room service</t>
+          <t>Check-in time</t>
         </is>
       </c>
       <c r="E294" s="41" t="inlineStr">
         <is>
-          <t>Horario</t>
+          <t>Costo early check-in</t>
         </is>
       </c>
       <c r="F294" s="41" t="inlineStr">
         <is>
-          <t>Disponible de 06:00 a 21:00</t>
+          <t>40.00 USD por habitación</t>
         </is>
       </c>
       <c r="G294" s="41" t="inlineStr">
         <is>
-          <t>Disponible 24/7</t>
+          <t>60.00 USD por habitación (impuestos no incluidos)</t>
         </is>
       </c>
       <c r="H294" s="41" t="n"/>
@@ -16495,32 +16495,32 @@
       </c>
       <c r="B295" s="41" t="inlineStr">
         <is>
-          <t>Sonesta Arequipa</t>
+          <t>Sonesta Cusco</t>
         </is>
       </c>
       <c r="C295" s="41" t="inlineStr">
         <is>
-          <t>16-06</t>
+          <t>11-11</t>
         </is>
       </c>
       <c r="D295" s="41" t="inlineStr">
         <is>
-          <t>Jobs &amp; internships</t>
+          <t>Check-out time</t>
         </is>
       </c>
       <c r="E295" s="41" t="inlineStr">
         <is>
-          <t>Correo de contacto RR.HH.</t>
+          <t>Costo late check-out</t>
         </is>
       </c>
       <c r="F295" s="41" t="inlineStr">
         <is>
-          <t>contactenos@ghlhoteles.com</t>
+          <t>40.00 USD por habitación</t>
         </is>
       </c>
       <c r="G295" s="41" t="inlineStr">
         <is>
-          <t>laydy.pauca@ghlhoteles.com</t>
+          <t>60.00 USD por habitación</t>
         </is>
       </c>
       <c r="H295" s="41" t="n"/>
@@ -16533,32 +16533,32 @@
       </c>
       <c r="B296" s="41" t="inlineStr">
         <is>
-          <t>Sonesta Arequipa</t>
+          <t>Sonesta Cusco</t>
         </is>
       </c>
       <c r="C296" s="41" t="inlineStr">
         <is>
-          <t>16-25</t>
+          <t>13-06</t>
         </is>
       </c>
       <c r="D296" s="41" t="inlineStr">
         <is>
-          <t>Tips policy</t>
+          <t>Room service</t>
         </is>
       </c>
       <c r="E296" s="41" t="inlineStr">
         <is>
-          <t>Política de propinas</t>
+          <t>Horario</t>
         </is>
       </c>
       <c r="F296" s="41" t="inlineStr">
         <is>
-          <t>Tarifa estándar incluye 19% de impuesto de servicio; propina habitual y opcional</t>
+          <t>Disponible de 06:00 a 21:00</t>
         </is>
       </c>
       <c r="G296" s="41" t="inlineStr">
         <is>
-          <t>Tarifa estándar incluye el cargo por servicio; propina opcional</t>
+          <t>Disponible 24/7</t>
         </is>
       </c>
       <c r="H296" s="41" t="n"/>
@@ -16576,27 +16576,27 @@
       </c>
       <c r="C297" s="41" t="inlineStr">
         <is>
-          <t>17-01</t>
+          <t>16-06</t>
         </is>
       </c>
       <c r="D297" s="41" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Jobs &amp; internships</t>
         </is>
       </c>
       <c r="E297" s="41" t="inlineStr">
         <is>
-          <t>Detalles bar Arcadia</t>
+          <t>Correo de contacto RR.HH.</t>
         </is>
       </c>
       <c r="F297" s="41" t="inlineStr">
         <is>
-          <t>Capacidad máx. 25 pax; se sirve comida; sin happy hour listado por separado</t>
+          <t>contactenos@ghlhoteles.com</t>
         </is>
       </c>
       <c r="G297" s="41" t="inlineStr">
         <is>
-          <t>Se retira capacidad máxima y mención de comida servida; resto de condiciones igual</t>
+          <t>laydy.pauca@ghlhoteles.com</t>
         </is>
       </c>
       <c r="H297" s="41" t="n"/>
@@ -16614,27 +16614,27 @@
       </c>
       <c r="C298" s="41" t="inlineStr">
         <is>
-          <t>17-02</t>
+          <t>16-25</t>
         </is>
       </c>
       <c r="D298" s="41" t="inlineStr">
         <is>
-          <t>Bar reservation</t>
+          <t>Tips policy</t>
         </is>
       </c>
       <c r="E298" s="41" t="inlineStr">
         <is>
-          <t>Reservas de bar</t>
+          <t>Política de propinas</t>
         </is>
       </c>
       <c r="F298" s="41" t="inlineStr">
         <is>
-          <t>No se toman reservas</t>
+          <t>Tarifa estándar incluye 19% de impuesto de servicio; propina habitual y opcional</t>
         </is>
       </c>
       <c r="G298" s="41" t="inlineStr">
         <is>
-          <t>Para reservar, contactar al +51 945739921</t>
+          <t>Tarifa estándar incluye el cargo por servicio; propina opcional</t>
         </is>
       </c>
       <c r="H298" s="41" t="n"/>
@@ -16652,27 +16652,27 @@
       </c>
       <c r="C299" s="41" t="inlineStr">
         <is>
-          <t>17-10</t>
+          <t>17-01</t>
         </is>
       </c>
       <c r="D299" s="41" t="inlineStr">
         <is>
-          <t>Spa</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="E299" s="41" t="inlineStr">
         <is>
-          <t>Tarifas y kit obligatorio</t>
+          <t>Detalles bar Arcadia</t>
         </is>
       </c>
       <c r="F299" s="41" t="inlineStr">
         <is>
-          <t>Precio de huésped variable; obligatorio: pantuflas y vestido de baño; no obligatorio: bata y gorro</t>
+          <t>Capacidad máx. 25 pax; se sirve comida; sin happy hour listado por separado</t>
         </is>
       </c>
       <c r="G299" s="41" t="inlineStr">
         <is>
-          <t>Masajes con cargo adicional; obligatorio: pantuflas, gorro y vestido de baño; no obligatorio: bata</t>
+          <t>Se retira capacidad máxima y mención de comida servida; resto de condiciones igual</t>
         </is>
       </c>
       <c r="H299" s="41" t="n"/>
@@ -16690,27 +16690,27 @@
       </c>
       <c r="C300" s="41" t="inlineStr">
         <is>
-          <t>17-15</t>
+          <t>17-02</t>
         </is>
       </c>
       <c r="D300" s="41" t="inlineStr">
         <is>
-          <t>Spa hours</t>
+          <t>Bar reservation</t>
         </is>
       </c>
       <c r="E300" s="41" t="inlineStr">
         <is>
-          <t>Límite de tiempo</t>
+          <t>Reservas de bar</t>
         </is>
       </c>
       <c r="F300" s="41" t="inlineStr">
         <is>
-          <t>Sin límite de tiempo</t>
+          <t>No se toman reservas</t>
         </is>
       </c>
       <c r="G300" s="41" t="inlineStr">
         <is>
-          <t>Estancia máxima de 1 hora</t>
+          <t>Para reservar, contactar al +51 945739921</t>
         </is>
       </c>
       <c r="H300" s="41" t="n"/>
@@ -16728,27 +16728,27 @@
       </c>
       <c r="C301" s="41" t="inlineStr">
         <is>
-          <t>18-01</t>
+          <t>17-10</t>
         </is>
       </c>
       <c r="D301" s="41" t="inlineStr">
         <is>
-          <t>Restaurant</t>
+          <t>Spa</t>
         </is>
       </c>
       <c r="E301" s="41" t="inlineStr">
         <is>
-          <t>Descripción restaurante Micaela</t>
+          <t>Tarifas y kit obligatorio</t>
         </is>
       </c>
       <c r="F301" s="41" t="inlineStr">
         <is>
-          <t>Descripción extensa (tipo de cocina, capacidad, niños, reservas, cajas altas, etc.)</t>
+          <t>Precio de huésped variable; obligatorio: pantuflas y vestido de baño; no obligatorio: bata y gorro</t>
         </is>
       </c>
       <c r="G301" s="41" t="inlineStr">
         <is>
-          <t>Descripción simplificada: horario, accesibilidad, mascotas no aceptadas</t>
+          <t>Masajes con cargo adicional; obligatorio: pantuflas, gorro y vestido de baño; no obligatorio: bata</t>
         </is>
       </c>
       <c r="H301" s="41" t="n"/>
@@ -16766,27 +16766,27 @@
       </c>
       <c r="C302" s="41" t="inlineStr">
         <is>
-          <t>18-02</t>
+          <t>17-15</t>
         </is>
       </c>
       <c r="D302" s="41" t="inlineStr">
         <is>
-          <t>Restaurant reservation</t>
+          <t>Spa hours</t>
         </is>
       </c>
       <c r="E302" s="41" t="inlineStr">
         <is>
-          <t>Método de reserva</t>
+          <t>Límite de tiempo</t>
         </is>
       </c>
       <c r="F302" s="41" t="inlineStr">
         <is>
-          <t>Reservar por correo a reservas.sonestaarequipa@ghlhoteles.com</t>
+          <t>Sin límite de tiempo</t>
         </is>
       </c>
       <c r="G302" s="41" t="inlineStr">
         <is>
-          <t>Contactar al +51 945739921</t>
+          <t>Estancia máxima de 1 hora</t>
         </is>
       </c>
       <c r="H302" s="41" t="n"/>
@@ -16804,27 +16804,27 @@
       </c>
       <c r="C303" s="41" t="inlineStr">
         <is>
-          <t>18-03</t>
+          <t>18-01</t>
         </is>
       </c>
       <c r="D303" s="41" t="inlineStr">
         <is>
-          <t>Restaurant reservation cancellation</t>
+          <t>Restaurant</t>
         </is>
       </c>
       <c r="E303" s="41" t="inlineStr">
         <is>
-          <t>Método de cancelación</t>
+          <t>Descripción restaurante Micaela</t>
         </is>
       </c>
       <c r="F303" s="41" t="inlineStr">
         <is>
-          <t>Cancelar por correo</t>
+          <t>Descripción extensa (tipo de cocina, capacidad, niños, reservas, cajas altas, etc.)</t>
         </is>
       </c>
       <c r="G303" s="41" t="inlineStr">
         <is>
-          <t>Contactar al +51 945739921</t>
+          <t>Descripción simplificada: horario, accesibilidad, mascotas no aceptadas</t>
         </is>
       </c>
       <c r="H303" s="41" t="n"/>
@@ -16842,22 +16842,22 @@
       </c>
       <c r="C304" s="41" t="inlineStr">
         <is>
-          <t>18-04</t>
+          <t>18-02</t>
         </is>
       </c>
       <c r="D304" s="41" t="inlineStr">
         <is>
-          <t>Restaurant reservation modification</t>
+          <t>Restaurant reservation</t>
         </is>
       </c>
       <c r="E304" s="41" t="inlineStr">
         <is>
-          <t>Método de modificación</t>
+          <t>Método de reserva</t>
         </is>
       </c>
       <c r="F304" s="41" t="inlineStr">
         <is>
-          <t>Modificar por correo</t>
+          <t>Reservar por correo a reservas.sonestaarequipa@ghlhoteles.com</t>
         </is>
       </c>
       <c r="G304" s="41" t="inlineStr">
@@ -16880,22 +16880,22 @@
       </c>
       <c r="C305" s="41" t="inlineStr">
         <is>
-          <t>18-05</t>
+          <t>18-03</t>
         </is>
       </c>
       <c r="D305" s="41" t="inlineStr">
         <is>
-          <t>Restaurant reservation confirmation</t>
+          <t>Restaurant reservation cancellation</t>
         </is>
       </c>
       <c r="E305" s="41" t="inlineStr">
         <is>
-          <t>Método de confirmación</t>
+          <t>Método de cancelación</t>
         </is>
       </c>
       <c r="F305" s="41" t="inlineStr">
         <is>
-          <t>Confirmar por correo</t>
+          <t>Cancelar por correo</t>
         </is>
       </c>
       <c r="G305" s="41" t="inlineStr">
@@ -16918,27 +16918,27 @@
       </c>
       <c r="C306" s="41" t="inlineStr">
         <is>
-          <t>18-11</t>
+          <t>18-04</t>
         </is>
       </c>
       <c r="D306" s="41" t="inlineStr">
         <is>
-          <t>Brunch</t>
+          <t>Restaurant reservation modification</t>
         </is>
       </c>
       <c r="E306" s="41" t="inlineStr">
         <is>
-          <t>Recomendación externa</t>
+          <t>Método de modificación</t>
         </is>
       </c>
       <c r="F306" s="41" t="inlineStr">
         <is>
-          <t>No ofrecen brunch; recomiendan Restaurante Santé como alternativa externa</t>
+          <t>Modificar por correo</t>
         </is>
       </c>
       <c r="G306" s="41" t="inlineStr">
         <is>
-          <t>No ofrecemos brunch (se retira la recomendación externa)</t>
+          <t>Contactar al +51 945739921</t>
         </is>
       </c>
       <c r="H306" s="41" t="n"/>
@@ -16956,27 +16956,27 @@
       </c>
       <c r="C307" s="41" t="inlineStr">
         <is>
-          <t>18-26</t>
+          <t>18-05</t>
         </is>
       </c>
       <c r="D307" s="41" t="inlineStr">
         <is>
-          <t>Valentine's day</t>
+          <t>Restaurant reservation confirmation</t>
         </is>
       </c>
       <c r="E307" s="41" t="inlineStr">
         <is>
-          <t>Forma de consulta</t>
+          <t>Método de confirmación</t>
         </is>
       </c>
       <c r="F307" s="41" t="inlineStr">
         <is>
-          <t>Ver oferta mediante enlace</t>
+          <t>Confirmar por correo</t>
         </is>
       </c>
       <c r="G307" s="41" t="inlineStr">
         <is>
-          <t>Escribir a reservas.sonestaarequipa@ghlhoteles.com o contactar al +51 939753285</t>
+          <t>Contactar al +51 945739921</t>
         </is>
       </c>
       <c r="H307" s="41" t="n"/>
@@ -16994,27 +16994,27 @@
       </c>
       <c r="C308" s="41" t="inlineStr">
         <is>
-          <t>19-03</t>
+          <t>18-11</t>
         </is>
       </c>
       <c r="D308" s="41" t="inlineStr">
         <is>
-          <t>City center</t>
+          <t>Brunch</t>
         </is>
       </c>
       <c r="E308" s="41" t="inlineStr">
         <is>
-          <t>Distancia al centro</t>
+          <t>Recomendación externa</t>
         </is>
       </c>
       <c r="F308" s="41" t="inlineStr">
         <is>
-          <t>26 m, 1 min caminando</t>
+          <t>No ofrecen brunch; recomiendan Restaurante Santé como alternativa externa</t>
         </is>
       </c>
       <c r="G308" s="41" t="inlineStr">
         <is>
-          <t>4 km</t>
+          <t>No ofrecemos brunch (se retira la recomendación externa)</t>
         </is>
       </c>
       <c r="H308" s="41" t="n"/>
@@ -17032,30 +17032,410 @@
       </c>
       <c r="C309" s="41" t="inlineStr">
         <is>
+          <t>18-26</t>
+        </is>
+      </c>
+      <c r="D309" s="41" t="inlineStr">
+        <is>
+          <t>Valentine's day</t>
+        </is>
+      </c>
+      <c r="E309" s="41" t="inlineStr">
+        <is>
+          <t>Forma de consulta</t>
+        </is>
+      </c>
+      <c r="F309" s="41" t="inlineStr">
+        <is>
+          <t>Ver oferta mediante enlace</t>
+        </is>
+      </c>
+      <c r="G309" s="41" t="inlineStr">
+        <is>
+          <t>Escribir a reservas.sonestaarequipa@ghlhoteles.com o contactar al +51 939753285</t>
+        </is>
+      </c>
+      <c r="H309" s="41" t="n"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B310" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C310" s="41" t="inlineStr">
+        <is>
+          <t>19-03</t>
+        </is>
+      </c>
+      <c r="D310" s="41" t="inlineStr">
+        <is>
+          <t>City center</t>
+        </is>
+      </c>
+      <c r="E310" s="41" t="inlineStr">
+        <is>
+          <t>Distancia al centro</t>
+        </is>
+      </c>
+      <c r="F310" s="41" t="inlineStr">
+        <is>
+          <t>26 m, 1 min caminando</t>
+        </is>
+      </c>
+      <c r="G310" s="41" t="inlineStr">
+        <is>
+          <t>4 km</t>
+        </is>
+      </c>
+      <c r="H310" s="41" t="n"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B311" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C311" s="41" t="inlineStr">
+        <is>
           <t>20-21</t>
         </is>
       </c>
-      <c r="D309" s="41" t="inlineStr">
+      <c r="D311" s="41" t="inlineStr">
         <is>
           <t>Celebration</t>
         </is>
       </c>
-      <c r="E309" s="41" t="inlineStr">
+      <c r="E311" s="41" t="inlineStr">
         <is>
           <t>Teléfono de eventos</t>
         </is>
       </c>
-      <c r="F309" s="41" t="inlineStr">
+      <c r="F311" s="41" t="inlineStr">
         <is>
           <t>+51 945 739 48</t>
         </is>
       </c>
-      <c r="G309" s="41" t="inlineStr">
+      <c r="G311" s="41" t="inlineStr">
         <is>
           <t>+51 945 739 484 (corrección de dígito faltante)</t>
         </is>
       </c>
-      <c r="H309" s="41" t="n"/>
+      <c r="H311" s="41" t="n"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B312" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Bogotá</t>
+        </is>
+      </c>
+      <c r="C312" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D312" s="41" t="inlineStr">
+        <is>
+          <t>Check in time</t>
+        </is>
+      </c>
+      <c r="E312" s="41" t="inlineStr">
+        <is>
+          <t>Costo early check-in</t>
+        </is>
+      </c>
+      <c r="F312" s="41" t="inlineStr">
+        <is>
+          <t>Versión anterior</t>
+        </is>
+      </c>
+      <c r="G312" s="41" t="inlineStr">
+        <is>
+          <t>$35.000, sujeto a disponibilidad</t>
+        </is>
+      </c>
+      <c r="H312" s="41" t="n"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B313" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Bogotá</t>
+        </is>
+      </c>
+      <c r="C313" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D313" s="41" t="inlineStr">
+        <is>
+          <t>Check out time</t>
+        </is>
+      </c>
+      <c r="E313" s="41" t="inlineStr">
+        <is>
+          <t>Late check-out</t>
+        </is>
+      </c>
+      <c r="F313" s="41" t="inlineStr">
+        <is>
+          <t>Versión anterior</t>
+        </is>
+      </c>
+      <c r="G313" s="41" t="inlineStr">
+        <is>
+          <t>$35.000 por hora; después de las 6:00 p.m. se cobra la tarifa completa</t>
+        </is>
+      </c>
+      <c r="H313" s="41" t="n"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B314" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Bogotá</t>
+        </is>
+      </c>
+      <c r="C314" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D314" s="41" t="inlineStr">
+        <is>
+          <t>Breakfast time</t>
+        </is>
+      </c>
+      <c r="E314" s="41" t="inlineStr">
+        <is>
+          <t>Horario sábados, domingos y festivos</t>
+        </is>
+      </c>
+      <c r="F314" s="41" t="inlineStr">
+        <is>
+          <t>Versión anterior</t>
+        </is>
+      </c>
+      <c r="G314" s="41" t="inlineStr">
+        <is>
+          <t>6:30 a.m. a 10:30 a.m.</t>
+        </is>
+      </c>
+      <c r="H314" s="41" t="n"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B315" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Bogotá</t>
+        </is>
+      </c>
+      <c r="C315" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D315" s="41" t="inlineStr">
+        <is>
+          <t>Breakfast rates</t>
+        </is>
+      </c>
+      <c r="E315" s="41" t="inlineStr">
+        <is>
+          <t>Precio por persona</t>
+        </is>
+      </c>
+      <c r="F315" s="41" t="inlineStr">
+        <is>
+          <t>Versión anterior</t>
+        </is>
+      </c>
+      <c r="G315" s="41" t="inlineStr">
+        <is>
+          <t>$65.000 COP</t>
+        </is>
+      </c>
+      <c r="H315" s="41" t="n"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B316" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Bogotá</t>
+        </is>
+      </c>
+      <c r="C316" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D316" s="41" t="inlineStr">
+        <is>
+          <t>Kids</t>
+        </is>
+      </c>
+      <c r="E316" s="41" t="inlineStr">
+        <is>
+          <t>Tarifa niños</t>
+        </is>
+      </c>
+      <c r="F316" s="41" t="inlineStr">
+        <is>
+          <t>Versión anterior</t>
+        </is>
+      </c>
+      <c r="G316" s="41" t="inlineStr">
+        <is>
+          <t>Menores de 12 años gratis con sus padres; mayores de 12 años $80.000 por noche</t>
+        </is>
+      </c>
+      <c r="H316" s="41" t="n"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B317" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Bogotá</t>
+        </is>
+      </c>
+      <c r="C317" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D317" s="41" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="E317" s="41" t="inlineStr">
+        <is>
+          <t>Peso permitido</t>
+        </is>
+      </c>
+      <c r="F317" s="41" t="inlineStr">
+        <is>
+          <t>Versión anterior</t>
+        </is>
+      </c>
+      <c r="G317" s="41" t="inlineStr">
+        <is>
+          <t>10 kg</t>
+        </is>
+      </c>
+      <c r="H317" s="41" t="n"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B318" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Bogotá</t>
+        </is>
+      </c>
+      <c r="C318" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D318" s="41" t="inlineStr">
+        <is>
+          <t>Social &amp; photoshoot</t>
+        </is>
+      </c>
+      <c r="E318" s="41" t="inlineStr">
+        <is>
+          <t>Correo de contacto</t>
+        </is>
+      </c>
+      <c r="F318" s="41" t="inlineStr">
+        <is>
+          <t>Versión anterior</t>
+        </is>
+      </c>
+      <c r="G318" s="41" t="inlineStr">
+        <is>
+          <t>cateryne.palacios@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="H318" s="41" t="n"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="40" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B319" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Bogotá</t>
+        </is>
+      </c>
+      <c r="C319" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D319" s="41" t="inlineStr">
+        <is>
+          <t>Restaurant Cook's Restaurante</t>
+        </is>
+      </c>
+      <c r="E319" s="41" t="inlineStr">
+        <is>
+          <t>Horario de apertura</t>
+        </is>
+      </c>
+      <c r="F319" s="41" t="inlineStr">
+        <is>
+          <t>Versión anterior</t>
+        </is>
+      </c>
+      <c r="G319" s="41" t="inlineStr">
+        <is>
+          <t>6:00 a.m. a 12:00 p.m.</t>
+        </is>
+      </c>
+      <c r="H319" s="41" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:H227"/>
@@ -17387,6 +17767,8 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>

--- a/Base_Maestra_Consolidada_Dialogos_Chatbot.xlsx
+++ b/Base_Maestra_Consolidada_Dialogos_Chatbot.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="26">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -171,8 +171,23 @@
       <color rgb="00006100"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="0092400E"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="009C0006"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001F4E79"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -260,8 +275,14 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -341,11 +362,55 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00023859"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D1D1D1"/>
+      </right>
+      <top style="medium">
+        <color rgb="00023859"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00023859"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D1D1D1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D1D1D1"/>
+      </right>
+      <top style="medium">
+        <color rgb="00023859"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D1D1D1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -465,6 +530,9 @@
     <xf numFmtId="0" fontId="25" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -830,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L87"/>
+  <dimension ref="A1:L129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4946,6 +5014,1600 @@
         </is>
       </c>
       <c r="L87" s="8" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Luis Saez</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>luis.saez@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K88" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Biohotel</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Maria Del Pilar Narvaez</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>pilar.narvaez@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K89" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Bioxury</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>calidad.bioxury@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K90" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Geotel Antofagasta</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Nelson Uriel Perez Ortiz</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>nelson.perez@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K91" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Geotel Calama</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Katherine Mora</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>katherine.mora@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K92" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>GHL Collection 93</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>James Mendoza</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>james.mendoza@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K93" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Armeria Real</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Saray Estrada</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Saray.estrada@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Confirmó sin cambios para agosto</t>
+        </is>
+      </c>
+      <c r="K94" s="45" t="inlineStr">
+        <is>
+          <t>Sin modificaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>GHL Collection Hamilton</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Wilson Bohorquez</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>andres.bohorquez@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K95" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>GHL Grand Villavicencio</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ingrid Mendez</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>jimena.mendez@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K96" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>GHL Hotel Capital</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Maira Piza</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>maira.piza@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K97" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>GHL Lago Titicaca</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Milagros Velazco Reyes</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>milagros.velazco@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K98" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>GHL Montería</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Jose Medina</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>mauricio.medina@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Confirmó sin cambios para agosto</t>
+        </is>
+      </c>
+      <c r="K99" s="45" t="inlineStr">
+        <is>
+          <t>Sin modificaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>GHL Portón Medellín</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Jose Fernando Villareal</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>jose.villareal@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K100" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>GHL Relax Club Hotel el Puente</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Maria Gomez</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>angelica.gomez@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K101" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>GHL Relax Hotel Corales de Indias</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Andres Narvaez</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>andres.narvaez@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K102" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>GHL Relax Hotel Costa Azul</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Marlis Marriaga</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>marlys.marriaga@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Confirmó sin cambios para agosto</t>
+        </is>
+      </c>
+      <c r="K103" s="45" t="inlineStr">
+        <is>
+          <t>Sin modificaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>GHL Relax Hotel Sunrise</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Juan Martinez</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>juan.martinez@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K104" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>GHL Style Barrancabermeja</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Luis Martinez</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>luis.martinez@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K105" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>GHL Style Bogotá Occidente</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Leidy Cely</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>jrecepcion.bogotaoccidente@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K106" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>GHL Style Neiva</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Carlos Robayo</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>yobani.robayo@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K107" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>GHL Style Yopal</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Mafy Daniela Rodriguez</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>daniela.rodriguez@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K108" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Hotel Tequendama Bogotá</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Sara Judith Aguirre</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>sara.aguirre@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K109" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>GHL Hotel Abadía Plaza</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Katerine Ospina Gil</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>suprecepcion.abadiaplaza@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K110" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>GHL Hotel Grand Barranquilla</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Jose Carlos Ibañez</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>jose.ibanez@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K111" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>LATAM XELA</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Gabriela Rodas</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>gabriela.rodas@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K112" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Makani Luxury Wanderlust</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Jose Macea</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>jose.macea@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K113" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Park Lake Luxury</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>reservas.parklake@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K114" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>San Lazaro Art</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Keilis Mercado</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>keilis.mercado@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K115" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Sonesta Bucaramanga</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Jeferson Reyes</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>jeferson.reyes@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K116" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Sonesta Cali</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Lorena Figueroa</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>lorena.figueroa@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K117" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Sonesta Cartagena</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Liliana Rodriguez</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>liliana.rodriguez@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K118" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Sonesta Cusco</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Adolfo Alfaro</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>adolfo.alfaro@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Confirmó sin cambios para agosto</t>
+        </is>
+      </c>
+      <c r="K119" s="45" t="inlineStr">
+        <is>
+          <t>Sin modificaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Sonesta El Olivar</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Andrea Silvana Zevallos</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>andrea.zevallos@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K120" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Tania Catacora</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>jefederecepcion.sonestaarequipa@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K121" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Sonesta Bogotá</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Catalina Rojas</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>catalina.rojas@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K122" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Sonesta Ibagué</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Wilmer Rodriguez</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>wilmer.rodriguez@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K123" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Sonesta Loja</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Miryam Ramirez</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>miryam.ramirez@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K124" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Sonesta Osorno</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Cristina Sanzana</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>cristina.sanzana@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K125" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Sonesta Pereira</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Edwar Pacanchique</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>edwar.pacanchique@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K126" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Sonesta Puno</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Delmy Nuñez</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>delmy.nunez@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K127" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Sonesta Yucay</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Monica Chirinos</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>monica.chirinos@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K128" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Sonesta Valledupar</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Emerson David Cotes</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>emerson.cotes@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K129" s="44" t="inlineStr">
+        <is>
+          <t>Sin respuesta</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:M87"/>
@@ -4971,7 +6633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5111,6 +6773,40 @@
       </c>
       <c r="I5" s="17">
         <f>IF(B5&gt;0,C5/B5,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="I6" s="17">
+        <f>IF(B6&gt;0,C6/B6,0)</f>
         <v/>
       </c>
     </row>
@@ -5138,7 +6834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5222,106 +6918,140 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="18" t="inlineStr">
         <is>
-          <t>Jul-26</t>
+          <t>Ago-26</t>
         </is>
       </c>
       <c r="B4" s="19" t="n">
         <v>42</v>
       </c>
       <c r="C4" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" s="19" t="n">
+        <v>38</v>
+      </c>
+      <c r="E4" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="20" t="n">
+        <v>0.09523809523809523</v>
+      </c>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t>███░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
+        </is>
+      </c>
+      <c r="I4" s="22" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="n">
+        <v>42</v>
+      </c>
+      <c r="C5" s="19" t="n">
         <v>16</v>
       </c>
-      <c r="D4" s="19" t="n">
+      <c r="D5" s="19" t="n">
         <v>26</v>
       </c>
-      <c r="E4" s="19" t="n">
+      <c r="E5" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="F4" s="19" t="n">
+      <c r="F5" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="G4" s="20" t="n">
+      <c r="G5" s="20" t="n">
         <v>0.3809523809523809</v>
       </c>
-      <c r="H4" s="21" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t>███████████░░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
-      <c r="I4" s="22" t="inlineStr">
+      <c r="I5" s="22" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
-        <is>
-          <t>Jun-26</t>
-        </is>
-      </c>
-      <c r="B5" s="24" t="n">
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>Jun-26</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="n">
         <v>42</v>
       </c>
-      <c r="C5" s="24" t="n">
+      <c r="C6" s="24" t="n">
         <v>23</v>
       </c>
-      <c r="D5" s="24" t="n">
+      <c r="D6" s="24" t="n">
         <v>19</v>
       </c>
-      <c r="E5" s="24" t="n">
+      <c r="E6" s="24" t="n">
         <v>23</v>
       </c>
-      <c r="F5" s="24" t="n">
+      <c r="F6" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="20" t="n">
+      <c r="G6" s="20" t="n">
         <v>0.5476190476190477</v>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="H6" s="25" t="inlineStr">
         <is>
           <t>████████████████░░░░░░░░░░░░░░</t>
         </is>
       </c>
-      <c r="I5" s="26" t="inlineStr">
+      <c r="I6" s="26" t="inlineStr">
         <is>
           <t>En progreso</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="27" t="inlineStr">
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B6" s="28" t="n">
-        <v>84</v>
-      </c>
-      <c r="C6" s="28" t="n">
-        <v>39</v>
-      </c>
-      <c r="D6" s="28" t="n">
-        <v>45</v>
-      </c>
-      <c r="E6" s="28" t="n">
+      <c r="B7" t="n">
+        <v>126</v>
+      </c>
+      <c r="C7" t="n">
+        <v>43</v>
+      </c>
+      <c r="D7" t="n">
+        <v>83</v>
+      </c>
+      <c r="E7" t="n">
         <v>31</v>
       </c>
-      <c r="F6" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="G6" s="29" t="n">
-        <v>0.4642857142857143</v>
-      </c>
-      <c r="H6" s="30" t="inlineStr">
-        <is>
-          <t>██████████████░░░░░░░░░░░░░░░░</t>
-        </is>
-      </c>
-      <c r="I6" s="28" t="inlineStr"/>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="36" t="inlineStr">
+      <c r="F7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3412698412698413</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>██████████░░░░░░░░░░░░░░░░░░░░</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>Nota: La barra de progreso refleja % de hoteles que respondieron el correo (con o sin modificaciones). Completo = 100% · En progreso = 50-99% · Pendiente = &lt; 50%</t>
         </is>
@@ -5329,9 +7059,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A7:I7"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A6"/>
+    <mergeCell ref="A8:I8"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17767,8 +19497,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>

--- a/Base_Maestra_Consolidada_Dialogos_Chatbot.xlsx
+++ b/Base_Maestra_Consolidada_Dialogos_Chatbot.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -184,6 +184,11 @@
     <font>
       <name val="Calibri"/>
       <color rgb="001F4E79"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00856404"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -410,7 +415,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -533,6 +538,7 @@
     <xf numFmtId="0" fontId="26" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5041,14 +5047,24 @@
           <t>02/08/2026</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K88" s="44" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2 diálogos modificados: Breakfast time, Fitness gym</t>
+        </is>
+      </c>
+      <c r="K88" s="46" t="inlineStr">
+        <is>
+          <t>Pendiente actualización</t>
         </is>
       </c>
     </row>
@@ -5189,14 +5205,24 @@
           <t>02/08/2026</t>
         </is>
       </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K92" s="44" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>14 diálogos modificados: Contact staff, Laundry/paraguas, Invoice, Currencies, Accommodation, Family accommodation, ...</t>
+        </is>
+      </c>
+      <c r="K92" s="46" t="inlineStr">
+        <is>
+          <t>Pendiente actualización</t>
         </is>
       </c>
     </row>
@@ -5542,14 +5568,24 @@
           <t>02/08/2026</t>
         </is>
       </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K101" s="44" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>11 diálogos modificados: Opening, closing &amp; renovation, Day use reservation, Extra bed, View, TV, Pets, ...</t>
+        </is>
+      </c>
+      <c r="K101" s="46" t="inlineStr">
+        <is>
+          <t>Pendiente actualización</t>
         </is>
       </c>
     </row>
@@ -5737,14 +5773,24 @@
           <t>02/08/2026</t>
         </is>
       </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K106" s="44" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>3 diálogos modificados: Business meetings, Breakfast rates, Private transfer</t>
+        </is>
+      </c>
+      <c r="K106" s="46" t="inlineStr">
+        <is>
+          <t>Pendiente actualización</t>
         </is>
       </c>
     </row>
@@ -5811,14 +5857,24 @@
           <t>02/08/2026</t>
         </is>
       </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K108" s="44" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>7 diálogos modificados: Payment method, Check-in time, Check-out time, Breakfast time, Breakfast rates, Pets, ...</t>
+        </is>
+      </c>
+      <c r="K108" s="46" t="inlineStr">
+        <is>
+          <t>Pendiente actualización</t>
         </is>
       </c>
     </row>
@@ -5848,14 +5904,24 @@
           <t>02/08/2026</t>
         </is>
       </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K109" s="44" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>2 diálogos modificados: Room service, Restaurant</t>
+        </is>
+      </c>
+      <c r="K109" s="46" t="inlineStr">
+        <is>
+          <t>Pendiente actualización</t>
         </is>
       </c>
     </row>
@@ -5922,14 +5988,24 @@
           <t>02/08/2026</t>
         </is>
       </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>08/08/2026</t>
+        </is>
+      </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K111" s="44" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>11 diálogos modificados: City tax, fees &amp; VAT, Payment method, Kids, Private transfer, Taxi, Smoking, ...</t>
+        </is>
+      </c>
+      <c r="K111" s="46" t="inlineStr">
+        <is>
+          <t>Pendiente actualización</t>
         </is>
       </c>
     </row>
@@ -6107,14 +6183,24 @@
           <t>02/08/2026</t>
         </is>
       </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K116" s="44" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>4 diálogos modificados: Room service, Bar, Rooftop, Restaurant</t>
+        </is>
+      </c>
+      <c r="K116" s="46" t="inlineStr">
+        <is>
+          <t>Pendiente actualización</t>
         </is>
       </c>
     </row>
@@ -6265,14 +6351,24 @@
           <t>02/08/2026</t>
         </is>
       </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K120" s="44" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>17 diálogos modificados: Contact staff, Check-in time, Check-out time, Breakfast rates, Parking, Connecting accommodation, ...</t>
+        </is>
+      </c>
+      <c r="K120" s="46" t="inlineStr">
+        <is>
+          <t>Pendiente actualización</t>
         </is>
       </c>
     </row>
@@ -6302,14 +6398,24 @@
           <t>02/08/2026</t>
         </is>
       </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K121" s="44" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>14 diálogos modificados: Breakfast reservation, Medical services, Currencies, Private transfer reservation, Accommodation, Smoking, ...</t>
+        </is>
+      </c>
+      <c r="K121" s="46" t="inlineStr">
+        <is>
+          <t>Pendiente actualización</t>
         </is>
       </c>
     </row>
@@ -6339,14 +6445,24 @@
           <t>02/08/2026</t>
         </is>
       </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K122" s="44" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>5 diálogos modificados: Breakfast time, Breakfast rates, Room service, Extra bed, Balcony &amp; windows</t>
+        </is>
+      </c>
+      <c r="K122" s="46" t="inlineStr">
+        <is>
+          <t>Pendiente actualización</t>
         </is>
       </c>
     </row>
@@ -6450,14 +6566,24 @@
           <t>02/08/2026</t>
         </is>
       </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K125" s="44" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>1 diálogos modificados: Breakfast rates</t>
+        </is>
+      </c>
+      <c r="K125" s="46" t="inlineStr">
+        <is>
+          <t>Pendiente actualización</t>
         </is>
       </c>
     </row>
@@ -6786,13 +6912,13 @@
         <v>42</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>4</v>
@@ -6802,7 +6928,7 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="I6" s="17">
@@ -6925,23 +7051,23 @@
         <v>42</v>
       </c>
       <c r="C4" s="19" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D4" s="19" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E4" s="19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F4" s="19" t="n">
         <v>4</v>
       </c>
       <c r="G4" s="20" t="n">
-        <v>0.09523809523809523</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t>███░░░░░░░░░░░░░░░░░░░░░░░░░░░</t>
+          <t>███████████░░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
       <c r="I4" s="22" t="inlineStr">
@@ -7030,23 +7156,23 @@
         <v>126</v>
       </c>
       <c r="C7" t="n">
+        <v>55</v>
+      </c>
+      <c r="D7" t="n">
+        <v>71</v>
+      </c>
+      <c r="E7" t="n">
         <v>43</v>
-      </c>
-      <c r="D7" t="n">
-        <v>83</v>
-      </c>
-      <c r="E7" t="n">
-        <v>31</v>
       </c>
       <c r="F7" t="n">
         <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3412698412698413</v>
+        <v>0.4365079365079365</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>██████████░░░░░░░░░░░░░░░░░░░░</t>
+          <t>█████████████░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H319"/>
+  <dimension ref="A1:H410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -19166,6 +19292,3464 @@
         </is>
       </c>
       <c r="H319" s="41" t="n"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B320" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Bogotá</t>
+        </is>
+      </c>
+      <c r="C320" s="41" t="inlineStr">
+        <is>
+          <t>12-01</t>
+        </is>
+      </c>
+      <c r="D320" s="41" t="inlineStr">
+        <is>
+          <t>Breakfast time</t>
+        </is>
+      </c>
+      <c r="E320" s="41" t="inlineStr">
+        <is>
+          <t>Servicio de desayuno en habitación</t>
+        </is>
+      </c>
+      <c r="F320" s="41" t="inlineStr">
+        <is>
+          <t>No se ofrecía desayuno en habitación</t>
+        </is>
+      </c>
+      <c r="G320" s="41" t="inlineStr">
+        <is>
+          <t>Se ofrece con costo adicional de $68.000 COP</t>
+        </is>
+      </c>
+      <c r="H320" s="41" t="n"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B321" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Bogotá</t>
+        </is>
+      </c>
+      <c r="C321" s="41" t="inlineStr">
+        <is>
+          <t>12-02</t>
+        </is>
+      </c>
+      <c r="D321" s="41" t="inlineStr">
+        <is>
+          <t>Breakfast rates</t>
+        </is>
+      </c>
+      <c r="E321" s="41" t="inlineStr">
+        <is>
+          <t>Precio por adulto</t>
+        </is>
+      </c>
+      <c r="F321" s="41" t="inlineStr">
+        <is>
+          <t>$65.000 COP</t>
+        </is>
+      </c>
+      <c r="G321" s="41" t="inlineStr">
+        <is>
+          <t>$68.000 COP</t>
+        </is>
+      </c>
+      <c r="H321" s="41" t="n"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B322" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Bogotá</t>
+        </is>
+      </c>
+      <c r="C322" s="41" t="inlineStr">
+        <is>
+          <t>13-06</t>
+        </is>
+      </c>
+      <c r="D322" s="41" t="inlineStr">
+        <is>
+          <t>Room service</t>
+        </is>
+      </c>
+      <c r="E322" s="41" t="inlineStr">
+        <is>
+          <t>Horario y código de marcado</t>
+        </is>
+      </c>
+      <c r="F322" s="41" t="inlineStr">
+        <is>
+          <t>07:00 a 21:00, marcar 2</t>
+        </is>
+      </c>
+      <c r="G322" s="41" t="inlineStr">
+        <is>
+          <t>Disponible 24/7, marcar 1</t>
+        </is>
+      </c>
+      <c r="H322" s="41" t="n"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B323" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Bogotá</t>
+        </is>
+      </c>
+      <c r="C323" s="41" t="inlineStr">
+        <is>
+          <t>15-23</t>
+        </is>
+      </c>
+      <c r="D323" s="41" t="inlineStr">
+        <is>
+          <t>Extra bed</t>
+        </is>
+      </c>
+      <c r="E323" s="41" t="inlineStr">
+        <is>
+          <t>Disponibilidad y solicitud</t>
+        </is>
+      </c>
+      <c r="F323" s="41" t="inlineStr">
+        <is>
+          <t>⚠ No especificado previamente</t>
+        </is>
+      </c>
+      <c r="G323" s="41" t="inlineStr">
+        <is>
+          <t>Cama supletoria disponible; solicitar a reservas.sonestabogota@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="H323" s="41" t="n"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B324" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Bogotá</t>
+        </is>
+      </c>
+      <c r="C324" s="41" t="inlineStr">
+        <is>
+          <t>15-61</t>
+        </is>
+      </c>
+      <c r="D324" s="41" t="inlineStr">
+        <is>
+          <t>Balcony &amp; windows</t>
+        </is>
+      </c>
+      <c r="E324" s="41" t="inlineStr">
+        <is>
+          <t>Disponibilidad de balcón</t>
+        </is>
+      </c>
+      <c r="F324" s="41" t="inlineStr">
+        <is>
+          <t>Todas las habitaciones tienen balcón</t>
+        </is>
+      </c>
+      <c r="G324" s="41" t="inlineStr">
+        <is>
+          <t>Se elimina esa afirmación (ventanas no se abren por seguridad)</t>
+        </is>
+      </c>
+      <c r="H324" s="41" t="n"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B325" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta El Olivar</t>
+        </is>
+      </c>
+      <c r="C325" s="41" t="inlineStr">
+        <is>
+          <t>16-02</t>
+        </is>
+      </c>
+      <c r="D325" s="41" t="inlineStr">
+        <is>
+          <t>Contact staff</t>
+        </is>
+      </c>
+      <c r="E325" s="41" t="inlineStr">
+        <is>
+          <t>Teléfonos por departamento y correo reservas</t>
+        </is>
+      </c>
+      <c r="F325" s="41" t="inlineStr">
+        <is>
+          <t>Solo correos; reservas.sonestaolivar1@...</t>
+        </is>
+      </c>
+      <c r="G325" s="41" t="inlineStr">
+        <is>
+          <t>Se agregan celulares por área; correo reservas pasa a reservas.sonestaolivar@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="H325" s="41" t="n"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B326" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta El Olivar</t>
+        </is>
+      </c>
+      <c r="C326" s="41" t="inlineStr">
+        <is>
+          <t>11-01</t>
+        </is>
+      </c>
+      <c r="D326" s="41" t="inlineStr">
+        <is>
+          <t>Check-in time</t>
+        </is>
+      </c>
+      <c r="E326" s="41" t="inlineStr">
+        <is>
+          <t>Costo early check-in</t>
+        </is>
+      </c>
+      <c r="F326" s="41" t="inlineStr">
+        <is>
+          <t>Desde 07:00 por 83.300 USD/habitación</t>
+        </is>
+      </c>
+      <c r="G326" s="41" t="inlineStr">
+        <is>
+          <t>Desde 10:00 por media tarifa/habitación</t>
+        </is>
+      </c>
+      <c r="H326" s="41" t="n"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B327" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta El Olivar</t>
+        </is>
+      </c>
+      <c r="C327" s="41" t="inlineStr">
+        <is>
+          <t>11-11</t>
+        </is>
+      </c>
+      <c r="D327" s="41" t="inlineStr">
+        <is>
+          <t>Check-out time</t>
+        </is>
+      </c>
+      <c r="E327" s="41" t="inlineStr">
+        <is>
+          <t>Check-out normal y tardío</t>
+        </is>
+      </c>
+      <c r="F327" s="41" t="inlineStr">
+        <is>
+          <t>Antes de 13:00; tardío 83.300 USD</t>
+        </is>
+      </c>
+      <c r="G327" s="41" t="inlineStr">
+        <is>
+          <t>Antes del mediodía; tardío por media tarifa</t>
+        </is>
+      </c>
+      <c r="H327" s="41" t="n"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B328" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta El Olivar</t>
+        </is>
+      </c>
+      <c r="C328" s="41" t="inlineStr">
+        <is>
+          <t>12-02</t>
+        </is>
+      </c>
+      <c r="D328" s="41" t="inlineStr">
+        <is>
+          <t>Breakfast rates</t>
+        </is>
+      </c>
+      <c r="E328" s="41" t="inlineStr">
+        <is>
+          <t>Precio adulto/niño</t>
+        </is>
+      </c>
+      <c r="F328" s="41" t="inlineStr">
+        <is>
+          <t>26 USD adulto / 14 USD niño</t>
+        </is>
+      </c>
+      <c r="G328" s="41" t="inlineStr">
+        <is>
+          <t>S/79 (Lun-Sáb) / S/89 (Dom) adulto; S/45 niño</t>
+        </is>
+      </c>
+      <c r="H328" s="41" t="n"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B329" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta El Olivar</t>
+        </is>
+      </c>
+      <c r="C329" s="41" t="inlineStr">
+        <is>
+          <t>13-01</t>
+        </is>
+      </c>
+      <c r="D329" s="41" t="inlineStr">
+        <is>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="E329" s="41" t="inlineStr">
+        <is>
+          <t>Servicio de aparcacoches</t>
+        </is>
+      </c>
+      <c r="F329" s="41" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="G329" s="41" t="inlineStr">
+        <is>
+          <t>No disponible</t>
+        </is>
+      </c>
+      <c r="H329" s="41" t="n"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B330" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta El Olivar</t>
+        </is>
+      </c>
+      <c r="C330" s="41" t="inlineStr">
+        <is>
+          <t>14-02</t>
+        </is>
+      </c>
+      <c r="D330" s="41" t="inlineStr">
+        <is>
+          <t>Connecting accommodation</t>
+        </is>
+      </c>
+      <c r="E330" s="41" t="inlineStr">
+        <is>
+          <t>Tipos de habitación conectados</t>
+        </is>
+      </c>
+      <c r="F330" s="41" t="inlineStr">
+        <is>
+          <t>6 tipos disponibles</t>
+        </is>
+      </c>
+      <c r="G330" s="41" t="inlineStr">
+        <is>
+          <t>Solo Executive Double</t>
+        </is>
+      </c>
+      <c r="H330" s="41" t="n"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B331" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta El Olivar</t>
+        </is>
+      </c>
+      <c r="C331" s="41" t="inlineStr">
+        <is>
+          <t>14-04</t>
+        </is>
+      </c>
+      <c r="D331" s="41" t="inlineStr">
+        <is>
+          <t>Smoking</t>
+        </is>
+      </c>
+      <c r="E331" s="41" t="inlineStr">
+        <is>
+          <t>Detectores de humo y tarifa</t>
+        </is>
+      </c>
+      <c r="F331" s="41" t="inlineStr">
+        <is>
+          <t>Sin detectores; tarifa 0 USD</t>
+        </is>
+      </c>
+      <c r="G331" s="41" t="inlineStr">
+        <is>
+          <t>Con detectores; tarifa 200 USD + impuestos</t>
+        </is>
+      </c>
+      <c r="H331" s="41" t="n"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B332" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta El Olivar</t>
+        </is>
+      </c>
+      <c r="C332" s="41" t="inlineStr">
+        <is>
+          <t>15-06</t>
+        </is>
+      </c>
+      <c r="D332" s="41" t="inlineStr">
+        <is>
+          <t>Bathroom equipment</t>
+        </is>
+      </c>
+      <c r="E332" s="41" t="inlineStr">
+        <is>
+          <t>Amenidades gratuitas a petición</t>
+        </is>
+      </c>
+      <c r="F332" s="41" t="inlineStr">
+        <is>
+          <t>Pantuflas, pasta dientes, kit afeitar</t>
+        </is>
+      </c>
+      <c r="G332" s="41" t="inlineStr">
+        <is>
+          <t>Pantuflas, vanity kit, kit dental, kit afeitar, peine</t>
+        </is>
+      </c>
+      <c r="H332" s="41" t="n"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B333" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta El Olivar</t>
+        </is>
+      </c>
+      <c r="C333" s="41" t="inlineStr">
+        <is>
+          <t>15-09</t>
+        </is>
+      </c>
+      <c r="D333" s="41" t="inlineStr">
+        <is>
+          <t>Shower/bathtub/jacuzzi</t>
+        </is>
+      </c>
+      <c r="E333" s="41" t="inlineStr">
+        <is>
+          <t>Habitaciones con ducha/bañera</t>
+        </is>
+      </c>
+      <c r="F333" s="41" t="inlineStr">
+        <is>
+          <t>Incluye Ejecutiva Simple y Junior Suite con bañera</t>
+        </is>
+      </c>
+      <c r="G333" s="41" t="inlineStr">
+        <is>
+          <t>Se renombran categorías; Suite solo con ducha</t>
+        </is>
+      </c>
+      <c r="H333" s="41" t="n"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B334" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta El Olivar</t>
+        </is>
+      </c>
+      <c r="C334" s="41" t="inlineStr">
+        <is>
+          <t>15-61</t>
+        </is>
+      </c>
+      <c r="D334" s="41" t="inlineStr">
+        <is>
+          <t>Balcony &amp; windows</t>
+        </is>
+      </c>
+      <c r="E334" s="41" t="inlineStr">
+        <is>
+          <t>Ventanas y balcón</t>
+        </is>
+      </c>
+      <c r="F334" s="41" t="inlineStr">
+        <is>
+          <t>No se abren; todas con balcón</t>
+        </is>
+      </c>
+      <c r="G334" s="41" t="inlineStr">
+        <is>
+          <t>Sí se abren; no todas tienen balcón</t>
+        </is>
+      </c>
+      <c r="H334" s="41" t="n"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B335" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta El Olivar</t>
+        </is>
+      </c>
+      <c r="C335" s="41" t="inlineStr">
+        <is>
+          <t>16-10</t>
+        </is>
+      </c>
+      <c r="D335" s="41" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="E335" s="41" t="inlineStr">
+        <is>
+          <t>Restricciones</t>
+        </is>
+      </c>
+      <c r="F335" s="41" t="inlineStr">
+        <is>
+          <t>Máx. 2 mascotas; peso 20kg</t>
+        </is>
+      </c>
+      <c r="G335" s="41" t="inlineStr">
+        <is>
+          <t>Solo 2 habitaciones pet-friendly; máx. 1 mascota</t>
+        </is>
+      </c>
+      <c r="H335" s="41" t="n"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B336" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta El Olivar</t>
+        </is>
+      </c>
+      <c r="C336" s="41" t="inlineStr">
+        <is>
+          <t>17-01</t>
+        </is>
+      </c>
+      <c r="D336" s="41" t="inlineStr">
+        <is>
+          <t>Bar</t>
+        </is>
+      </c>
+      <c r="E336" s="41" t="inlineStr">
+        <is>
+          <t>Horario y servicio de comida</t>
+        </is>
+      </c>
+      <c r="F336" s="41" t="inlineStr">
+        <is>
+          <t>12:00-21:00, se sirve comida</t>
+        </is>
+      </c>
+      <c r="G336" s="41" t="inlineStr">
+        <is>
+          <t>12:00-23:00, ya no se sirve comida</t>
+        </is>
+      </c>
+      <c r="H336" s="41" t="n"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B337" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta El Olivar</t>
+        </is>
+      </c>
+      <c r="C337" s="41" t="inlineStr">
+        <is>
+          <t>17-31</t>
+        </is>
+      </c>
+      <c r="D337" s="41" t="inlineStr">
+        <is>
+          <t>Fitness gym</t>
+        </is>
+      </c>
+      <c r="E337" s="41" t="inlineStr">
+        <is>
+          <t>Equipamiento</t>
+        </is>
+      </c>
+      <c r="F337" s="41" t="inlineStr">
+        <is>
+          <t>Solo cinta de correr</t>
+        </is>
+      </c>
+      <c r="G337" s="41" t="inlineStr">
+        <is>
+          <t>Se agregan máquinas, pesas y mat de yoga</t>
+        </is>
+      </c>
+      <c r="H337" s="41" t="n"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B338" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta El Olivar</t>
+        </is>
+      </c>
+      <c r="C338" s="41" t="inlineStr">
+        <is>
+          <t>17-34</t>
+        </is>
+      </c>
+      <c r="D338" s="41" t="inlineStr">
+        <is>
+          <t>Rooftop</t>
+        </is>
+      </c>
+      <c r="E338" s="41" t="inlineStr">
+        <is>
+          <t>Acceso</t>
+        </is>
+      </c>
+      <c r="F338" s="41" t="inlineStr">
+        <is>
+          <t>Clientes y visitantes</t>
+        </is>
+      </c>
+      <c r="G338" s="41" t="inlineStr">
+        <is>
+          <t>Solo clientes del hotel</t>
+        </is>
+      </c>
+      <c r="H338" s="41" t="n"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B339" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta El Olivar</t>
+        </is>
+      </c>
+      <c r="C339" s="41" t="inlineStr">
+        <is>
+          <t>17-43</t>
+        </is>
+      </c>
+      <c r="D339" s="41" t="inlineStr">
+        <is>
+          <t>Floor arrangement</t>
+        </is>
+      </c>
+      <c r="E339" s="41" t="inlineStr">
+        <is>
+          <t>Piso Senior/Presidential Suite</t>
+        </is>
+      </c>
+      <c r="F339" s="41" t="inlineStr">
+        <is>
+          <t>Cualquier piso</t>
+        </is>
+      </c>
+      <c r="G339" s="41" t="inlineStr">
+        <is>
+          <t>Senior Suite pisos 2-3-4; Presidential piso 5</t>
+        </is>
+      </c>
+      <c r="H339" s="41" t="n"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B340" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta El Olivar</t>
+        </is>
+      </c>
+      <c r="C340" s="41" t="inlineStr">
+        <is>
+          <t>18-01</t>
+        </is>
+      </c>
+      <c r="D340" s="41" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E340" s="41" t="inlineStr">
+        <is>
+          <t>Horario Sushi Bar</t>
+        </is>
+      </c>
+      <c r="F340" s="41" t="inlineStr">
+        <is>
+          <t>Lunes a viernes</t>
+        </is>
+      </c>
+      <c r="G340" s="41" t="inlineStr">
+        <is>
+          <t>Lunes a sábado (agrega sábado 13:00-20:00)</t>
+        </is>
+      </c>
+      <c r="H340" s="41" t="n"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B341" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta El Olivar</t>
+        </is>
+      </c>
+      <c r="C341" s="41" t="inlineStr">
+        <is>
+          <t>18-08</t>
+        </is>
+      </c>
+      <c r="D341" s="41" t="inlineStr">
+        <is>
+          <t>Takeaway &amp; delivery</t>
+        </is>
+      </c>
+      <c r="E341" s="41" t="inlineStr">
+        <is>
+          <t>Disponibilidad</t>
+        </is>
+      </c>
+      <c r="F341" s="41" t="inlineStr">
+        <is>
+          <t>Sí, con plataformas</t>
+        </is>
+      </c>
+      <c r="G341" s="41" t="inlineStr">
+        <is>
+          <t>No se realiza delivery</t>
+        </is>
+      </c>
+      <c r="H341" s="41" t="n"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B342" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Osorno</t>
+        </is>
+      </c>
+      <c r="C342" s="41" t="inlineStr">
+        <is>
+          <t>12-02</t>
+        </is>
+      </c>
+      <c r="D342" s="41" t="inlineStr">
+        <is>
+          <t>Breakfast rates</t>
+        </is>
+      </c>
+      <c r="E342" s="41" t="inlineStr">
+        <is>
+          <t>Precio por adulto</t>
+        </is>
+      </c>
+      <c r="F342" s="41" t="inlineStr">
+        <is>
+          <t>15 USD</t>
+        </is>
+      </c>
+      <c r="G342" s="41" t="inlineStr">
+        <is>
+          <t>25 USD</t>
+        </is>
+      </c>
+      <c r="H342" s="41" t="n"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B343" s="41" t="inlineStr">
+        <is>
+          <t>GHL Style Yopal</t>
+        </is>
+      </c>
+      <c r="C343" s="41" t="inlineStr">
+        <is>
+          <t>10-71</t>
+        </is>
+      </c>
+      <c r="D343" s="41" t="inlineStr">
+        <is>
+          <t>Payment method</t>
+        </is>
+      </c>
+      <c r="E343" s="41" t="inlineStr">
+        <is>
+          <t>Efectivo y tarjetas aceptadas</t>
+        </is>
+      </c>
+      <c r="F343" s="41" t="inlineStr">
+        <is>
+          <t>No se aceptaba efectivo; sin Visa</t>
+        </is>
+      </c>
+      <c r="G343" s="41" t="inlineStr">
+        <is>
+          <t>Se acepta efectivo; se agrega Visa</t>
+        </is>
+      </c>
+      <c r="H343" s="41" t="n"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B344" s="41" t="inlineStr">
+        <is>
+          <t>GHL Style Yopal</t>
+        </is>
+      </c>
+      <c r="C344" s="41" t="inlineStr">
+        <is>
+          <t>11-01</t>
+        </is>
+      </c>
+      <c r="D344" s="41" t="inlineStr">
+        <is>
+          <t>Check-in time</t>
+        </is>
+      </c>
+      <c r="E344" s="41" t="inlineStr">
+        <is>
+          <t>Costo early check-in</t>
+        </is>
+      </c>
+      <c r="F344" s="41" t="inlineStr">
+        <is>
+          <t>70.000 COP</t>
+        </is>
+      </c>
+      <c r="G344" s="41" t="inlineStr">
+        <is>
+          <t>70.000 COP + IVA</t>
+        </is>
+      </c>
+      <c r="H344" s="41" t="n"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B345" s="41" t="inlineStr">
+        <is>
+          <t>GHL Style Yopal</t>
+        </is>
+      </c>
+      <c r="C345" s="41" t="inlineStr">
+        <is>
+          <t>11-11</t>
+        </is>
+      </c>
+      <c r="D345" s="41" t="inlineStr">
+        <is>
+          <t>Check-out time</t>
+        </is>
+      </c>
+      <c r="E345" s="41" t="inlineStr">
+        <is>
+          <t>Costo late check-out</t>
+        </is>
+      </c>
+      <c r="F345" s="41" t="inlineStr">
+        <is>
+          <t>70.000 COP</t>
+        </is>
+      </c>
+      <c r="G345" s="41" t="inlineStr">
+        <is>
+          <t>70.000 COP + IVA</t>
+        </is>
+      </c>
+      <c r="H345" s="41" t="n"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B346" s="41" t="inlineStr">
+        <is>
+          <t>GHL Style Yopal</t>
+        </is>
+      </c>
+      <c r="C346" s="41" t="inlineStr">
+        <is>
+          <t>12-01</t>
+        </is>
+      </c>
+      <c r="D346" s="41" t="inlineStr">
+        <is>
+          <t>Breakfast time</t>
+        </is>
+      </c>
+      <c r="E346" s="41" t="inlineStr">
+        <is>
+          <t>Horario y servicio en habitación</t>
+        </is>
+      </c>
+      <c r="F346" s="41" t="inlineStr">
+        <is>
+          <t>06:00-10:00 todos los días; sin servicio en habitación</t>
+        </is>
+      </c>
+      <c r="G346" s="41" t="inlineStr">
+        <is>
+          <t>Lun-Sáb 06:00-10:00, Dom/festivos 06:00-10:30; ahora con servicio en habitación (costo adicional)</t>
+        </is>
+      </c>
+      <c r="H346" s="41" t="n"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B347" s="41" t="inlineStr">
+        <is>
+          <t>GHL Style Yopal</t>
+        </is>
+      </c>
+      <c r="C347" s="41" t="inlineStr">
+        <is>
+          <t>12-02</t>
+        </is>
+      </c>
+      <c r="D347" s="41" t="inlineStr">
+        <is>
+          <t>Breakfast rates</t>
+        </is>
+      </c>
+      <c r="E347" s="41" t="inlineStr">
+        <is>
+          <t>Precio por adulto</t>
+        </is>
+      </c>
+      <c r="F347" s="41" t="inlineStr">
+        <is>
+          <t>48.000 COP</t>
+        </is>
+      </c>
+      <c r="G347" s="41" t="inlineStr">
+        <is>
+          <t>40.000 COP</t>
+        </is>
+      </c>
+      <c r="H347" s="41" t="n"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B348" s="41" t="inlineStr">
+        <is>
+          <t>GHL Style Yopal</t>
+        </is>
+      </c>
+      <c r="C348" s="41" t="inlineStr">
+        <is>
+          <t>16-10</t>
+        </is>
+      </c>
+      <c r="D348" s="41" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="E348" s="41" t="inlineStr">
+        <is>
+          <t>Tasa por mascota</t>
+        </is>
+      </c>
+      <c r="F348" s="41" t="inlineStr">
+        <is>
+          <t>70.000 COP/mascota</t>
+        </is>
+      </c>
+      <c r="G348" s="41" t="inlineStr">
+        <is>
+          <t>70.000 COP + IVA/mascota</t>
+        </is>
+      </c>
+      <c r="H348" s="41" t="n"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B349" s="41" t="inlineStr">
+        <is>
+          <t>GHL Style Yopal</t>
+        </is>
+      </c>
+      <c r="C349" s="41" t="inlineStr">
+        <is>
+          <t>17-15</t>
+        </is>
+      </c>
+      <c r="D349" s="41" t="inlineStr">
+        <is>
+          <t>Spa hours</t>
+        </is>
+      </c>
+      <c r="E349" s="41" t="inlineStr">
+        <is>
+          <t>Disponibilidad de spa</t>
+        </is>
+      </c>
+      <c r="F349" s="41" t="inlineStr">
+        <is>
+          <t>Horario sin límite, todo el año</t>
+        </is>
+      </c>
+      <c r="G349" s="41" t="inlineStr">
+        <is>
+          <t>Ya no se cuenta con spa</t>
+        </is>
+      </c>
+      <c r="H349" s="41" t="n"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B350" s="41" t="inlineStr">
+        <is>
+          <t>Geotel Calama</t>
+        </is>
+      </c>
+      <c r="C350" s="41" t="inlineStr">
+        <is>
+          <t>16-02</t>
+        </is>
+      </c>
+      <c r="D350" s="41" t="inlineStr">
+        <is>
+          <t>Contact staff</t>
+        </is>
+      </c>
+      <c r="E350" s="41" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="F350" s="41" t="inlineStr">
+        <is>
+          <t>⚠ No especificado</t>
+        </is>
+      </c>
+      <c r="G350" s="41" t="inlineStr">
+        <is>
+          <t>+56 931909316 / +56 996795687</t>
+        </is>
+      </c>
+      <c r="H350" s="41" t="n"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B351" s="41" t="inlineStr">
+        <is>
+          <t>Geotel Calama</t>
+        </is>
+      </c>
+      <c r="C351" s="41" t="inlineStr">
+        <is>
+          <t>13-15</t>
+        </is>
+      </c>
+      <c r="D351" s="41" t="inlineStr">
+        <is>
+          <t>Laundry/paraguas</t>
+        </is>
+      </c>
+      <c r="E351" s="41" t="inlineStr">
+        <is>
+          <t>Servicio de paraguas y lavandería</t>
+        </is>
+      </c>
+      <c r="F351" s="41" t="inlineStr">
+        <is>
+          <t>⚠ No especificado</t>
+        </is>
+      </c>
+      <c r="G351" s="41" t="inlineStr">
+        <is>
+          <t>No disponen de paraguas; ofrecen lavandería regular y express (+50% recargo)</t>
+        </is>
+      </c>
+      <c r="H351" s="41" t="n"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B352" s="41" t="inlineStr">
+        <is>
+          <t>Geotel Calama</t>
+        </is>
+      </c>
+      <c r="C352" s="41" t="inlineStr">
+        <is>
+          <t>13-47</t>
+        </is>
+      </c>
+      <c r="D352" s="41" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="E352" s="41" t="inlineStr">
+        <is>
+          <t>Datos requeridos</t>
+        </is>
+      </c>
+      <c r="F352" s="41" t="inlineStr">
+        <is>
+          <t>⚠ No especificado</t>
+        </is>
+      </c>
+      <c r="G352" s="41" t="inlineStr">
+        <is>
+          <t>Enviar Rol Único Tributario por correo o presentarlo en recepción</t>
+        </is>
+      </c>
+      <c r="H352" s="41" t="n"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B353" s="41" t="inlineStr">
+        <is>
+          <t>Geotel Calama</t>
+        </is>
+      </c>
+      <c r="C353" s="41" t="inlineStr">
+        <is>
+          <t>13-48</t>
+        </is>
+      </c>
+      <c r="D353" s="41" t="inlineStr">
+        <is>
+          <t>Currencies</t>
+        </is>
+      </c>
+      <c r="E353" s="41" t="inlineStr">
+        <is>
+          <t>Monedas aceptadas</t>
+        </is>
+      </c>
+      <c r="F353" s="41" t="inlineStr">
+        <is>
+          <t>⚠ No especificado</t>
+        </is>
+      </c>
+      <c r="G353" s="41" t="inlineStr">
+        <is>
+          <t>Aceptan pagos en CLP y USD; facturas en CLP y USD</t>
+        </is>
+      </c>
+      <c r="H353" s="41" t="n"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B354" s="41" t="inlineStr">
+        <is>
+          <t>Geotel Calama</t>
+        </is>
+      </c>
+      <c r="C354" s="41" t="inlineStr">
+        <is>
+          <t>14-01</t>
+        </is>
+      </c>
+      <c r="D354" s="41" t="inlineStr">
+        <is>
+          <t>Accommodation</t>
+        </is>
+      </c>
+      <c r="E354" s="41" t="inlineStr">
+        <is>
+          <t>Ocupación y composición por tipo</t>
+        </is>
+      </c>
+      <c r="F354" s="41" t="inlineStr">
+        <is>
+          <t>⚠ No especificado</t>
+        </is>
+      </c>
+      <c r="G354" s="41" t="inlineStr">
+        <is>
+          <t>Queen/Junior Suite: máx. 2 adultos+1 niño; Suite especial: máx. 4 adultos+2 niños; no fumar ni mascotas</t>
+        </is>
+      </c>
+      <c r="H354" s="41" t="n"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B355" s="41" t="inlineStr">
+        <is>
+          <t>Geotel Calama</t>
+        </is>
+      </c>
+      <c r="C355" s="41" t="inlineStr">
+        <is>
+          <t>14-03</t>
+        </is>
+      </c>
+      <c r="D355" s="41" t="inlineStr">
+        <is>
+          <t>Family accommodation</t>
+        </is>
+      </c>
+      <c r="E355" s="41" t="inlineStr">
+        <is>
+          <t>Ocupación máxima por tipo</t>
+        </is>
+      </c>
+      <c r="F355" s="41" t="inlineStr">
+        <is>
+          <t>⚠ No especificado</t>
+        </is>
+      </c>
+      <c r="G355" s="41" t="inlineStr">
+        <is>
+          <t>Queen y Junior Suite máx. 2 adultos+1 niño; Suite Doble máx. 4 adultos+2 niños</t>
+        </is>
+      </c>
+      <c r="H355" s="41" t="n"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B356" s="41" t="inlineStr">
+        <is>
+          <t>Geotel Calama</t>
+        </is>
+      </c>
+      <c r="C356" s="41" t="inlineStr">
+        <is>
+          <t>14-04</t>
+        </is>
+      </c>
+      <c r="D356" s="41" t="inlineStr">
+        <is>
+          <t>Smoking</t>
+        </is>
+      </c>
+      <c r="E356" s="41" t="inlineStr">
+        <is>
+          <t>Tarifa limpieza por humo</t>
+        </is>
+      </c>
+      <c r="F356" s="41" t="inlineStr">
+        <is>
+          <t>⚠ No especificado</t>
+        </is>
+      </c>
+      <c r="G356" s="41" t="inlineStr">
+        <is>
+          <t>200 USD</t>
+        </is>
+      </c>
+      <c r="H356" s="41" t="n"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B357" s="41" t="inlineStr">
+        <is>
+          <t>Geotel Calama</t>
+        </is>
+      </c>
+      <c r="C357" s="41" t="inlineStr">
+        <is>
+          <t>15-26</t>
+        </is>
+      </c>
+      <c r="D357" s="41" t="inlineStr">
+        <is>
+          <t>Twin beds</t>
+        </is>
+      </c>
+      <c r="E357" s="41" t="inlineStr">
+        <is>
+          <t>Disponibilidad</t>
+        </is>
+      </c>
+      <c r="F357" s="41" t="inlineStr">
+        <is>
+          <t>⚠ No especificado</t>
+        </is>
+      </c>
+      <c r="G357" s="41" t="inlineStr">
+        <is>
+          <t>No ofrecen camas individuales, adicionales ni sofacamas</t>
+        </is>
+      </c>
+      <c r="H357" s="41" t="n"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B358" s="41" t="inlineStr">
+        <is>
+          <t>Geotel Calama</t>
+        </is>
+      </c>
+      <c r="C358" s="41" t="inlineStr">
+        <is>
+          <t>15-48</t>
+        </is>
+      </c>
+      <c r="D358" s="41" t="inlineStr">
+        <is>
+          <t>Electrical facilities</t>
+        </is>
+      </c>
+      <c r="E358" s="41" t="inlineStr">
+        <is>
+          <t>Adaptadores y cargador</t>
+        </is>
+      </c>
+      <c r="F358" s="41" t="inlineStr">
+        <is>
+          <t>⚠ No especificado</t>
+        </is>
+      </c>
+      <c r="G358" s="41" t="inlineStr">
+        <is>
+          <t>Consultar disponibilidad y precio en recepción</t>
+        </is>
+      </c>
+      <c r="H358" s="41" t="n"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B359" s="41" t="inlineStr">
+        <is>
+          <t>Geotel Calama</t>
+        </is>
+      </c>
+      <c r="C359" s="41" t="inlineStr">
+        <is>
+          <t>15-61</t>
+        </is>
+      </c>
+      <c r="D359" s="41" t="inlineStr">
+        <is>
+          <t>Balcony &amp; windows</t>
+        </is>
+      </c>
+      <c r="E359" s="41" t="inlineStr">
+        <is>
+          <t>Disponibilidad de balcón</t>
+        </is>
+      </c>
+      <c r="F359" s="41" t="inlineStr">
+        <is>
+          <t>⚠ No especificado</t>
+        </is>
+      </c>
+      <c r="G359" s="41" t="inlineStr">
+        <is>
+          <t>Junior Suite y Suite Doble cuentan con balcones pequeños</t>
+        </is>
+      </c>
+      <c r="H359" s="41" t="n"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B360" s="41" t="inlineStr">
+        <is>
+          <t>Geotel Calama</t>
+        </is>
+      </c>
+      <c r="C360" s="41" t="inlineStr">
+        <is>
+          <t>17-15</t>
+        </is>
+      </c>
+      <c r="D360" s="41" t="inlineStr">
+        <is>
+          <t>Spa hours</t>
+        </is>
+      </c>
+      <c r="E360" s="41" t="inlineStr">
+        <is>
+          <t>Disponibilidad de spa</t>
+        </is>
+      </c>
+      <c r="F360" s="41" t="inlineStr">
+        <is>
+          <t>⚠ No especificado</t>
+        </is>
+      </c>
+      <c r="G360" s="41" t="inlineStr">
+        <is>
+          <t>No cuentan con spa</t>
+        </is>
+      </c>
+      <c r="H360" s="41" t="n"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B361" s="41" t="inlineStr">
+        <is>
+          <t>Geotel Calama</t>
+        </is>
+      </c>
+      <c r="C361" s="41" t="inlineStr">
+        <is>
+          <t>17-31</t>
+        </is>
+      </c>
+      <c r="D361" s="41" t="inlineStr">
+        <is>
+          <t>Fitness gym</t>
+        </is>
+      </c>
+      <c r="E361" s="41" t="inlineStr">
+        <is>
+          <t>Horario y acceso</t>
+        </is>
+      </c>
+      <c r="F361" s="41" t="inlineStr">
+        <is>
+          <t>⚠ No especificado</t>
+        </is>
+      </c>
+      <c r="G361" s="41" t="inlineStr">
+        <is>
+          <t>Lun-Dom 05:00-23:00, código de acceso en recepción</t>
+        </is>
+      </c>
+      <c r="H361" s="41" t="n"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B362" s="41" t="inlineStr">
+        <is>
+          <t>Geotel Calama</t>
+        </is>
+      </c>
+      <c r="C362" s="41" t="inlineStr">
+        <is>
+          <t>17-44</t>
+        </is>
+      </c>
+      <c r="D362" s="41" t="inlineStr">
+        <is>
+          <t>Disabled guest</t>
+        </is>
+      </c>
+      <c r="E362" s="41" t="inlineStr">
+        <is>
+          <t>Habitación adaptada</t>
+        </is>
+      </c>
+      <c r="F362" s="41" t="inlineStr">
+        <is>
+          <t>⚠ No especificado</t>
+        </is>
+      </c>
+      <c r="G362" s="41" t="inlineStr">
+        <is>
+          <t>Habitación con 2 camas individuales y baño adaptado</t>
+        </is>
+      </c>
+      <c r="H362" s="41" t="n"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B363" s="41" t="inlineStr">
+        <is>
+          <t>Geotel Calama</t>
+        </is>
+      </c>
+      <c r="C363" s="41" t="inlineStr">
+        <is>
+          <t>18-01</t>
+        </is>
+      </c>
+      <c r="D363" s="41" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E363" s="41" t="inlineStr">
+        <is>
+          <t>Nombre y capacidad</t>
+        </is>
+      </c>
+      <c r="F363" s="41" t="inlineStr">
+        <is>
+          <t>⚠ No especificado</t>
+        </is>
+      </c>
+      <c r="G363" s="41" t="inlineStr">
+        <is>
+          <t>Restaurante "Entre piedras"; ofrece tronas/sillas para niños</t>
+        </is>
+      </c>
+      <c r="H363" s="41" t="n"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B364" s="41" t="inlineStr">
+        <is>
+          <t>GHL Style Bogotá Occidente</t>
+        </is>
+      </c>
+      <c r="C364" s="41" t="inlineStr">
+        <is>
+          <t>20-01</t>
+        </is>
+      </c>
+      <c r="D364" s="41" t="inlineStr">
+        <is>
+          <t>Business meetings</t>
+        </is>
+      </c>
+      <c r="E364" s="41" t="inlineStr">
+        <is>
+          <t>Correo de contacto eventos</t>
+        </is>
+      </c>
+      <c r="F364" s="41" t="inlineStr">
+        <is>
+          <t>sandra.castillo@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="G364" s="41" t="inlineStr">
+        <is>
+          <t>eventos.bogotaoccidente@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="H364" s="41" t="n"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B365" s="41" t="inlineStr">
+        <is>
+          <t>GHL Style Bogotá Occidente</t>
+        </is>
+      </c>
+      <c r="C365" s="41" t="inlineStr">
+        <is>
+          <t>12-02</t>
+        </is>
+      </c>
+      <c r="D365" s="41" t="inlineStr">
+        <is>
+          <t>Breakfast rates</t>
+        </is>
+      </c>
+      <c r="E365" s="41" t="inlineStr">
+        <is>
+          <t>Redacción del beneficio</t>
+        </is>
+      </c>
+      <c r="F365" s="41" t="inlineStr">
+        <is>
+          <t>"Incluido en la tarifa"</t>
+        </is>
+      </c>
+      <c r="G365" s="41" t="inlineStr">
+        <is>
+          <t>"Cortesía para huéspedes" (no reembolsable)</t>
+        </is>
+      </c>
+      <c r="H365" s="41" t="n"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B366" s="41" t="inlineStr">
+        <is>
+          <t>GHL Style Bogotá Occidente</t>
+        </is>
+      </c>
+      <c r="C366" s="41" t="inlineStr">
+        <is>
+          <t>13-51</t>
+        </is>
+      </c>
+      <c r="D366" s="41" t="inlineStr">
+        <is>
+          <t>Private transfer</t>
+        </is>
+      </c>
+      <c r="E366" s="41" t="inlineStr">
+        <is>
+          <t>Tarifas aeropuerto y espera</t>
+        </is>
+      </c>
+      <c r="F366" s="41" t="inlineStr">
+        <is>
+          <t>$95.000/$100.000; espera $30.000</t>
+        </is>
+      </c>
+      <c r="G366" s="41" t="inlineStr">
+        <is>
+          <t>$102.000/$107.000; espera $33.000</t>
+        </is>
+      </c>
+      <c r="H366" s="41" t="n"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B367" s="41" t="inlineStr">
+        <is>
+          <t>GHL Hotel Grand Barranquilla</t>
+        </is>
+      </c>
+      <c r="C367" s="41" t="inlineStr">
+        <is>
+          <t>10-51</t>
+        </is>
+      </c>
+      <c r="D367" s="41" t="inlineStr">
+        <is>
+          <t>City tax, fees &amp; VAT</t>
+        </is>
+      </c>
+      <c r="E367" s="41" t="inlineStr">
+        <is>
+          <t>Impuestos aplicables</t>
+        </is>
+      </c>
+      <c r="F367" s="41" t="inlineStr">
+        <is>
+          <t>No hay impuesto municipal</t>
+        </is>
+      </c>
+      <c r="G367" s="41" t="inlineStr">
+        <is>
+          <t>Se cobran IVA e IPC (exento para extranjeros que califiquen)</t>
+        </is>
+      </c>
+      <c r="H367" s="41" t="n"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B368" s="41" t="inlineStr">
+        <is>
+          <t>GHL Hotel Grand Barranquilla</t>
+        </is>
+      </c>
+      <c r="C368" s="41" t="inlineStr">
+        <is>
+          <t>10-71</t>
+        </is>
+      </c>
+      <c r="D368" s="41" t="inlineStr">
+        <is>
+          <t>Payment method</t>
+        </is>
+      </c>
+      <c r="E368" s="41" t="inlineStr">
+        <is>
+          <t>Métodos de pago aceptados</t>
+        </is>
+      </c>
+      <c r="F368" s="41" t="inlineStr">
+        <is>
+          <t>Incluía Paypal</t>
+        </is>
+      </c>
+      <c r="G368" s="41" t="inlineStr">
+        <is>
+          <t>Se retira Paypal de la lista</t>
+        </is>
+      </c>
+      <c r="H368" s="41" t="n"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B369" s="41" t="inlineStr">
+        <is>
+          <t>GHL Hotel Grand Barranquilla</t>
+        </is>
+      </c>
+      <c r="C369" s="41" t="inlineStr">
+        <is>
+          <t>13-21</t>
+        </is>
+      </c>
+      <c r="D369" s="41" t="inlineStr">
+        <is>
+          <t>Kids</t>
+        </is>
+      </c>
+      <c r="E369" s="41" t="inlineStr">
+        <is>
+          <t>Rango de edad tarifa infantil</t>
+        </is>
+      </c>
+      <c r="F369" s="41" t="inlineStr">
+        <is>
+          <t>12 a 18 años</t>
+        </is>
+      </c>
+      <c r="G369" s="41" t="inlineStr">
+        <is>
+          <t>12 a 17 años</t>
+        </is>
+      </c>
+      <c r="H369" s="41" t="n"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B370" s="41" t="inlineStr">
+        <is>
+          <t>GHL Hotel Grand Barranquilla</t>
+        </is>
+      </c>
+      <c r="C370" s="41" t="inlineStr">
+        <is>
+          <t>13-51</t>
+        </is>
+      </c>
+      <c r="D370" s="41" t="inlineStr">
+        <is>
+          <t>Private transfer</t>
+        </is>
+      </c>
+      <c r="E370" s="41" t="inlineStr">
+        <is>
+          <t>Tarifa en USD</t>
+        </is>
+      </c>
+      <c r="F370" s="41" t="inlineStr">
+        <is>
+          <t>15 USD (ida y vuelta)</t>
+        </is>
+      </c>
+      <c r="G370" s="41" t="inlineStr">
+        <is>
+          <t>25 USD (ida y vuelta)</t>
+        </is>
+      </c>
+      <c r="H370" s="41" t="n"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B371" s="41" t="inlineStr">
+        <is>
+          <t>GHL Hotel Grand Barranquilla</t>
+        </is>
+      </c>
+      <c r="C371" s="41" t="inlineStr">
+        <is>
+          <t>13-53</t>
+        </is>
+      </c>
+      <c r="D371" s="41" t="inlineStr">
+        <is>
+          <t>Taxi</t>
+        </is>
+      </c>
+      <c r="E371" s="41" t="inlineStr">
+        <is>
+          <t>Precios de referencia</t>
+        </is>
+      </c>
+      <c r="F371" s="41" t="inlineStr">
+        <is>
+          <t>Estadio 30.000, Malecón 20.000, Ventana 1.000 COP</t>
+        </is>
+      </c>
+      <c r="G371" s="41" t="inlineStr">
+        <is>
+          <t>Estadio 35.000, Malecón 25.000, Ventana 15.000 COP</t>
+        </is>
+      </c>
+      <c r="H371" s="41" t="n"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B372" s="41" t="inlineStr">
+        <is>
+          <t>GHL Hotel Grand Barranquilla</t>
+        </is>
+      </c>
+      <c r="C372" s="41" t="inlineStr">
+        <is>
+          <t>14-04</t>
+        </is>
+      </c>
+      <c r="D372" s="41" t="inlineStr">
+        <is>
+          <t>Smoking</t>
+        </is>
+      </c>
+      <c r="E372" s="41" t="inlineStr">
+        <is>
+          <t>Tarifa limpieza por humo</t>
+        </is>
+      </c>
+      <c r="F372" s="41" t="inlineStr">
+        <is>
+          <t>35.000 COP</t>
+        </is>
+      </c>
+      <c r="G372" s="41" t="inlineStr">
+        <is>
+          <t>100 USD</t>
+        </is>
+      </c>
+      <c r="H372" s="41" t="n"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B373" s="41" t="inlineStr">
+        <is>
+          <t>GHL Hotel Grand Barranquilla</t>
+        </is>
+      </c>
+      <c r="C373" s="41" t="inlineStr">
+        <is>
+          <t>17-01</t>
+        </is>
+      </c>
+      <c r="D373" s="41" t="inlineStr">
+        <is>
+          <t>Bar</t>
+        </is>
+      </c>
+      <c r="E373" s="41" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="F373" s="41" t="inlineStr">
+        <is>
+          <t>Texto genérico sin información</t>
+        </is>
+      </c>
+      <c r="G373" s="41" t="inlineStr">
+        <is>
+          <t>Lobby Bar en el primer piso con bebidas y alimentos</t>
+        </is>
+      </c>
+      <c r="H373" s="41" t="n"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B374" s="41" t="inlineStr">
+        <is>
+          <t>GHL Hotel Grand Barranquilla</t>
+        </is>
+      </c>
+      <c r="C374" s="41" t="inlineStr">
+        <is>
+          <t>17-15</t>
+        </is>
+      </c>
+      <c r="D374" s="41" t="inlineStr">
+        <is>
+          <t>Spa hours</t>
+        </is>
+      </c>
+      <c r="E374" s="41" t="inlineStr">
+        <is>
+          <t>Disponibilidad de spa</t>
+        </is>
+      </c>
+      <c r="F374" s="41" t="inlineStr">
+        <is>
+          <t>Listaba horario de spa</t>
+        </is>
+      </c>
+      <c r="G374" s="41" t="inlineStr">
+        <is>
+          <t>No cuentan con spa</t>
+        </is>
+      </c>
+      <c r="H374" s="41" t="n"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B375" s="41" t="inlineStr">
+        <is>
+          <t>GHL Hotel Grand Barranquilla</t>
+        </is>
+      </c>
+      <c r="C375" s="41" t="inlineStr">
+        <is>
+          <t>17-31</t>
+        </is>
+      </c>
+      <c r="D375" s="41" t="inlineStr">
+        <is>
+          <t>Fitness gym</t>
+        </is>
+      </c>
+      <c r="E375" s="41" t="inlineStr">
+        <is>
+          <t>Ubicación</t>
+        </is>
+      </c>
+      <c r="F375" s="41" t="inlineStr">
+        <is>
+          <t>Piso 123 (error tipográfico)</t>
+        </is>
+      </c>
+      <c r="G375" s="41" t="inlineStr">
+        <is>
+          <t>Piso 13</t>
+        </is>
+      </c>
+      <c r="H375" s="41" t="n"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B376" s="41" t="inlineStr">
+        <is>
+          <t>GHL Hotel Grand Barranquilla</t>
+        </is>
+      </c>
+      <c r="C376" s="41" t="inlineStr">
+        <is>
+          <t>17-34</t>
+        </is>
+      </c>
+      <c r="D376" s="41" t="inlineStr">
+        <is>
+          <t>Rooftop</t>
+        </is>
+      </c>
+      <c r="E376" s="41" t="inlineStr">
+        <is>
+          <t>Disponibilidad</t>
+        </is>
+      </c>
+      <c r="F376" s="41" t="inlineStr">
+        <is>
+          <t>"No tenemos terraza"</t>
+        </is>
+      </c>
+      <c r="G376" s="41" t="inlineStr">
+        <is>
+          <t>Bar Terraza en el piso 13 con bebidas y alimentos</t>
+        </is>
+      </c>
+      <c r="H376" s="41" t="n"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B377" s="41" t="inlineStr">
+        <is>
+          <t>GHL Hotel Grand Barranquilla</t>
+        </is>
+      </c>
+      <c r="C377" s="41" t="inlineStr">
+        <is>
+          <t>17-61</t>
+        </is>
+      </c>
+      <c r="D377" s="41" t="inlineStr">
+        <is>
+          <t>Swimming pool</t>
+        </is>
+      </c>
+      <c r="E377" s="41" t="inlineStr">
+        <is>
+          <t>Precio público por día</t>
+        </is>
+      </c>
+      <c r="F377" s="41" t="inlineStr">
+        <is>
+          <t>80.000 COP/día</t>
+        </is>
+      </c>
+      <c r="G377" s="41" t="inlineStr">
+        <is>
+          <t>150.000 COP/día</t>
+        </is>
+      </c>
+      <c r="H377" s="41" t="n"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B378" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C378" s="41" t="inlineStr">
+        <is>
+          <t>12-04</t>
+        </is>
+      </c>
+      <c r="D378" s="41" t="inlineStr">
+        <is>
+          <t>Breakfast reservation</t>
+        </is>
+      </c>
+      <c r="E378" s="41" t="inlineStr">
+        <is>
+          <t>Correo para reservar desayuno</t>
+        </is>
+      </c>
+      <c r="F378" s="41" t="inlineStr">
+        <is>
+          <t>reservas.sonestaarequipa@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="G378" s="41" t="inlineStr">
+        <is>
+          <t>restaurante.sonestaarequipa@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="H378" s="41" t="n"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B379" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C379" s="41" t="inlineStr">
+        <is>
+          <t>13-32</t>
+        </is>
+      </c>
+      <c r="D379" s="41" t="inlineStr">
+        <is>
+          <t>Medical services</t>
+        </is>
+      </c>
+      <c r="E379" s="41" t="inlineStr">
+        <is>
+          <t>Números de emergencia</t>
+        </is>
+      </c>
+      <c r="F379" s="41" t="inlineStr">
+        <is>
+          <t>Policía 911, Fuego 911, Ambulancia 911</t>
+        </is>
+      </c>
+      <c r="G379" s="41" t="inlineStr">
+        <is>
+          <t>Policía 105, Fuego 116, Ambulancia 106</t>
+        </is>
+      </c>
+      <c r="H379" s="41" t="n"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B380" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C380" s="41" t="inlineStr">
+        <is>
+          <t>13-48</t>
+        </is>
+      </c>
+      <c r="D380" s="41" t="inlineStr">
+        <is>
+          <t>Currencies</t>
+        </is>
+      </c>
+      <c r="E380" s="41" t="inlineStr">
+        <is>
+          <t>Pagos en propiedad</t>
+        </is>
+      </c>
+      <c r="F380" s="41" t="inlineStr">
+        <is>
+          <t>Solo PEN</t>
+        </is>
+      </c>
+      <c r="G380" s="41" t="inlineStr">
+        <is>
+          <t>PEN y USD</t>
+        </is>
+      </c>
+      <c r="H380" s="41" t="n"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B381" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C381" s="41" t="inlineStr">
+        <is>
+          <t>13-52</t>
+        </is>
+      </c>
+      <c r="D381" s="41" t="inlineStr">
+        <is>
+          <t>Private transfer reservation</t>
+        </is>
+      </c>
+      <c r="E381" s="41" t="inlineStr">
+        <is>
+          <t>Información requerida</t>
+        </is>
+      </c>
+      <c r="F381" s="41" t="inlineStr">
+        <is>
+          <t>Incluía número de vuelo/tren y estación</t>
+        </is>
+      </c>
+      <c r="G381" s="41" t="inlineStr">
+        <is>
+          <t>Se retira estación de tren/aeropuerto</t>
+        </is>
+      </c>
+      <c r="H381" s="41" t="n"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B382" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C382" s="41" t="inlineStr">
+        <is>
+          <t>14-01</t>
+        </is>
+      </c>
+      <c r="D382" s="41" t="inlineStr">
+        <is>
+          <t>Accommodation</t>
+        </is>
+      </c>
+      <c r="E382" s="41" t="inlineStr">
+        <is>
+          <t>Superficie de habitaciones (m²)</t>
+        </is>
+      </c>
+      <c r="F382" s="41" t="inlineStr">
+        <is>
+          <t>28 m² (King/Twin/Ejecutiva)</t>
+        </is>
+      </c>
+      <c r="G382" s="41" t="inlineStr">
+        <is>
+          <t>34 m²; Ejecutiva King pasa a llamarse Superior King</t>
+        </is>
+      </c>
+      <c r="H382" s="41" t="n"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B383" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C383" s="41" t="inlineStr">
+        <is>
+          <t>14-04</t>
+        </is>
+      </c>
+      <c r="D383" s="41" t="inlineStr">
+        <is>
+          <t>Smoking</t>
+        </is>
+      </c>
+      <c r="E383" s="41" t="inlineStr">
+        <is>
+          <t>Detectores y tarifa limpieza</t>
+        </is>
+      </c>
+      <c r="F383" s="41" t="inlineStr">
+        <is>
+          <t>Sin detectores; tarifa 0 PEN</t>
+        </is>
+      </c>
+      <c r="G383" s="41" t="inlineStr">
+        <is>
+          <t>Con detectores; tarifa USD 200</t>
+        </is>
+      </c>
+      <c r="H383" s="41" t="n"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B384" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C384" s="41" t="inlineStr">
+        <is>
+          <t>15-06</t>
+        </is>
+      </c>
+      <c r="D384" s="41" t="inlineStr">
+        <is>
+          <t>Bathroom equipment</t>
+        </is>
+      </c>
+      <c r="E384" s="41" t="inlineStr">
+        <is>
+          <t>Amenidades gratuitas a petición</t>
+        </is>
+      </c>
+      <c r="F384" s="41" t="inlineStr">
+        <is>
+          <t>Pantuflas, pasta dientes, kit afeitar</t>
+        </is>
+      </c>
+      <c r="G384" s="41" t="inlineStr">
+        <is>
+          <t>Pantuflas, vanity kit, kit dental, kit afeitar, peine</t>
+        </is>
+      </c>
+      <c r="H384" s="41" t="n"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B385" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C385" s="41" t="inlineStr">
+        <is>
+          <t>15-09</t>
+        </is>
+      </c>
+      <c r="D385" s="41" t="inlineStr">
+        <is>
+          <t>Shower/bathtub</t>
+        </is>
+      </c>
+      <c r="E385" s="41" t="inlineStr">
+        <is>
+          <t>Nombres de categorías</t>
+        </is>
+      </c>
+      <c r="F385" s="41" t="inlineStr">
+        <is>
+          <t>Ejecutiva King</t>
+        </is>
+      </c>
+      <c r="G385" s="41" t="inlineStr">
+        <is>
+          <t>Superior King</t>
+        </is>
+      </c>
+      <c r="H385" s="41" t="n"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B386" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C386" s="41" t="inlineStr">
+        <is>
+          <t>15-21</t>
+        </is>
+      </c>
+      <c r="D386" s="41" t="inlineStr">
+        <is>
+          <t>Bedding</t>
+        </is>
+      </c>
+      <c r="E386" s="41" t="inlineStr">
+        <is>
+          <t>Nombres de categorías</t>
+        </is>
+      </c>
+      <c r="F386" s="41" t="inlineStr">
+        <is>
+          <t>Ejecutiva King</t>
+        </is>
+      </c>
+      <c r="G386" s="41" t="inlineStr">
+        <is>
+          <t>Superior King</t>
+        </is>
+      </c>
+      <c r="H386" s="41" t="n"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B387" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C387" s="41" t="inlineStr">
+        <is>
+          <t>16-06</t>
+        </is>
+      </c>
+      <c r="D387" s="41" t="inlineStr">
+        <is>
+          <t>Jobs &amp; internships</t>
+        </is>
+      </c>
+      <c r="E387" s="41" t="inlineStr">
+        <is>
+          <t>Correo y teléfono RR.HH.</t>
+        </is>
+      </c>
+      <c r="F387" s="41" t="inlineStr">
+        <is>
+          <t>contactenos@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="G387" s="41" t="inlineStr">
+        <is>
+          <t>laydy.pauca@ghlhoteles.com / +054 308 777</t>
+        </is>
+      </c>
+      <c r="H387" s="41" t="n"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B388" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C388" s="41" t="inlineStr">
+        <is>
+          <t>16-25</t>
+        </is>
+      </c>
+      <c r="D388" s="41" t="inlineStr">
+        <is>
+          <t>Tips policy</t>
+        </is>
+      </c>
+      <c r="E388" s="41" t="inlineStr">
+        <is>
+          <t>Redacción de la política</t>
+        </is>
+      </c>
+      <c r="F388" s="41" t="inlineStr">
+        <is>
+          <t>Incluía "es costumbre dejar propina"</t>
+        </is>
+      </c>
+      <c r="G388" s="41" t="inlineStr">
+        <is>
+          <t>Se retira esa línea</t>
+        </is>
+      </c>
+      <c r="H388" s="41" t="n"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B389" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C389" s="41" t="inlineStr">
+        <is>
+          <t>17-31</t>
+        </is>
+      </c>
+      <c r="D389" s="41" t="inlineStr">
+        <is>
+          <t>Fitness gym</t>
+        </is>
+      </c>
+      <c r="E389" s="41" t="inlineStr">
+        <is>
+          <t>Equipamiento</t>
+        </is>
+      </c>
+      <c r="F389" s="41" t="inlineStr">
+        <is>
+          <t>Incluía bicicleta estática</t>
+        </is>
+      </c>
+      <c r="G389" s="41" t="inlineStr">
+        <is>
+          <t>Se retira bicicleta estática</t>
+        </is>
+      </c>
+      <c r="H389" s="41" t="n"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B390" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C390" s="41" t="inlineStr">
+        <is>
+          <t>17-41</t>
+        </is>
+      </c>
+      <c r="D390" s="41" t="inlineStr">
+        <is>
+          <t>Heating &amp; cooling</t>
+        </is>
+      </c>
+      <c r="E390" s="41" t="inlineStr">
+        <is>
+          <t>Nombre de equipo y tipo A/A</t>
+        </is>
+      </c>
+      <c r="F390" s="41" t="inlineStr">
+        <is>
+          <t>"Radiador"; tipo Reversible (Caliente/Frío)</t>
+        </is>
+      </c>
+      <c r="G390" s="41" t="inlineStr">
+        <is>
+          <t>"Calefactor"; tipo Frío únicamente</t>
+        </is>
+      </c>
+      <c r="H390" s="41" t="n"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B391" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Arequipa</t>
+        </is>
+      </c>
+      <c r="C391" s="41" t="inlineStr">
+        <is>
+          <t>19-03</t>
+        </is>
+      </c>
+      <c r="D391" s="41" t="inlineStr">
+        <is>
+          <t>City center</t>
+        </is>
+      </c>
+      <c r="E391" s="41" t="inlineStr">
+        <is>
+          <t>Redacción de indicaciones</t>
+        </is>
+      </c>
+      <c r="F391" s="41" t="inlineStr">
+        <is>
+          <t>Incluía tiempo a pie</t>
+        </is>
+      </c>
+      <c r="G391" s="41" t="inlineStr">
+        <is>
+          <t>Se simplifica, solo enlace de indicaciones</t>
+        </is>
+      </c>
+      <c r="H391" s="41" t="n"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B392" s="41" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="C392" s="41" t="inlineStr">
+        <is>
+          <t>12-01</t>
+        </is>
+      </c>
+      <c r="D392" s="41" t="inlineStr">
+        <is>
+          <t>Breakfast time</t>
+        </is>
+      </c>
+      <c r="E392" s="41" t="inlineStr">
+        <is>
+          <t>Nombre del restaurante</t>
+        </is>
+      </c>
+      <c r="F392" s="41" t="inlineStr">
+        <is>
+          <t>Restaurante Corozo &amp; Timbal</t>
+        </is>
+      </c>
+      <c r="G392" s="41" t="inlineStr">
+        <is>
+          <t>Restaurante Úrsula</t>
+        </is>
+      </c>
+      <c r="H392" s="41" t="n"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B393" s="41" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="C393" s="41" t="inlineStr">
+        <is>
+          <t>17-31</t>
+        </is>
+      </c>
+      <c r="D393" s="41" t="inlineStr">
+        <is>
+          <t>Fitness gym</t>
+        </is>
+      </c>
+      <c r="E393" s="41" t="inlineStr">
+        <is>
+          <t>Equipamiento</t>
+        </is>
+      </c>
+      <c r="F393" s="41" t="inlineStr">
+        <is>
+          <t>Incluía máquina de remo</t>
+        </is>
+      </c>
+      <c r="G393" s="41" t="inlineStr">
+        <is>
+          <t>Se retira máquina de remo</t>
+        </is>
+      </c>
+      <c r="H393" s="41" t="n"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B394" s="41" t="inlineStr">
+        <is>
+          <t>Hotel Tequendama Bogotá</t>
+        </is>
+      </c>
+      <c r="C394" s="41" t="inlineStr">
+        <is>
+          <t>13-06</t>
+        </is>
+      </c>
+      <c r="D394" s="41" t="inlineStr">
+        <is>
+          <t>Room service</t>
+        </is>
+      </c>
+      <c r="E394" s="41" t="inlineStr">
+        <is>
+          <t>Código de marcado</t>
+        </is>
+      </c>
+      <c r="F394" s="41" t="inlineStr">
+        <is>
+          <t>Marcar 2</t>
+        </is>
+      </c>
+      <c r="G394" s="41" t="inlineStr">
+        <is>
+          <t>Marcar *2</t>
+        </is>
+      </c>
+      <c r="H394" s="41" t="n"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B395" s="41" t="inlineStr">
+        <is>
+          <t>Hotel Tequendama Bogotá</t>
+        </is>
+      </c>
+      <c r="C395" s="41" t="inlineStr">
+        <is>
+          <t>18-01</t>
+        </is>
+      </c>
+      <c r="D395" s="41" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E395" s="41" t="inlineStr">
+        <is>
+          <t>Días de apertura Café Vienes</t>
+        </is>
+      </c>
+      <c r="F395" s="41" t="inlineStr">
+        <is>
+          <t>Abierto 7/7</t>
+        </is>
+      </c>
+      <c r="G395" s="41" t="inlineStr">
+        <is>
+          <t>Abierto de lunes a viernes</t>
+        </is>
+      </c>
+      <c r="H395" s="41" t="n"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B396" s="41" t="inlineStr">
+        <is>
+          <t>GHL Relax Club Hotel el Puente</t>
+        </is>
+      </c>
+      <c r="C396" s="41" t="inlineStr">
+        <is>
+          <t>10-13</t>
+        </is>
+      </c>
+      <c r="D396" s="41" t="inlineStr">
+        <is>
+          <t>Opening, closing &amp; renovation</t>
+        </is>
+      </c>
+      <c r="E396" s="41" t="inlineStr">
+        <is>
+          <t>Fecha fin remodelación</t>
+        </is>
+      </c>
+      <c r="F396" s="41" t="inlineStr">
+        <is>
+          <t>30 de agosto de 2026</t>
+        </is>
+      </c>
+      <c r="G396" s="41" t="inlineStr">
+        <is>
+          <t>30 de septiembre de 2026</t>
+        </is>
+      </c>
+      <c r="H396" s="41" t="n"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B397" s="41" t="inlineStr">
+        <is>
+          <t>GHL Relax Club Hotel el Puente</t>
+        </is>
+      </c>
+      <c r="C397" s="41" t="inlineStr">
+        <is>
+          <t>10-42</t>
+        </is>
+      </c>
+      <c r="D397" s="41" t="inlineStr">
+        <is>
+          <t>Day use reservation</t>
+        </is>
+      </c>
+      <c r="E397" s="41" t="inlineStr">
+        <is>
+          <t>Fecha fin remodelación</t>
+        </is>
+      </c>
+      <c r="F397" s="41" t="inlineStr">
+        <is>
+          <t>31 de agosto</t>
+        </is>
+      </c>
+      <c r="G397" s="41" t="inlineStr">
+        <is>
+          <t>30 de septiembre</t>
+        </is>
+      </c>
+      <c r="H397" s="41" t="n"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B398" s="41" t="inlineStr">
+        <is>
+          <t>GHL Relax Club Hotel el Puente</t>
+        </is>
+      </c>
+      <c r="C398" s="41" t="inlineStr">
+        <is>
+          <t>15-23</t>
+        </is>
+      </c>
+      <c r="D398" s="41" t="inlineStr">
+        <is>
+          <t>Extra bed</t>
+        </is>
+      </c>
+      <c r="E398" s="41" t="inlineStr">
+        <is>
+          <t>Precio por noche</t>
+        </is>
+      </c>
+      <c r="F398" s="41" t="inlineStr">
+        <is>
+          <t>80.000 COP</t>
+        </is>
+      </c>
+      <c r="G398" s="41" t="inlineStr">
+        <is>
+          <t>90.000 COP</t>
+        </is>
+      </c>
+      <c r="H398" s="41" t="n"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B399" s="41" t="inlineStr">
+        <is>
+          <t>GHL Relax Club Hotel el Puente</t>
+        </is>
+      </c>
+      <c r="C399" s="41" t="inlineStr">
+        <is>
+          <t>15-62</t>
+        </is>
+      </c>
+      <c r="D399" s="41" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="E399" s="41" t="inlineStr">
+        <is>
+          <t>Redacción de la vista</t>
+        </is>
+      </c>
+      <c r="F399" s="41" t="inlineStr">
+        <is>
+          <t>Depende de la ubicación asignada</t>
+        </is>
+      </c>
+      <c r="G399" s="41" t="inlineStr">
+        <is>
+          <t>Vista interna, depende de la ubicación asignada</t>
+        </is>
+      </c>
+      <c r="H399" s="41" t="n"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B400" s="41" t="inlineStr">
+        <is>
+          <t>GHL Relax Club Hotel el Puente</t>
+        </is>
+      </c>
+      <c r="C400" s="41" t="inlineStr">
+        <is>
+          <t>15-81</t>
+        </is>
+      </c>
+      <c r="D400" s="41" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="E400" s="41" t="inlineStr">
+        <is>
+          <t>Guía de canales</t>
+        </is>
+      </c>
+      <c r="F400" s="41" t="inlineStr">
+        <is>
+          <t>Disponible en app GHL Plus</t>
+        </is>
+      </c>
+      <c r="G400" s="41" t="inlineStr">
+        <is>
+          <t>Se retira mención de la app</t>
+        </is>
+      </c>
+      <c r="H400" s="41" t="n"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B401" s="41" t="inlineStr">
+        <is>
+          <t>GHL Relax Club Hotel el Puente</t>
+        </is>
+      </c>
+      <c r="C401" s="41" t="inlineStr">
+        <is>
+          <t>16-10</t>
+        </is>
+      </c>
+      <c r="D401" s="41" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="E401" s="41" t="inlineStr">
+        <is>
+          <t>Máximo de mascotas y correa</t>
+        </is>
+      </c>
+      <c r="F401" s="41" t="inlineStr">
+        <is>
+          <t>Máx. 2 mascotas por habitación</t>
+        </is>
+      </c>
+      <c r="G401" s="41" t="inlineStr">
+        <is>
+          <t>Máx. 1 mascota; se exige correa</t>
+        </is>
+      </c>
+      <c r="H401" s="41" t="n"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B402" s="41" t="inlineStr">
+        <is>
+          <t>GHL Relax Club Hotel el Puente</t>
+        </is>
+      </c>
+      <c r="C402" s="41" t="inlineStr">
+        <is>
+          <t>17-11</t>
+        </is>
+      </c>
+      <c r="D402" s="41" t="inlineStr">
+        <is>
+          <t>Spa reservation</t>
+        </is>
+      </c>
+      <c r="E402" s="41" t="inlineStr">
+        <is>
+          <t>Método de contacto</t>
+        </is>
+      </c>
+      <c r="F402" s="41" t="inlineStr">
+        <is>
+          <t>Reservar por correo</t>
+        </is>
+      </c>
+      <c r="G402" s="41" t="inlineStr">
+        <is>
+          <t>Teléfono/WhatsApp +57 3138725411</t>
+        </is>
+      </c>
+      <c r="H402" s="41" t="n"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B403" s="41" t="inlineStr">
+        <is>
+          <t>GHL Relax Club Hotel el Puente</t>
+        </is>
+      </c>
+      <c r="C403" s="41" t="inlineStr">
+        <is>
+          <t>17-41</t>
+        </is>
+      </c>
+      <c r="D403" s="41" t="inlineStr">
+        <is>
+          <t>Heating &amp; cooling</t>
+        </is>
+      </c>
+      <c r="E403" s="41" t="inlineStr">
+        <is>
+          <t>Sistema de climatización</t>
+        </is>
+      </c>
+      <c r="F403" s="41" t="inlineStr">
+        <is>
+          <t>Sistemas de regulación de temperatura</t>
+        </is>
+      </c>
+      <c r="G403" s="41" t="inlineStr">
+        <is>
+          <t>Ambiente con temperatura natural de la región (sin A/A)</t>
+        </is>
+      </c>
+      <c r="H403" s="41" t="n"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B404" s="41" t="inlineStr">
+        <is>
+          <t>GHL Relax Club Hotel el Puente</t>
+        </is>
+      </c>
+      <c r="C404" s="41" t="inlineStr">
+        <is>
+          <t>17-43</t>
+        </is>
+      </c>
+      <c r="D404" s="41" t="inlineStr">
+        <is>
+          <t>Floor arrangement</t>
+        </is>
+      </c>
+      <c r="E404" s="41" t="inlineStr">
+        <is>
+          <t>Ubicación Superior Twin</t>
+        </is>
+      </c>
+      <c r="F404" s="41" t="inlineStr">
+        <is>
+          <t>Solo planta baja</t>
+        </is>
+      </c>
+      <c r="G404" s="41" t="inlineStr">
+        <is>
+          <t>Planta baja y planta alta</t>
+        </is>
+      </c>
+      <c r="H404" s="41" t="n"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B405" s="41" t="inlineStr">
+        <is>
+          <t>GHL Relax Club Hotel el Puente</t>
+        </is>
+      </c>
+      <c r="C405" s="41" t="inlineStr">
+        <is>
+          <t>18-01</t>
+        </is>
+      </c>
+      <c r="D405" s="41" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E405" s="41" t="inlineStr">
+        <is>
+          <t>Código de vestimenta</t>
+        </is>
+      </c>
+      <c r="F405" s="41" t="inlineStr">
+        <is>
+          <t>Casual con detalle de outfits</t>
+        </is>
+      </c>
+      <c r="G405" s="41" t="inlineStr">
+        <is>
+          <t>Casual; no se permite traje de baño ni ropa húmeda</t>
+        </is>
+      </c>
+      <c r="H405" s="41" t="n"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B406" s="41" t="inlineStr">
+        <is>
+          <t>GHL Relax Club Hotel el Puente</t>
+        </is>
+      </c>
+      <c r="C406" s="41" t="inlineStr">
+        <is>
+          <t>20-21</t>
+        </is>
+      </c>
+      <c r="D406" s="41" t="inlineStr">
+        <is>
+          <t>Celebration</t>
+        </is>
+      </c>
+      <c r="E406" s="41" t="inlineStr">
+        <is>
+          <t>Teléfono de eventos</t>
+        </is>
+      </c>
+      <c r="F406" s="41" t="inlineStr">
+        <is>
+          <t>+57 601 8366824</t>
+        </is>
+      </c>
+      <c r="G406" s="41" t="inlineStr">
+        <is>
+          <t>+57 321 469 3086</t>
+        </is>
+      </c>
+      <c r="H406" s="41" t="n"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B407" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Bucaramanga</t>
+        </is>
+      </c>
+      <c r="C407" s="41" t="inlineStr">
+        <is>
+          <t>13-06</t>
+        </is>
+      </c>
+      <c r="D407" s="41" t="inlineStr">
+        <is>
+          <t>Room service</t>
+        </is>
+      </c>
+      <c r="E407" s="41" t="inlineStr">
+        <is>
+          <t>Horario</t>
+        </is>
+      </c>
+      <c r="F407" s="41" t="inlineStr">
+        <is>
+          <t>Disponible 24/7</t>
+        </is>
+      </c>
+      <c r="G407" s="41" t="inlineStr">
+        <is>
+          <t>06:00 a 22:00, jornada continua</t>
+        </is>
+      </c>
+      <c r="H407" s="41" t="n"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B408" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Bucaramanga</t>
+        </is>
+      </c>
+      <c r="C408" s="41" t="inlineStr">
+        <is>
+          <t>17-01</t>
+        </is>
+      </c>
+      <c r="D408" s="41" t="inlineStr">
+        <is>
+          <t>Bar</t>
+        </is>
+      </c>
+      <c r="E408" s="41" t="inlineStr">
+        <is>
+          <t>Horario</t>
+        </is>
+      </c>
+      <c r="F408" s="41" t="inlineStr">
+        <is>
+          <t>Lun-Jue 12:00-23:00; Vie-Sáb 12:00-23:59</t>
+        </is>
+      </c>
+      <c r="G408" s="41" t="inlineStr">
+        <is>
+          <t>Dom-Lun 12:00-22:00; Vie-Sáb 12:00-23:00</t>
+        </is>
+      </c>
+      <c r="H408" s="41" t="n"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B409" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Bucaramanga</t>
+        </is>
+      </c>
+      <c r="C409" s="41" t="inlineStr">
+        <is>
+          <t>17-34</t>
+        </is>
+      </c>
+      <c r="D409" s="41" t="inlineStr">
+        <is>
+          <t>Rooftop</t>
+        </is>
+      </c>
+      <c r="E409" s="41" t="inlineStr">
+        <is>
+          <t>Días y horario</t>
+        </is>
+      </c>
+      <c r="F409" s="41" t="inlineStr">
+        <is>
+          <t>Cerrado domingos; horarios variables</t>
+        </is>
+      </c>
+      <c r="G409" s="41" t="inlineStr">
+        <is>
+          <t>Abierto todos los días; horario unificado (Vie-Sáb hasta 23:00, resto hasta 22:00)</t>
+        </is>
+      </c>
+      <c r="H409" s="41" t="n"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B410" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Bucaramanga</t>
+        </is>
+      </c>
+      <c r="C410" s="41" t="inlineStr">
+        <is>
+          <t>18-01</t>
+        </is>
+      </c>
+      <c r="D410" s="41" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E410" s="41" t="inlineStr">
+        <is>
+          <t>Horario</t>
+        </is>
+      </c>
+      <c r="F410" s="41" t="inlineStr">
+        <is>
+          <t>Variable por día hasta 00:00 Vie-Sáb</t>
+        </is>
+      </c>
+      <c r="G410" s="41" t="inlineStr">
+        <is>
+          <t>Horario unificado, Vie-Sáb hasta 23:00, resto hasta 22:00</t>
+        </is>
+      </c>
+      <c r="H410" s="41" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:H227"/>

--- a/Base_Maestra_Consolidada_Dialogos_Chatbot.xlsx
+++ b/Base_Maestra_Consolidada_Dialogos_Chatbot.xlsx
@@ -6650,14 +6650,29 @@
           <t>02/08/2026</t>
         </is>
       </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K127" s="44" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>7 diálogos modificados: desayuno, taxi, habitaciones conectadas, ducha/tina, mascotas, restaurante, celebraciones</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>El hotel envió el formato de manera informal (Antes/Ahora); se interpretó "Ahora" como el valor "después"</t>
+        </is>
+      </c>
+      <c r="K127" s="46" t="inlineStr">
+        <is>
+          <t>Pendiente actualización</t>
         </is>
       </c>
     </row>
@@ -6912,13 +6927,13 @@
         <v>42</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>4</v>
@@ -6928,7 +6943,7 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="I6" s="17">
@@ -7051,23 +7066,23 @@
         <v>42</v>
       </c>
       <c r="C4" s="19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4" s="19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" s="19" t="n">
         <v>4</v>
       </c>
       <c r="G4" s="20" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.4047619047619048</v>
       </c>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t>███████████░░░░░░░░░░░░░░░░░░░</t>
+          <t>████████████░░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
       <c r="I4" s="22" t="inlineStr">
@@ -7156,19 +7171,19 @@
         <v>126</v>
       </c>
       <c r="C7" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D7" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F7" t="n">
         <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4365079365079365</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -7200,7 +7215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H410"/>
+  <dimension ref="A1:H417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -22750,6 +22765,272 @@
         </is>
       </c>
       <c r="H410" s="41" t="n"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B411" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Puno</t>
+        </is>
+      </c>
+      <c r="C411" s="41" t="inlineStr">
+        <is>
+          <t>12-01</t>
+        </is>
+      </c>
+      <c r="D411" s="41" t="inlineStr">
+        <is>
+          <t>Breakfast time</t>
+        </is>
+      </c>
+      <c r="E411" s="41" t="inlineStr">
+        <is>
+          <t>Horario y precio</t>
+        </is>
+      </c>
+      <c r="F411" s="41" t="inlineStr">
+        <is>
+          <t>10:30am; precio sin especificar</t>
+        </is>
+      </c>
+      <c r="G411" s="41" t="inlineStr">
+        <is>
+          <t>09:30am; USD 18.00</t>
+        </is>
+      </c>
+      <c r="H411" s="41" t="n"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B412" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Puno</t>
+        </is>
+      </c>
+      <c r="C412" s="41" t="inlineStr">
+        <is>
+          <t>13-53</t>
+        </is>
+      </c>
+      <c r="D412" s="41" t="inlineStr">
+        <is>
+          <t>Taxi</t>
+        </is>
+      </c>
+      <c r="E412" s="41" t="inlineStr">
+        <is>
+          <t>Precios</t>
+        </is>
+      </c>
+      <c r="F412" s="41" t="inlineStr">
+        <is>
+          <t>⚠ No especificado</t>
+        </is>
+      </c>
+      <c r="G412" s="41" t="inlineStr">
+        <is>
+          <t>Downtown $6.00; Aeropuerto Juliaca $80.00</t>
+        </is>
+      </c>
+      <c r="H412" s="41" t="n"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B413" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Puno</t>
+        </is>
+      </c>
+      <c r="C413" s="41" t="inlineStr">
+        <is>
+          <t>14-03</t>
+        </is>
+      </c>
+      <c r="D413" s="41" t="inlineStr">
+        <is>
+          <t>Family accommodation</t>
+        </is>
+      </c>
+      <c r="E413" s="41" t="inlineStr">
+        <is>
+          <t>Habitaciones conectadas</t>
+        </is>
+      </c>
+      <c r="F413" s="41" t="inlineStr">
+        <is>
+          <t>⚠ No especificado</t>
+        </is>
+      </c>
+      <c r="G413" s="41" t="inlineStr">
+        <is>
+          <t>Se elimina la mención de habitaciones conectadas</t>
+        </is>
+      </c>
+      <c r="H413" s="41" t="n"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B414" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Puno</t>
+        </is>
+      </c>
+      <c r="C414" s="41" t="inlineStr">
+        <is>
+          <t>15-09</t>
+        </is>
+      </c>
+      <c r="D414" s="41" t="inlineStr">
+        <is>
+          <t>Shower, bathtub, jacuzzi, pool</t>
+        </is>
+      </c>
+      <c r="E414" s="41" t="inlineStr">
+        <is>
+          <t>Ducha y tina</t>
+        </is>
+      </c>
+      <c r="F414" s="41" t="inlineStr">
+        <is>
+          <t>⚠ No especificado</t>
+        </is>
+      </c>
+      <c r="G414" s="41" t="inlineStr">
+        <is>
+          <t>Disponibles con garantía desde reservas</t>
+        </is>
+      </c>
+      <c r="H414" s="41" t="n"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B415" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Puno</t>
+        </is>
+      </c>
+      <c r="C415" s="41" t="inlineStr">
+        <is>
+          <t>16-10</t>
+        </is>
+      </c>
+      <c r="D415" s="41" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="E415" s="41" t="inlineStr">
+        <is>
+          <t>Restricciones y tasas por daños</t>
+        </is>
+      </c>
+      <c r="F415" s="41" t="inlineStr">
+        <is>
+          <t>⚠ No especificado</t>
+        </is>
+      </c>
+      <c r="G415" s="41" t="inlineStr">
+        <is>
+          <t>Máximo 1 mascota hasta 15kg; tasas por daños: USD 80 muebles, USD 50 lencería, USD 400 colchón</t>
+        </is>
+      </c>
+      <c r="H415" s="41" t="n"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B416" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Puno</t>
+        </is>
+      </c>
+      <c r="C416" s="41" t="inlineStr">
+        <is>
+          <t>18-01</t>
+        </is>
+      </c>
+      <c r="D416" s="41" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E416" s="41" t="inlineStr">
+        <is>
+          <t>Picnic y capacidad Inkafe</t>
+        </is>
+      </c>
+      <c r="F416" s="41" t="inlineStr">
+        <is>
+          <t>⚠ No especificado</t>
+        </is>
+      </c>
+      <c r="G416" s="41" t="inlineStr">
+        <is>
+          <t>Picnic con reserva mínimo 24h antes; capacidad máxima Inkafe 90 personas</t>
+        </is>
+      </c>
+      <c r="H416" s="41" t="n"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B417" s="41" t="inlineStr">
+        <is>
+          <t>Sonesta Puno</t>
+        </is>
+      </c>
+      <c r="C417" s="41" t="inlineStr">
+        <is>
+          <t>20-21</t>
+        </is>
+      </c>
+      <c r="D417" s="41" t="inlineStr">
+        <is>
+          <t>Celebration</t>
+        </is>
+      </c>
+      <c r="E417" s="41" t="inlineStr">
+        <is>
+          <t>Correo de contacto</t>
+        </is>
+      </c>
+      <c r="F417" s="41" t="inlineStr">
+        <is>
+          <t>ubaldo.laquise@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="G417" s="41" t="inlineStr">
+        <is>
+          <t>restaurante.spipuno@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="H417" s="41" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:H227"/>

--- a/Base_Maestra_Consolidada_Dialogos_Chatbot.xlsx
+++ b/Base_Maestra_Consolidada_Dialogos_Chatbot.xlsx
@@ -5736,14 +5736,24 @@
           <t>02/08/2026</t>
         </is>
       </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K105" s="44" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>4 diálogos modificados: contacto eventos, desayuno, bar, terraza</t>
+        </is>
+      </c>
+      <c r="K105" s="46" t="inlineStr">
+        <is>
+          <t>Pendiente actualización</t>
         </is>
       </c>
     </row>
@@ -6927,13 +6937,13 @@
         <v>42</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>4</v>
@@ -6943,7 +6953,7 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="I6" s="17">
@@ -7066,23 +7076,23 @@
         <v>42</v>
       </c>
       <c r="C4" s="19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" s="19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E4" s="19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" s="19" t="n">
         <v>4</v>
       </c>
       <c r="G4" s="20" t="n">
-        <v>0.4047619047619048</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t>████████████░░░░░░░░░░░░░░░░░░</t>
+          <t>█████████████░░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
       <c r="I4" s="22" t="inlineStr">
@@ -7171,23 +7181,23 @@
         <v>126</v>
       </c>
       <c r="C7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D7" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F7" t="n">
         <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4523809523809524</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>█████████████░░░░░░░░░░░░░░░░░</t>
+          <t>██████████████░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
     </row>
@@ -7215,7 +7225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H417"/>
+  <dimension ref="A1:H421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -23031,6 +23041,158 @@
         </is>
       </c>
       <c r="H417" s="41" t="n"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B418" s="41" t="inlineStr">
+        <is>
+          <t>GHL Style Barrancabermeja</t>
+        </is>
+      </c>
+      <c r="C418" s="41" t="inlineStr">
+        <is>
+          <t>16-02</t>
+        </is>
+      </c>
+      <c r="D418" s="41" t="inlineStr">
+        <is>
+          <t>Contact staff</t>
+        </is>
+      </c>
+      <c r="E418" s="41" t="inlineStr">
+        <is>
+          <t>Teléfono Eventos</t>
+        </is>
+      </c>
+      <c r="F418" s="41" t="inlineStr">
+        <is>
+          <t>+57 319 7530014</t>
+        </is>
+      </c>
+      <c r="G418" s="41" t="inlineStr">
+        <is>
+          <t>+57 311 2845935</t>
+        </is>
+      </c>
+      <c r="H418" s="41" t="n"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B419" s="41" t="inlineStr">
+        <is>
+          <t>GHL Style Barrancabermeja</t>
+        </is>
+      </c>
+      <c r="C419" s="41" t="inlineStr">
+        <is>
+          <t>12-02</t>
+        </is>
+      </c>
+      <c r="D419" s="41" t="inlineStr">
+        <is>
+          <t>Breakfast rates</t>
+        </is>
+      </c>
+      <c r="E419" s="41" t="inlineStr">
+        <is>
+          <t>Precio por adulto</t>
+        </is>
+      </c>
+      <c r="F419" s="41" t="inlineStr">
+        <is>
+          <t>36.000 COP</t>
+        </is>
+      </c>
+      <c r="G419" s="41" t="inlineStr">
+        <is>
+          <t>59.000 COP</t>
+        </is>
+      </c>
+      <c r="H419" s="41" t="n"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B420" s="41" t="inlineStr">
+        <is>
+          <t>GHL Style Barrancabermeja</t>
+        </is>
+      </c>
+      <c r="C420" s="41" t="inlineStr">
+        <is>
+          <t>17-01</t>
+        </is>
+      </c>
+      <c r="D420" s="41" t="inlineStr">
+        <is>
+          <t>Bar</t>
+        </is>
+      </c>
+      <c r="E420" s="41" t="inlineStr">
+        <is>
+          <t>Horario y acceso</t>
+        </is>
+      </c>
+      <c r="F420" s="41" t="inlineStr">
+        <is>
+          <t>17:00 a 22:00; solo clientes del hotel</t>
+        </is>
+      </c>
+      <c r="G420" s="41" t="inlineStr">
+        <is>
+          <t>11:00 a 22:00; abierto para visitantes y huéspedes</t>
+        </is>
+      </c>
+      <c r="H420" s="41" t="n"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B421" s="41" t="inlineStr">
+        <is>
+          <t>GHL Style Barrancabermeja</t>
+        </is>
+      </c>
+      <c r="C421" s="41" t="inlineStr">
+        <is>
+          <t>17-34</t>
+        </is>
+      </c>
+      <c r="D421" s="41" t="inlineStr">
+        <is>
+          <t>Rooftop</t>
+        </is>
+      </c>
+      <c r="E421" s="41" t="inlineStr">
+        <is>
+          <t>Horario</t>
+        </is>
+      </c>
+      <c r="F421" s="41" t="inlineStr">
+        <is>
+          <t>17:00 a 22:00 todos los días</t>
+        </is>
+      </c>
+      <c r="G421" s="41" t="inlineStr">
+        <is>
+          <t>11:00 a 22:00 todos los días</t>
+        </is>
+      </c>
+      <c r="H421" s="41" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:H227"/>

--- a/Base_Maestra_Consolidada_Dialogos_Chatbot.xlsx
+++ b/Base_Maestra_Consolidada_Dialogos_Chatbot.xlsx
@@ -6106,22 +6106,27 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
+          <t>Sergio Víctor Alejandro Yevenes Escobar</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>sergio.yevenes@ghlhoteles.com</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>02/08/2026</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>reservas.parklake@ghlhoteles.com</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>02/08/2026</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Nuevo contacto: Jefe de Recepción. Antes solo se tenía el correo genérico reservas.parklake@ghlhoteles.com, sin nombre de contacto.</t>
         </is>
       </c>
       <c r="K114" s="44" t="inlineStr">

--- a/Base_Maestra_Consolidada_Dialogos_Chatbot.xlsx
+++ b/Base_Maestra_Consolidada_Dialogos_Chatbot.xlsx
@@ -5131,14 +5131,29 @@
           <t>02/08/2026</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K90" s="44" t="inlineStr">
-        <is>
-          <t>Sin respuesta</t>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>7 diálogos modificados: mascotas, restaurante</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>⚠ Verificar con el hotel: 10-71 (Payment method) solo cambió el idioma de los rótulos y una nota de 'Moneda Local' que desapareció — no se registró como cambio real. 17-43 (Floor arrangement) tenía anotado un posible teléfono adicional 314 8839675 que no aparece en el archivo final — no se registró.</t>
+        </is>
+      </c>
+      <c r="K90" s="46" t="inlineStr">
+        <is>
+          <t>Pendiente actualización</t>
         </is>
       </c>
     </row>
@@ -6942,13 +6957,13 @@
         <v>42</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>4</v>
@@ -6958,7 +6973,7 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="I6" s="17">
@@ -7081,23 +7096,23 @@
         <v>42</v>
       </c>
       <c r="C4" s="19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E4" s="19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4" s="19" t="n">
         <v>4</v>
       </c>
       <c r="G4" s="20" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4523809523809524</v>
       </c>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t>█████████████░░░░░░░░░░░░░░░░░</t>
+          <t>██████████████░░░░░░░░░░░░░░░░</t>
         </is>
       </c>
       <c r="I4" s="22" t="inlineStr">
@@ -7186,19 +7201,19 @@
         <v>126</v>
       </c>
       <c r="C7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D7" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F7" t="n">
         <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4523809523809524</v>
+        <v>0.4603174603174603</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -7230,7 +7245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H421"/>
+  <dimension ref="A1:H428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -23198,6 +23213,272 @@
         </is>
       </c>
       <c r="H421" s="41" t="n"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B422" s="41" t="inlineStr">
+        <is>
+          <t>Bioxury</t>
+        </is>
+      </c>
+      <c r="C422" s="41" t="inlineStr">
+        <is>
+          <t>16-10</t>
+        </is>
+      </c>
+      <c r="D422" s="41" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="E422" s="41" t="inlineStr">
+        <is>
+          <t>Máximo mascotas por habitación</t>
+        </is>
+      </c>
+      <c r="F422" s="41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G422" s="41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H422" s="41" t="n"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B423" s="41" t="inlineStr">
+        <is>
+          <t>Bioxury</t>
+        </is>
+      </c>
+      <c r="C423" s="41" t="inlineStr">
+        <is>
+          <t>16-10</t>
+        </is>
+      </c>
+      <c r="D423" s="41" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="E423" s="41" t="inlineStr">
+        <is>
+          <t>Peso máximo</t>
+        </is>
+      </c>
+      <c r="F423" s="41" t="inlineStr">
+        <is>
+          <t>5 kg</t>
+        </is>
+      </c>
+      <c r="G423" s="41" t="inlineStr">
+        <is>
+          <t>10 kg</t>
+        </is>
+      </c>
+      <c r="H423" s="41" t="n"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B424" s="41" t="inlineStr">
+        <is>
+          <t>Bioxury</t>
+        </is>
+      </c>
+      <c r="C424" s="41" t="inlineStr">
+        <is>
+          <t>16-10</t>
+        </is>
+      </c>
+      <c r="D424" s="41" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="E424" s="41" t="inlineStr">
+        <is>
+          <t>Altura máxima</t>
+        </is>
+      </c>
+      <c r="F424" s="41" t="inlineStr">
+        <is>
+          <t>20 cm</t>
+        </is>
+      </c>
+      <c r="G424" s="41" t="inlineStr">
+        <is>
+          <t>30 cm</t>
+        </is>
+      </c>
+      <c r="H424" s="41" t="n"/>
+    </row>
+    <row r="425">
+      <c r="A425" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B425" s="41" t="inlineStr">
+        <is>
+          <t>Bioxury</t>
+        </is>
+      </c>
+      <c r="C425" s="41" t="inlineStr">
+        <is>
+          <t>16-10</t>
+        </is>
+      </c>
+      <c r="D425" s="41" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="E425" s="41" t="inlineStr">
+        <is>
+          <t>Tasa por mascota</t>
+        </is>
+      </c>
+      <c r="F425" s="41" t="inlineStr">
+        <is>
+          <t>90.000 COP/día</t>
+        </is>
+      </c>
+      <c r="G425" s="41" t="inlineStr">
+        <is>
+          <t>119.000 COP/día</t>
+        </is>
+      </c>
+      <c r="H425" s="41" t="n"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B426" s="41" t="inlineStr">
+        <is>
+          <t>Bioxury</t>
+        </is>
+      </c>
+      <c r="C426" s="41" t="inlineStr">
+        <is>
+          <t>16-10</t>
+        </is>
+      </c>
+      <c r="D426" s="41" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="E426" s="41" t="inlineStr">
+        <is>
+          <t>Zonas donde no se permiten mascotas</t>
+        </is>
+      </c>
+      <c r="F426" s="41" t="inlineStr">
+        <is>
+          <t>…Gimnasio y Salvaje</t>
+        </is>
+      </c>
+      <c r="G426" s="41" t="inlineStr">
+        <is>
+          <t>…Playas, Gimnasio, Salvaje y Gitane</t>
+        </is>
+      </c>
+      <c r="H426" s="41" t="n"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B427" s="41" t="inlineStr">
+        <is>
+          <t>Bioxury</t>
+        </is>
+      </c>
+      <c r="C427" s="41" t="inlineStr">
+        <is>
+          <t>16-10</t>
+        </is>
+      </c>
+      <c r="D427" s="41" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="E427" s="41" t="inlineStr">
+        <is>
+          <t>Cama para mascotas</t>
+        </is>
+      </c>
+      <c r="F427" s="41" t="inlineStr">
+        <is>
+          <t>No disponible</t>
+        </is>
+      </c>
+      <c r="G427" s="41" t="inlineStr">
+        <is>
+          <t>Disponible de manera gratuita</t>
+        </is>
+      </c>
+      <c r="H427" s="41" t="n"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="43" t="inlineStr">
+        <is>
+          <t>Ago-26</t>
+        </is>
+      </c>
+      <c r="B428" s="41" t="inlineStr">
+        <is>
+          <t>Bioxury</t>
+        </is>
+      </c>
+      <c r="C428" s="41" t="inlineStr">
+        <is>
+          <t>18-01</t>
+        </is>
+      </c>
+      <c r="D428" s="41" t="inlineStr">
+        <is>
+          <t>Restaurant</t>
+        </is>
+      </c>
+      <c r="E428" s="41" t="inlineStr">
+        <is>
+          <t>Horario apertura Restaurante Salvaje</t>
+        </is>
+      </c>
+      <c r="F428" s="41" t="inlineStr">
+        <is>
+          <t>12:00–20:00</t>
+        </is>
+      </c>
+      <c r="G428" s="41" t="inlineStr">
+        <is>
+          <t>12:00–21:00</t>
+        </is>
+      </c>
+      <c r="H428" s="41" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:H227"/>

--- a/Base_Maestra_Consolidada_Dialogos_Chatbot.xlsx
+++ b/Base_Maestra_Consolidada_Dialogos_Chatbot.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -189,6 +189,11 @@
     <font>
       <name val="Calibri"/>
       <color rgb="00856404"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00006100"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -415,7 +420,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -539,6 +544,7 @@
     <xf numFmtId="0" fontId="27" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="29" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5062,9 +5068,14 @@
           <t>2 diálogos modificados: Breakfast time, Fitness gym</t>
         </is>
       </c>
-      <c r="K88" s="46" t="inlineStr">
-        <is>
-          <t>Pendiente actualización</t>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="K88" s="47" t="inlineStr">
+        <is>
+          <t>Actualizado</t>
         </is>
       </c>
     </row>
@@ -5146,14 +5157,19 @@
           <t>7 diálogos modificados: mascotas, restaurante</t>
         </is>
       </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
       <c r="J90" t="inlineStr">
         <is>
           <t>⚠ Verificar con el hotel: 10-71 (Payment method) solo cambió el idioma de los rótulos y una nota de 'Moneda Local' que desapareció — no se registró como cambio real. 17-43 (Floor arrangement) tenía anotado un posible teléfono adicional 314 8839675 que no aparece en el archivo final — no se registró.</t>
         </is>
       </c>
-      <c r="K90" s="46" t="inlineStr">
-        <is>
-          <t>Pendiente actualización</t>
+      <c r="K90" s="47" t="inlineStr">
+        <is>
+          <t>Actualizado</t>
         </is>
       </c>
     </row>
@@ -5235,9 +5251,14 @@
           <t>14 diálogos modificados: Contact staff, Laundry/paraguas, Invoice, Currencies, Accommodation, Family accommodation, ...</t>
         </is>
       </c>
-      <c r="K92" s="46" t="inlineStr">
-        <is>
-          <t>Pendiente actualización</t>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="K92" s="47" t="inlineStr">
+        <is>
+          <t>Actualizado</t>
         </is>
       </c>
     </row>
@@ -5598,9 +5619,14 @@
           <t>11 diálogos modificados: Opening, closing &amp; renovation, Day use reservation, Extra bed, View, TV, Pets, ...</t>
         </is>
       </c>
-      <c r="K101" s="46" t="inlineStr">
-        <is>
-          <t>Pendiente actualización</t>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="K101" s="47" t="inlineStr">
+        <is>
+          <t>Actualizado</t>
         </is>
       </c>
     </row>
@@ -5766,9 +5792,14 @@
           <t>4 diálogos modificados: contacto eventos, desayuno, bar, terraza</t>
         </is>
       </c>
-      <c r="K105" s="46" t="inlineStr">
-        <is>
-          <t>Pendiente actualización</t>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="K105" s="47" t="inlineStr">
+        <is>
+          <t>Actualizado</t>
         </is>
       </c>
     </row>
@@ -5813,9 +5844,14 @@
           <t>3 diálogos modificados: Business meetings, Breakfast rates, Private transfer</t>
         </is>
       </c>
-      <c r="K106" s="46" t="inlineStr">
-        <is>
-          <t>Pendiente actualización</t>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="K106" s="47" t="inlineStr">
+        <is>
+          <t>Actualizado</t>
         </is>
       </c>
     </row>
@@ -5897,9 +5933,14 @@
           <t>7 diálogos modificados: Payment method, Check-in time, Check-out time, Breakfast time, Breakfast rates, Pets, ...</t>
         </is>
       </c>
-      <c r="K108" s="46" t="inlineStr">
-        <is>
-          <t>Pendiente actualización</t>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="K108" s="47" t="inlineStr">
+        <is>
+          <t>Actualizado</t>
         </is>
       </c>
     </row>
@@ -5944,9 +5985,14 @@
           <t>2 diálogos modificados: Room service, Restaurant</t>
         </is>
       </c>
-      <c r="K109" s="46" t="inlineStr">
-        <is>
-          <t>Pendiente actualización</t>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="K109" s="47" t="inlineStr">
+        <is>
+          <t>Actualizado</t>
         </is>
       </c>
     </row>
@@ -6028,9 +6074,14 @@
           <t>11 diálogos modificados: City tax, fees &amp; VAT, Payment method, Kids, Private transfer, Taxi, Smoking, ...</t>
         </is>
       </c>
-      <c r="K111" s="46" t="inlineStr">
-        <is>
-          <t>Pendiente actualización</t>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="K111" s="47" t="inlineStr">
+        <is>
+          <t>Actualizado</t>
         </is>
       </c>
     </row>
@@ -6228,9 +6279,14 @@
           <t>4 diálogos modificados: Room service, Bar, Rooftop, Restaurant</t>
         </is>
       </c>
-      <c r="K116" s="46" t="inlineStr">
-        <is>
-          <t>Pendiente actualización</t>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="K116" s="47" t="inlineStr">
+        <is>
+          <t>Actualizado</t>
         </is>
       </c>
     </row>
@@ -6396,9 +6452,14 @@
           <t>17 diálogos modificados: Contact staff, Check-in time, Check-out time, Breakfast rates, Parking, Connecting accommodation, ...</t>
         </is>
       </c>
-      <c r="K120" s="46" t="inlineStr">
-        <is>
-          <t>Pendiente actualización</t>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="K120" s="47" t="inlineStr">
+        <is>
+          <t>Actualizado</t>
         </is>
       </c>
     </row>
@@ -6443,9 +6504,14 @@
           <t>14 diálogos modificados: Breakfast reservation, Medical services, Currencies, Private transfer reservation, Accommodation, Smoking, ...</t>
         </is>
       </c>
-      <c r="K121" s="46" t="inlineStr">
-        <is>
-          <t>Pendiente actualización</t>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="K121" s="47" t="inlineStr">
+        <is>
+          <t>Actualizado</t>
         </is>
       </c>
     </row>
@@ -6490,9 +6556,14 @@
           <t>5 diálogos modificados: Breakfast time, Breakfast rates, Room service, Extra bed, Balcony &amp; windows</t>
         </is>
       </c>
-      <c r="K122" s="46" t="inlineStr">
-        <is>
-          <t>Pendiente actualización</t>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="K122" s="47" t="inlineStr">
+        <is>
+          <t>Actualizado</t>
         </is>
       </c>
     </row>
@@ -6611,9 +6682,14 @@
           <t>1 diálogos modificados: Breakfast rates</t>
         </is>
       </c>
-      <c r="K125" s="46" t="inlineStr">
-        <is>
-          <t>Pendiente actualización</t>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="K125" s="47" t="inlineStr">
+        <is>
+          <t>Actualizado</t>
         </is>
       </c>
     </row>
@@ -6695,14 +6771,19 @@
           <t>7 diálogos modificados: desayuno, taxi, habitaciones conectadas, ducha/tina, mascotas, restaurante, celebraciones</t>
         </is>
       </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
       <c r="J127" t="inlineStr">
         <is>
           <t>El hotel envió el formato de manera informal (Antes/Ahora); se interpretó "Ahora" como el valor "después"</t>
         </is>
       </c>
-      <c r="K127" s="46" t="inlineStr">
-        <is>
-          <t>Pendiente actualización</t>
+      <c r="K127" s="47" t="inlineStr">
+        <is>
+          <t>Actualizado</t>
         </is>
       </c>
     </row>
@@ -6969,7 +7050,7 @@
         <v>4</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
